--- a/examples/validation_results/validation_frame_member_loads.xlsx
+++ b/examples/validation_results/validation_frame_member_loads.xlsx
@@ -643,25 +643,25 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>3.595119805279563</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>-5.817587131184721e-06</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>3.595127663702197</v>
       </c>
     </row>
     <row r="7">
@@ -678,25 +678,25 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>3.595127663700326</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +713,25 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>3.596184483337589</v>
       </c>
     </row>
     <row r="9">
@@ -748,25 +748,25 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>3.59618448333946</v>
       </c>
     </row>
     <row r="10">
@@ -783,25 +783,25 @@
         <v>12</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>8.113133295381624</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1.276246312356512e-06</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>8.113142201635418</v>
       </c>
     </row>
     <row r="11">
@@ -818,25 +818,25 @@
         <v>12</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>8.113142201630454</v>
       </c>
     </row>
     <row r="12">
@@ -853,25 +853,25 @@
         <v>12</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>8.114184384690539</v>
       </c>
     </row>
     <row r="13">
@@ -888,25 +888,25 @@
         <v>12</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="F13" t="n">
-        <v>-0</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>8.1141843846955</v>
       </c>
     </row>
     <row r="14">
@@ -923,25 +923,25 @@
         <v>18</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>11.24253477912758</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>-2.886833036039658e-07</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>11.24254353576703</v>
       </c>
     </row>
     <row r="15">
@@ -958,25 +958,25 @@
         <v>18</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="F15" t="n">
-        <v>-0</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>11.24254353575955</v>
       </c>
     </row>
     <row r="16">
@@ -993,25 +993,25 @@
         <v>18</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>11.24365756438923</v>
       </c>
     </row>
     <row r="17">
@@ -1028,25 +1028,25 @@
         <v>18</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="I17" t="n">
-        <v>-0</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="K17" t="n">
-        <v>0</v>
+        <v>11.2436575643967</v>
       </c>
     </row>
     <row r="18">
@@ -1063,25 +1063,25 @@
         <v>24</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>12.7636275507655</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>1.041020896839185e-07</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>12.76363588680199</v>
       </c>
     </row>
     <row r="19">
@@ -1098,25 +1098,25 @@
         <v>24</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>12.76362755075735</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-1.041020131429611e-07</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>12.76363588679385</v>
       </c>
     </row>
     <row r="20">
@@ -1133,25 +1133,25 @@
         <v>24</v>
       </c>
       <c r="E20" t="n">
-        <v>-0</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="I20" t="n">
-        <v>-0</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="J20" t="n">
-        <v>-0</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>12.7643256963182</v>
       </c>
     </row>
     <row r="21">
@@ -1168,25 +1168,25 @@
         <v>24</v>
       </c>
       <c r="E21" t="n">
-        <v>-0</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="H21" t="n">
-        <v>-0</v>
+        <v>-1.041020899760041e-07</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>12.76432569632636</v>
       </c>
     </row>
   </sheetData>
@@ -1242,19 +1242,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>12.76432569632636</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-0.01458744045581826</v>
       </c>
     </row>
     <row r="3">
@@ -1264,19 +1264,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-0.01458744045581826</v>
       </c>
     </row>
     <row r="4">
@@ -1286,19 +1286,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>11</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0.012021337085073</v>
       </c>
     </row>
     <row r="5">
@@ -1308,19 +1308,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>1</v>
+        <v>19</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.01458744045581832</v>
       </c>
     </row>
   </sheetData>
@@ -1379,22 +1379,22 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>-462.4872063002725</v>
       </c>
       <c r="C2" t="n">
-        <v>0</v>
+        <v>-0.008681138355291034</v>
       </c>
       <c r="D2" t="n">
-        <v>0</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>0.03034842954294979</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>-1811.770631236171</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>-0.04262502787522724</v>
       </c>
     </row>
     <row r="3">
@@ -1402,22 +1402,22 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>0</v>
+        <v>-462.4872063000618</v>
       </c>
       <c r="C3" t="n">
-        <v>0</v>
+        <v>0.00868113856954778</v>
       </c>
       <c r="D3" t="n">
-        <v>0</v>
+        <v>-1187.643359996955</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>-0.03034843041376769</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>-1811.770631235287</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.04262502787392255</v>
       </c>
     </row>
     <row r="4">
@@ -1425,22 +1425,22 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>0</v>
+        <v>-537.5127936996093</v>
       </c>
       <c r="C4" t="n">
-        <v>0</v>
+        <v>-0.008681138569743792</v>
       </c>
       <c r="D4" t="n">
-        <v>0</v>
+        <v>1187.643359996957</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.03034843041456974</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-1887.082488781221</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0.1280965491398132</v>
       </c>
     </row>
     <row r="5">
@@ -1448,22 +1448,22 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>-537.51279369982</v>
       </c>
       <c r="C5" t="n">
-        <v>0</v>
+        <v>0.008681138355098365</v>
       </c>
       <c r="D5" t="n">
-        <v>0</v>
+        <v>1187.643359997</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-0.03034842954215432</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-1887.082488782104</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>0.1280965491385087</v>
       </c>
     </row>
   </sheetData>
@@ -1546,16 +1546,16 @@
         <v>6</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>0.001252788354427215</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>1187.643359997</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>250557.670885443</v>
       </c>
     </row>
     <row r="3">
@@ -1577,16 +1577,16 @@
         <v>6</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="G3" t="n">
-        <v>0</v>
+        <v>0.001252788354427168</v>
       </c>
       <c r="H3" t="n">
-        <v>0</v>
+        <v>1187.643359996955</v>
       </c>
       <c r="I3" t="n">
-        <v>0</v>
+        <v>250557.6708854335</v>
       </c>
     </row>
     <row r="4">
@@ -1608,16 +1608,16 @@
         <v>6</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>-0.00125278835442717</v>
       </c>
       <c r="H4" t="n">
-        <v>0</v>
+        <v>-1187.643359996957</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>-250557.6708854339</v>
       </c>
     </row>
     <row r="5">
@@ -1639,16 +1639,16 @@
         <v>6</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>-0.001252788354427215</v>
       </c>
       <c r="H5" t="n">
-        <v>0</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="I5" t="n">
-        <v>0</v>
+        <v>-250557.670885443</v>
       </c>
     </row>
     <row r="6">
@@ -1670,16 +1670,16 @@
         <v>6</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>0.004504606958510098</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.0007507678264183497</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>711.7278994445956</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>150153.5652836699</v>
       </c>
     </row>
     <row r="7">
@@ -1701,16 +1701,16 @@
         <v>6</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>0.004504606958509978</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.0007507678264183296</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>711.7278994445765</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>150153.5652836659</v>
       </c>
     </row>
     <row r="8">
@@ -1732,16 +1732,16 @@
         <v>6</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-0.004504606958509985</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>-0.0007507678264183309</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>-711.7278994445777</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-150153.5652836662</v>
       </c>
     </row>
     <row r="9">
@@ -1763,16 +1763,16 @@
         <v>6</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-0.004504606958510099</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>-0.0007507678264183498</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-711.7278994445957</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-150153.56528367</v>
       </c>
     </row>
     <row r="10">
@@ -1794,16 +1794,16 @@
         <v>6</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>0.002010446251387233</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>0.0003350743752312055</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>317.6505077191828</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>67014.8750462411</v>
       </c>
     </row>
     <row r="11">
@@ -1825,16 +1825,16 @@
         <v>6</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>0.00201044625138745</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>0.0003350743752312416</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>317.6505077192171</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>67014.87504624833</v>
       </c>
     </row>
     <row r="12">
@@ -1856,16 +1856,16 @@
         <v>6</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-0.002010446251387455</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>-0.0003350743752312425</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>-317.6505077192179</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-67014.8750462485</v>
       </c>
     </row>
     <row r="13">
@@ -1887,16 +1887,16 @@
         <v>6</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-0.002010446251387236</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.0003350743752312061</v>
       </c>
       <c r="H13" t="n">
-        <v>0</v>
+        <v>-317.6505077191833</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-67014.87504624121</v>
       </c>
     </row>
     <row r="14">
@@ -1918,16 +1918,16 @@
         <v>6</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>0.0005556571193576412</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>9.260951989294019e-05</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>87.79382485850731</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>18521.90397858804</v>
       </c>
     </row>
     <row r="15">
@@ -1949,16 +1949,16 @@
         <v>6</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>0.0005556571193578615</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>9.260951989297692e-05</v>
       </c>
       <c r="H15" t="n">
-        <v>0</v>
+        <v>87.79382485854211</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>18521.90397859538</v>
       </c>
     </row>
     <row r="16">
@@ -1980,16 +1980,16 @@
         <v>6</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-0.0005556571193578649</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>-9.260951989297748e-05</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>-87.79382485854266</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-18521.9039785955</v>
       </c>
     </row>
     <row r="17">
@@ -2011,16 +2011,16 @@
         <v>6</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-0.0005556571193576377</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-9.260951989293962e-05</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-87.79382485850675</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-18521.90397858792</v>
       </c>
     </row>
     <row r="18">
@@ -2042,16 +2042,16 @@
         <v>8</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-0.0001052931328663778</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>-1.316164160829722e-05</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>-12.47723624466577</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>-2632.328321659445</v>
       </c>
     </row>
     <row r="19">
@@ -2073,16 +2073,16 @@
         <v>8</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>0.001056821946642028</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>0.0001321027433302535</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>125.2334006770803</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>26420.5486660507</v>
       </c>
     </row>
     <row r="20">
@@ -2104,16 +2104,16 @@
         <v>8</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>0.0001052931328663774</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1.316164160829718e-05</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>12.47723624466572</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>2632.328321659435</v>
       </c>
     </row>
     <row r="21">
@@ -2135,16 +2135,16 @@
         <v>8</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>0.001056821946642472</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.000132102743330309</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>125.2334006771329</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>26420.5486660618</v>
       </c>
     </row>
     <row r="22">
@@ -2166,16 +2166,16 @@
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-0.0001054962997791679</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>-1.318703747239599e-05</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>-12.5013115238314</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>-2637.407494479197</v>
       </c>
     </row>
     <row r="23">
@@ -2197,16 +2197,16 @@
         <v>8</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>0.001042184204001373</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.0001302730255001716</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>123.4988281741627</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>26054.60510003432</v>
       </c>
     </row>
     <row r="24">
@@ -2228,16 +2228,16 @@
         <v>8</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>0.0001054962997791679</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>1.318703747239598e-05</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>12.50131152383139</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>2637.407494479197</v>
       </c>
     </row>
     <row r="25">
@@ -2259,16 +2259,16 @@
         <v>8</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>0.001042184204001373</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>0.0001302730255001716</v>
       </c>
       <c r="H25" t="n">
-        <v>0</v>
+        <v>123.4988281741627</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>26054.60510003432</v>
       </c>
     </row>
     <row r="26">
@@ -2290,16 +2290,16 @@
         <v>8</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-0.0001054548126048016</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>-1.318185157560019e-05</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>-12.49639529366899</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>-2636.370315120039</v>
       </c>
     </row>
     <row r="27">
@@ -2321,16 +2321,16 @@
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>0.001114029497289337</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>0.0001392536871611672</v>
       </c>
       <c r="H27" t="n">
-        <v>0</v>
+        <v>132.0124954287865</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>27850.73743223343</v>
       </c>
     </row>
     <row r="28">
@@ -2352,16 +2352,16 @@
         <v>8</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>0.000105454812604793</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>1.318185157559913e-05</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>12.49639529366798</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>2636.370315119826</v>
       </c>
     </row>
     <row r="29">
@@ -2383,16 +2383,16 @@
         <v>8</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>0.001114029497285784</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>0.0001392536871607231</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>132.0124954283655</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>27850.73743214461</v>
       </c>
     </row>
     <row r="30">
@@ -2414,16 +2414,16 @@
         <v>8</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-0.0001054632224549705</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>-1.318290280687131e-05</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>-12.49739186091401</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>-2636.580561374263</v>
       </c>
     </row>
     <row r="31">
@@ -2445,16 +2445,16 @@
         <v>8</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>0.0006898099748529063</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>8.622624685661329e-05</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>81.74248202006939</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>17245.24937132265</v>
       </c>
     </row>
     <row r="32">
@@ -2476,16 +2476,16 @@
         <v>8</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>0.000105463222454975</v>
       </c>
       <c r="G32" t="n">
-        <v>0</v>
+        <v>1.318290280687187e-05</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>12.49739186091453</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>2636.580561374374</v>
       </c>
     </row>
     <row r="33">
@@ -2507,16 +2507,16 @@
         <v>8</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>0.0006898099748582354</v>
       </c>
       <c r="G33" t="n">
-        <v>0</v>
+        <v>8.622624685727942e-05</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>81.74248202070089</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>17245.24937145588</v>
       </c>
     </row>
   </sheetData>
@@ -2759,10 +2759,10 @@
         <v>6</v>
       </c>
       <c r="E2" t="n">
-        <v>0</v>
+        <v>1187.643359997</v>
       </c>
       <c r="F2" t="n">
-        <v>0</v>
+        <v>250557.670885443</v>
       </c>
       <c r="G2" t="n">
         <v>0</v>
@@ -2783,22 +2783,22 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.595119805279563</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>-5.817587131184721e-06</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="S2" t="n">
         <v>0</v>
@@ -2819,58 +2819,58 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>-3.595119805279563</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>5.817587131184721e-06</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>-0.008681138355291034</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>462.4872063002725</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>-0.04262502787522724</v>
       </c>
       <c r="AI2" t="n">
-        <v>0</v>
+        <v>-1811.770631236171</v>
       </c>
       <c r="AJ2" t="n">
-        <v>0</v>
+        <v>-0.03034842954294979</v>
       </c>
       <c r="AK2" t="n">
-        <v>0</v>
+        <v>1187.643359997</v>
       </c>
       <c r="AL2" t="n">
-        <v>0</v>
+        <v>0.008681138355291034</v>
       </c>
       <c r="AM2" t="n">
-        <v>0</v>
+        <v>-462.4872063002725</v>
       </c>
       <c r="AN2" t="n">
-        <v>0</v>
+        <v>0.04262502787522724</v>
       </c>
       <c r="AO2" t="n">
-        <v>0</v>
+        <v>-963.1526065654646</v>
       </c>
       <c r="AP2" t="n">
-        <v>0</v>
+        <v>-0.02173840058879641</v>
       </c>
     </row>
     <row r="3">
@@ -2887,10 +2887,10 @@
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0</v>
+        <v>1187.643359996955</v>
       </c>
       <c r="F3" t="n">
-        <v>0</v>
+        <v>250557.6708854335</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
@@ -2911,22 +2911,22 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
@@ -2947,58 +2947,58 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>-3.595119805277692</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>-5.817587439357226e-06</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>-1187.643359996955</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>0.00868113856954778</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>462.4872063000618</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>0.04262502787392255</v>
       </c>
       <c r="AI3" t="n">
-        <v>0</v>
+        <v>-1811.770631235287</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0</v>
+        <v>0.03034843041376769</v>
       </c>
       <c r="AK3" t="n">
-        <v>0</v>
+        <v>1187.643359996955</v>
       </c>
       <c r="AL3" t="n">
-        <v>0</v>
+        <v>-0.00868113856954778</v>
       </c>
       <c r="AM3" t="n">
-        <v>0</v>
+        <v>-462.4872063000618</v>
       </c>
       <c r="AN3" t="n">
-        <v>0</v>
+        <v>-0.04262502787392255</v>
       </c>
       <c r="AO3" t="n">
-        <v>0</v>
+        <v>-963.1526065650828</v>
       </c>
       <c r="AP3" t="n">
-        <v>0</v>
+        <v>0.021738401003519</v>
       </c>
     </row>
     <row r="4">
@@ -3015,10 +3015,10 @@
         <v>6</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>-1187.643359996957</v>
       </c>
       <c r="F4" t="n">
-        <v>0</v>
+        <v>-250557.6708854339</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -3039,22 +3039,22 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -3075,58 +3075,58 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>-3.596176627224334</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>5.817587439646455e-06</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>1187.643359996957</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>-0.008681138569743792</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>537.5127936996093</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>-0.1280965491398132</v>
       </c>
       <c r="AI4" t="n">
-        <v>0</v>
+        <v>-1887.082488781221</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0</v>
+        <v>-0.03034843041456974</v>
       </c>
       <c r="AK4" t="n">
-        <v>0</v>
+        <v>-1187.643359996957</v>
       </c>
       <c r="AL4" t="n">
-        <v>0</v>
+        <v>0.008681138569743792</v>
       </c>
       <c r="AM4" t="n">
-        <v>0</v>
+        <v>-387.5127936996093</v>
       </c>
       <c r="AN4" t="n">
-        <v>0</v>
+        <v>0.1280965491398132</v>
       </c>
       <c r="AO4" t="n">
-        <v>0</v>
+        <v>-887.9942734164347</v>
       </c>
       <c r="AP4" t="n">
-        <v>0</v>
+        <v>-0.02173840100389299</v>
       </c>
     </row>
     <row r="5">
@@ -3143,10 +3143,10 @@
         <v>6</v>
       </c>
       <c r="E5" t="n">
-        <v>0</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="F5" t="n">
-        <v>0</v>
+        <v>-250557.670885443</v>
       </c>
       <c r="G5" t="n">
         <v>0</v>
@@ -3167,22 +3167,22 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="S5" t="n">
         <v>0</v>
@@ -3203,58 +3203,58 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>-3.596176627226205</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>-5.817587130890855e-06</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1187.643359997</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>0.008681138355098365</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>537.51279369982</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>0.1280965491385087</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>-1887.082488782104</v>
       </c>
       <c r="AJ5" t="n">
-        <v>0</v>
+        <v>0.03034842954215432</v>
       </c>
       <c r="AK5" t="n">
-        <v>0</v>
+        <v>-1187.643359997</v>
       </c>
       <c r="AL5" t="n">
-        <v>0</v>
+        <v>-0.008681138355098365</v>
       </c>
       <c r="AM5" t="n">
-        <v>0</v>
+        <v>-387.51279369982</v>
       </c>
       <c r="AN5" t="n">
-        <v>0</v>
+        <v>-0.1280965491385087</v>
       </c>
       <c r="AO5" t="n">
-        <v>0</v>
+        <v>-887.9942734168162</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>0.02173840058843586</v>
       </c>
     </row>
     <row r="6">
@@ -3271,118 +3271,118 @@
         <v>6</v>
       </c>
       <c r="E6" t="n">
-        <v>0</v>
+        <v>711.7278994445956</v>
       </c>
       <c r="F6" t="n">
-        <v>0</v>
+        <v>150153.5652836699</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>3.595119805279563</v>
       </c>
       <c r="H6" t="n">
-        <v>0</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="I6" t="n">
-        <v>0</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>-5.817587131184721e-06</v>
       </c>
       <c r="K6" t="n">
-        <v>0</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>8.113133295381624</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>1.276246312356512e-06</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>-3.595119805279563</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>5.817587131184721e-06</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>-8.113133295381624</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>-1.276246312356512e-06</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>-711.7278994445956</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>0.003335535281722257</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>337.2538056231967</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>-8.174341103647093e-05</v>
       </c>
       <c r="AI6" t="n">
-        <v>0</v>
+        <v>-940.3329141341959</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0</v>
+        <v>0.01525604259338728</v>
       </c>
       <c r="AK6" t="n">
-        <v>0</v>
+        <v>711.7278994445956</v>
       </c>
       <c r="AL6" t="n">
-        <v>0</v>
+        <v>-0.003335535281722257</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>-337.2538056231967</v>
       </c>
       <c r="AN6" t="n">
-        <v>0</v>
+        <v>8.174341103647093e-05</v>
       </c>
       <c r="AO6" t="n">
-        <v>0</v>
+        <v>-1083.189919604984</v>
       </c>
       <c r="AP6" t="n">
-        <v>0</v>
+        <v>0.004757169096946262</v>
       </c>
     </row>
     <row r="7">
@@ -3399,118 +3399,118 @@
         <v>6</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>711.7278994445765</v>
       </c>
       <c r="F7" t="n">
-        <v>0</v>
+        <v>150153.5652836659</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="H7" t="n">
-        <v>0</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="K7" t="n">
-        <v>0</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>-3.595119805277692</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>-5.817587439357226e-06</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>-8.113133295376661</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.276246011702428e-06</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>-711.7278994445767</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>-0.003335535075520275</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>337.2538056229537</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>8.174340898744331e-05</v>
       </c>
       <c r="AI7" t="n">
-        <v>0</v>
+        <v>-940.3329141334489</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>-0.01525604198034497</v>
       </c>
       <c r="AK7" t="n">
-        <v>0</v>
+        <v>711.7278994445767</v>
       </c>
       <c r="AL7" t="n">
-        <v>0</v>
+        <v>0.003335535075520275</v>
       </c>
       <c r="AM7" t="n">
-        <v>0</v>
+        <v>-337.2538056229537</v>
       </c>
       <c r="AN7" t="n">
-        <v>0</v>
+        <v>-8.174340898744331e-05</v>
       </c>
       <c r="AO7" t="n">
-        <v>0</v>
+        <v>-1083.189919604273</v>
       </c>
       <c r="AP7" t="n">
-        <v>0</v>
+        <v>-0.004757168472776685</v>
       </c>
     </row>
     <row r="8">
@@ -3527,118 +3527,118 @@
         <v>6</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>-711.7278994445777</v>
       </c>
       <c r="F8" t="n">
-        <v>0</v>
+        <v>-150153.5652836662</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="H8" t="n">
-        <v>0</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="I8" t="n">
-        <v>0</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>-3.596176627224334</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>5.817587439646455e-06</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="Z8" t="n">
-        <v>0</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="AA8" t="n">
-        <v>0</v>
+        <v>-8.114175479580663</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="AD8" t="n">
-        <v>0</v>
+        <v>-1.27624601135778e-06</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>711.7278994445778</v>
       </c>
       <c r="AF8" t="n">
-        <v>0</v>
+        <v>0.003335535075336502</v>
       </c>
       <c r="AG8" t="n">
-        <v>0</v>
+        <v>412.7461943766295</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>-0.0001365709851156582</v>
       </c>
       <c r="AI8" t="n">
-        <v>0</v>
+        <v>-1015.843890303033</v>
       </c>
       <c r="AJ8" t="n">
-        <v>0</v>
+        <v>0.01525604197975264</v>
       </c>
       <c r="AK8" t="n">
-        <v>0</v>
+        <v>-711.7278994445778</v>
       </c>
       <c r="AL8" t="n">
-        <v>0</v>
+        <v>-0.003335535075336502</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>-262.7461943766295</v>
       </c>
       <c r="AN8" t="n">
-        <v>0</v>
+        <v>0.0001365709851156582</v>
       </c>
       <c r="AO8" t="n">
-        <v>0</v>
+        <v>-1010.633275956742</v>
       </c>
       <c r="AP8" t="n">
-        <v>0</v>
+        <v>0.004757168472266371</v>
       </c>
     </row>
     <row r="9">
@@ -3655,118 +3655,118 @@
         <v>6</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>-711.7278994445957</v>
       </c>
       <c r="F9" t="n">
-        <v>0</v>
+        <v>-150153.56528367</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="H9" t="n">
-        <v>0</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="K9" t="n">
-        <v>0</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="N9" t="n">
-        <v>-0</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="R9" t="n">
-        <v>0</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="S9" t="n">
-        <v>0</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="U9" t="n">
-        <v>0</v>
+        <v>-3.596176627226205</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-5.817587130890855e-06</v>
       </c>
       <c r="Y9" t="n">
-        <v>0</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="Z9" t="n">
-        <v>0</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>-8.114175479585626</v>
       </c>
       <c r="AB9" t="n">
-        <v>0</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="AC9" t="n">
-        <v>0</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="AD9" t="n">
-        <v>0</v>
+        <v>1.276246312679776e-06</v>
       </c>
       <c r="AE9" t="n">
-        <v>0</v>
+        <v>711.7278994445958</v>
       </c>
       <c r="AF9" t="n">
-        <v>0</v>
+        <v>-0.003335535281918336</v>
       </c>
       <c r="AG9" t="n">
-        <v>0</v>
+        <v>412.7461943768724</v>
       </c>
       <c r="AH9" t="n">
-        <v>0</v>
+        <v>0.0001365709830680184</v>
       </c>
       <c r="AI9" t="n">
-        <v>0</v>
+        <v>-1015.843890303781</v>
       </c>
       <c r="AJ9" t="n">
-        <v>0</v>
+        <v>-0.01525604259399728</v>
       </c>
       <c r="AK9" t="n">
-        <v>0</v>
+        <v>-711.7278994445958</v>
       </c>
       <c r="AL9" t="n">
-        <v>0</v>
+        <v>0.003335535281918336</v>
       </c>
       <c r="AM9" t="n">
-        <v>0</v>
+        <v>-262.7461943768724</v>
       </c>
       <c r="AN9" t="n">
-        <v>0</v>
+        <v>-0.0001365709830680184</v>
       </c>
       <c r="AO9" t="n">
-        <v>0</v>
+        <v>-1010.633275957454</v>
       </c>
       <c r="AP9" t="n">
-        <v>0</v>
+        <v>-0.00475716909751274</v>
       </c>
     </row>
     <row r="10">
@@ -3783,118 +3783,118 @@
         <v>6</v>
       </c>
       <c r="E10" t="n">
-        <v>0</v>
+        <v>317.6505077191828</v>
       </c>
       <c r="F10" t="n">
-        <v>0</v>
+        <v>67014.8750462411</v>
       </c>
       <c r="G10" t="n">
-        <v>0</v>
+        <v>8.113133295381624</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>1.276246312356512e-06</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>11.24253477912758</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>-2.886833036039658e-07</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>-8.113133295381624</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.276246312356512e-06</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="Z10" t="n">
-        <v>0</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>-11.24253477912758</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>2.886833036039658e-07</v>
       </c>
       <c r="AE10" t="n">
-        <v>0</v>
+        <v>-317.6505077191828</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
+        <v>-0.000725679616803785</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>213.7549774489315</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>-1.330920974471073e-07</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>-493.6679683552808</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>-0.003335086766222121</v>
       </c>
       <c r="AK10" t="n">
-        <v>0</v>
+        <v>317.6505077191828</v>
       </c>
       <c r="AL10" t="n">
-        <v>0</v>
+        <v>0.000725679616803785</v>
       </c>
       <c r="AM10" t="n">
-        <v>0</v>
+        <v>-213.7549774489315</v>
       </c>
       <c r="AN10" t="n">
-        <v>0</v>
+        <v>1.330920974471073e-07</v>
       </c>
       <c r="AO10" t="n">
-        <v>0</v>
+        <v>-788.861896338309</v>
       </c>
       <c r="AP10" t="n">
-        <v>0</v>
+        <v>-0.00101899093460061</v>
       </c>
     </row>
     <row r="11">
@@ -3911,118 +3911,118 @@
         <v>6</v>
       </c>
       <c r="E11" t="n">
-        <v>0</v>
+        <v>317.6505077192171</v>
       </c>
       <c r="F11" t="n">
-        <v>0</v>
+        <v>67014.87504624833</v>
       </c>
       <c r="G11" t="n">
-        <v>0</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="H11" t="n">
-        <v>0</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="K11" t="n">
-        <v>0</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="L11" t="n">
-        <v>0</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="N11" t="n">
-        <v>-0</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>-8.113133295376661</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1.276246011702428e-06</v>
       </c>
       <c r="Y11" t="n">
-        <v>0</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="Z11" t="n">
-        <v>0</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>-11.2425347791201</v>
       </c>
       <c r="AB11" t="n">
-        <v>0</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="AC11" t="n">
-        <v>0</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="AD11" t="n">
-        <v>0</v>
+        <v>-2.886834930193329e-07</v>
       </c>
       <c r="AE11" t="n">
-        <v>0</v>
+        <v>-317.6505077192171</v>
       </c>
       <c r="AF11" t="n">
-        <v>0</v>
+        <v>0.0007256797704882252</v>
       </c>
       <c r="AG11" t="n">
-        <v>0</v>
+        <v>213.7549774487221</v>
       </c>
       <c r="AH11" t="n">
-        <v>0</v>
+        <v>1.330904625743146e-07</v>
       </c>
       <c r="AI11" t="n">
-        <v>0</v>
+        <v>-493.6679683547802</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>0.003335087144958782</v>
       </c>
       <c r="AK11" t="n">
-        <v>0</v>
+        <v>317.6505077192171</v>
       </c>
       <c r="AL11" t="n">
-        <v>0</v>
+        <v>-0.0007256797704882252</v>
       </c>
       <c r="AM11" t="n">
-        <v>0</v>
+        <v>-213.7549774487221</v>
       </c>
       <c r="AN11" t="n">
-        <v>0</v>
+        <v>-1.330904625743146e-07</v>
       </c>
       <c r="AO11" t="n">
-        <v>0</v>
+        <v>-788.8618963375543</v>
       </c>
       <c r="AP11" t="n">
-        <v>0</v>
+        <v>0.001018991477970577</v>
       </c>
     </row>
     <row r="12">
@@ -4039,118 +4039,118 @@
         <v>6</v>
       </c>
       <c r="E12" t="n">
-        <v>0</v>
+        <v>-317.6505077192179</v>
       </c>
       <c r="F12" t="n">
-        <v>0</v>
+        <v>-67014.8750462485</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="H12" t="n">
-        <v>0</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>-8.114175479580663</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>-1.27624601135778e-06</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>-11.24364880861739</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>2.886834933623841e-07</v>
       </c>
       <c r="AE12" t="n">
-        <v>0</v>
+        <v>317.6505077192182</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
+        <v>-0.0007256797706754747</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>286.2450225507185</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>-1.460844122613825e-07</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>-565.1279698860859</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>-0.003335087145519354</v>
       </c>
       <c r="AK12" t="n">
-        <v>0</v>
+        <v>-317.6505077192182</v>
       </c>
       <c r="AL12" t="n">
-        <v>0</v>
+        <v>0.0007256797706754747</v>
       </c>
       <c r="AM12" t="n">
-        <v>0</v>
+        <v>-136.2450225507185</v>
       </c>
       <c r="AN12" t="n">
-        <v>0</v>
+        <v>1.460844122613825e-07</v>
       </c>
       <c r="AO12" t="n">
-        <v>0</v>
+        <v>-702.342165418225</v>
       </c>
       <c r="AP12" t="n">
-        <v>0</v>
+        <v>-0.001018991478533501</v>
       </c>
     </row>
     <row r="13">
@@ -4167,118 +4167,118 @@
         <v>6</v>
       </c>
       <c r="E13" t="n">
-        <v>0</v>
+        <v>-317.6505077191833</v>
       </c>
       <c r="F13" t="n">
-        <v>0</v>
+        <v>-67014.87504624121</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="H13" t="n">
-        <v>-0</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="K13" t="n">
-        <v>0</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="Q13" t="n">
-        <v>-0</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>-8.114175479585626</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>1.276246312679776e-06</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>-11.24364880862486</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>-2.886833031477993e-07</v>
       </c>
       <c r="AE13" t="n">
-        <v>0</v>
+        <v>317.6505077191835</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
+        <v>0.0007256796166823266</v>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>286.245022550927</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.460827712407298e-07</v>
       </c>
       <c r="AI13" t="n">
-        <v>0</v>
+        <v>-565.127969886584</v>
       </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>0.003335086765759374</v>
       </c>
       <c r="AK13" t="n">
-        <v>0</v>
+        <v>-317.6505077191835</v>
       </c>
       <c r="AL13" t="n">
-        <v>0</v>
+        <v>-0.0007256796166823266</v>
       </c>
       <c r="AM13" t="n">
-        <v>0</v>
+        <v>-136.245022550927</v>
       </c>
       <c r="AN13" t="n">
-        <v>0</v>
+        <v>-1.460827712407298e-07</v>
       </c>
       <c r="AO13" t="n">
-        <v>0</v>
+        <v>-702.3421654189774</v>
       </c>
       <c r="AP13" t="n">
-        <v>0</v>
+        <v>0.001018990934334565</v>
       </c>
     </row>
     <row r="14">
@@ -4295,118 +4295,118 @@
         <v>6</v>
       </c>
       <c r="E14" t="n">
-        <v>0</v>
+        <v>87.79382485850731</v>
       </c>
       <c r="F14" t="n">
-        <v>0</v>
+        <v>18521.90397858804</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>11.24253477912758</v>
       </c>
       <c r="H14" t="n">
-        <v>0</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="I14" t="n">
-        <v>0</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>-2.886833036039658e-07</v>
       </c>
       <c r="K14" t="n">
-        <v>0</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="M14" t="n">
-        <v>0</v>
+        <v>12.7636275507655</v>
       </c>
       <c r="N14" t="n">
-        <v>0</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.041020896839185e-07</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>-11.24253477912758</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.886833036039658e-07</v>
       </c>
       <c r="Y14" t="n">
-        <v>0</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="Z14" t="n">
-        <v>0</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>-12.7636275507655</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>-1.041020896839185e-07</v>
       </c>
       <c r="AE14" t="n">
-        <v>0</v>
+        <v>-87.79382485850738</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
+        <v>0.000135553010461472</v>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>81.74248202001982</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>2.066456408766904e-09</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>-128.1207564938366</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>0.0006973202224174468</v>
       </c>
       <c r="AK14" t="n">
-        <v>0</v>
+        <v>87.79382485850738</v>
       </c>
       <c r="AL14" t="n">
-        <v>0</v>
+        <v>-0.000135553010461472</v>
       </c>
       <c r="AM14" t="n">
-        <v>0</v>
+        <v>-81.74248202001982</v>
       </c>
       <c r="AN14" t="n">
-        <v>0</v>
+        <v>-2.066456408766904e-09</v>
       </c>
       <c r="AO14" t="n">
-        <v>0</v>
+        <v>-362.3341356262787</v>
       </c>
       <c r="AP14" t="n">
-        <v>0</v>
+        <v>0.0001159978403513784</v>
       </c>
     </row>
     <row r="15">
@@ -4423,118 +4423,118 @@
         <v>6</v>
       </c>
       <c r="E15" t="n">
-        <v>0</v>
+        <v>87.79382485854211</v>
       </c>
       <c r="F15" t="n">
-        <v>0</v>
+        <v>18521.90397859538</v>
       </c>
       <c r="G15" t="n">
-        <v>0</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="H15" t="n">
-        <v>-0</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="J15" t="n">
-        <v>0</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="K15" t="n">
-        <v>0</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="L15" t="n">
-        <v>0</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="M15" t="n">
-        <v>0</v>
+        <v>12.76362755075735</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="P15" t="n">
-        <v>0</v>
+        <v>-1.041020131429611e-07</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="R15" t="n">
-        <v>0</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="S15" t="n">
-        <v>0</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="T15" t="n">
-        <v>0</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="U15" t="n">
-        <v>0</v>
+        <v>-11.2425347791201</v>
       </c>
       <c r="V15" t="n">
-        <v>0</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="W15" t="n">
-        <v>0</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
+        <v>-2.886834930193329e-07</v>
       </c>
       <c r="Y15" t="n">
-        <v>0</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="Z15" t="n">
-        <v>0</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="AA15" t="n">
-        <v>0</v>
+        <v>-12.76362755075735</v>
       </c>
       <c r="AB15" t="n">
-        <v>0</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="AC15" t="n">
-        <v>0</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="AD15" t="n">
-        <v>0</v>
+        <v>1.041020131429611e-07</v>
       </c>
       <c r="AE15" t="n">
-        <v>0</v>
+        <v>-87.79382485854194</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
+        <v>-0.0001355529532395382</v>
       </c>
       <c r="AG15" t="n">
-        <v>0</v>
+        <v>81.74248202002072</v>
       </c>
       <c r="AH15" t="n">
-        <v>0</v>
+        <v>-2.06706612937424e-09</v>
       </c>
       <c r="AI15" t="n">
-        <v>0</v>
+        <v>-128.1207564939566</v>
       </c>
       <c r="AJ15" t="n">
-        <v>0</v>
+        <v>-0.0006973201342787144</v>
       </c>
       <c r="AK15" t="n">
-        <v>0</v>
+        <v>87.79382485854194</v>
       </c>
       <c r="AL15" t="n">
-        <v>0</v>
+        <v>0.0001355529532395382</v>
       </c>
       <c r="AM15" t="n">
-        <v>0</v>
+        <v>-81.74248202002072</v>
       </c>
       <c r="AN15" t="n">
-        <v>0</v>
+        <v>2.06706612937424e-09</v>
       </c>
       <c r="AO15" t="n">
-        <v>0</v>
+        <v>-362.3341356261658</v>
       </c>
       <c r="AP15" t="n">
-        <v>0</v>
+        <v>-0.0001159975851585185</v>
       </c>
     </row>
     <row r="16">
@@ -4551,118 +4551,118 @@
         <v>6</v>
       </c>
       <c r="E16" t="n">
-        <v>0</v>
+        <v>-87.79382485854266</v>
       </c>
       <c r="F16" t="n">
-        <v>0</v>
+        <v>-18521.9039785955</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="I16" t="n">
-        <v>0</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="K16" t="n">
-        <v>0</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="M16" t="n">
-        <v>-0</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="N16" t="n">
-        <v>0</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="O16" t="n">
-        <v>0</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="Q16" t="n">
-        <v>-0</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="R16" t="n">
-        <v>-0</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="S16" t="n">
-        <v>0</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="T16" t="n">
-        <v>0</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="U16" t="n">
-        <v>0</v>
+        <v>-11.24364880861739</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>2.886834933623841e-07</v>
       </c>
       <c r="Y16" t="n">
-        <v>0</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="Z16" t="n">
-        <v>0</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="AA16" t="n">
-        <v>0</v>
+        <v>-12.76431736073221</v>
       </c>
       <c r="AB16" t="n">
-        <v>0</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="AC16" t="n">
-        <v>0</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="AD16" t="n">
-        <v>0</v>
+        <v>-1.041020126456332e-07</v>
       </c>
       <c r="AE16" t="n">
-        <v>0</v>
+        <v>87.79382485854239</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
+        <v>0.0001355529529342408</v>
       </c>
       <c r="AG16" t="n">
-        <v>0</v>
+        <v>168.2575179794908</v>
       </c>
       <c r="AH16" t="n">
-        <v>0</v>
+        <v>-2.424063477723948e-09</v>
       </c>
       <c r="AI16" t="n">
-        <v>0</v>
+        <v>-219.5286446350328</v>
       </c>
       <c r="AJ16" t="n">
-        <v>0</v>
+        <v>0.0006973201332486564</v>
       </c>
       <c r="AK16" t="n">
-        <v>0</v>
+        <v>-87.79382485854239</v>
       </c>
       <c r="AL16" t="n">
-        <v>0</v>
+        <v>-0.0001355529529342408</v>
       </c>
       <c r="AM16" t="n">
-        <v>0</v>
+        <v>-18.25751797949079</v>
       </c>
       <c r="AN16" t="n">
-        <v>0</v>
+        <v>2.424063477723948e-09</v>
       </c>
       <c r="AO16" t="n">
-        <v>0</v>
+        <v>-340.0164632419128</v>
       </c>
       <c r="AP16" t="n">
-        <v>0</v>
+        <v>0.0001159975843567848</v>
       </c>
     </row>
     <row r="17">
@@ -4679,118 +4679,118 @@
         <v>6</v>
       </c>
       <c r="E17" t="n">
-        <v>0</v>
+        <v>-87.79382485850675</v>
       </c>
       <c r="F17" t="n">
-        <v>0</v>
+        <v>-18521.90397858792</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="H17" t="n">
-        <v>0</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="I17" t="n">
-        <v>0</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="K17" t="n">
-        <v>-0</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="M17" t="n">
-        <v>-0</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="N17" t="n">
-        <v>0</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="P17" t="n">
-        <v>-0</v>
+        <v>-1.041020899760041e-07</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="R17" t="n">
-        <v>0</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="S17" t="n">
-        <v>0</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="T17" t="n">
-        <v>0</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="U17" t="n">
-        <v>0</v>
+        <v>-11.24364880862486</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-2.886833031477993e-07</v>
       </c>
       <c r="Y17" t="n">
-        <v>0</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="Z17" t="n">
-        <v>0</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="AA17" t="n">
-        <v>0</v>
+        <v>-12.76431736074036</v>
       </c>
       <c r="AB17" t="n">
-        <v>0</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="AC17" t="n">
-        <v>0</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="AD17" t="n">
-        <v>0</v>
+        <v>1.041020899760041e-07</v>
       </c>
       <c r="AE17" t="n">
-        <v>0</v>
+        <v>87.79382485850692</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
+        <v>-0.0001355530108317436</v>
       </c>
       <c r="AG17" t="n">
-        <v>0</v>
+        <v>168.2575179794911</v>
       </c>
       <c r="AH17" t="n">
-        <v>0</v>
+        <v>2.423457712286137e-09</v>
       </c>
       <c r="AI17" t="n">
-        <v>0</v>
+        <v>-219.528644634917</v>
       </c>
       <c r="AJ17" t="n">
-        <v>0</v>
+        <v>-0.000697320223406836</v>
       </c>
       <c r="AK17" t="n">
-        <v>0</v>
+        <v>-87.79382485850692</v>
       </c>
       <c r="AL17" t="n">
-        <v>0</v>
+        <v>0.0001355530108317436</v>
       </c>
       <c r="AM17" t="n">
-        <v>0</v>
+        <v>-18.2575179794911</v>
       </c>
       <c r="AN17" t="n">
-        <v>0</v>
+        <v>-2.423457712286137e-09</v>
       </c>
       <c r="AO17" t="n">
-        <v>0</v>
+        <v>-340.0164632420323</v>
       </c>
       <c r="AP17" t="n">
-        <v>0</v>
+        <v>-0.0001159978415836149</v>
       </c>
     </row>
     <row r="18">
@@ -4807,118 +4807,118 @@
         <v>8</v>
       </c>
       <c r="E18" t="n">
-        <v>0</v>
+        <v>-12.47723624466577</v>
       </c>
       <c r="F18" t="n">
-        <v>0</v>
+        <v>-2632.328321659445</v>
       </c>
       <c r="G18" t="n">
-        <v>0</v>
+        <v>3.595119805279563</v>
       </c>
       <c r="H18" t="n">
-        <v>0</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="I18" t="n">
-        <v>0</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="J18" t="n">
-        <v>0</v>
+        <v>-5.817587131184721e-06</v>
       </c>
       <c r="K18" t="n">
-        <v>0</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="L18" t="n">
-        <v>0</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="M18" t="n">
-        <v>0</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="N18" t="n">
-        <v>0</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="O18" t="n">
-        <v>0</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="R18" t="n">
-        <v>0</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="S18" t="n">
-        <v>0</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="T18" t="n">
-        <v>0</v>
+        <v>-3.595119805279563</v>
       </c>
       <c r="U18" t="n">
-        <v>0</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>5.817587131184721e-06</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="Y18" t="n">
-        <v>0</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="Z18" t="n">
-        <v>0</v>
+        <v>-3.595119805277692</v>
       </c>
       <c r="AA18" t="n">
-        <v>0</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="AB18" t="n">
-        <v>0</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="AC18" t="n">
-        <v>0</v>
+        <v>-5.817587439357226e-06</v>
       </c>
       <c r="AD18" t="n">
-        <v>0</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="AE18" t="n">
-        <v>0</v>
+        <v>12.47723624466577</v>
       </c>
       <c r="AF18" t="n">
-        <v>0</v>
+        <v>-3.865352482534945e-12</v>
       </c>
       <c r="AG18" t="n">
-        <v>0</v>
+        <v>1.28306291372754e-10</v>
       </c>
       <c r="AH18" t="n">
-        <v>0</v>
+        <v>7.23199278240827e-13</v>
       </c>
       <c r="AI18" t="n">
-        <v>0</v>
+        <v>0.006457521373425529</v>
       </c>
       <c r="AJ18" t="n">
-        <v>0</v>
+        <v>16.62376087106873</v>
       </c>
       <c r="AK18" t="n">
-        <v>0</v>
+        <v>-12.47723624466577</v>
       </c>
       <c r="AL18" t="n">
-        <v>0</v>
+        <v>3.865352482534945e-12</v>
       </c>
       <c r="AM18" t="n">
-        <v>0</v>
+        <v>-1.28306291372754e-10</v>
       </c>
       <c r="AN18" t="n">
-        <v>0</v>
+        <v>-7.23199278240827e-13</v>
       </c>
       <c r="AO18" t="n">
-        <v>0</v>
+        <v>-0.006457522399876302</v>
       </c>
       <c r="AP18" t="n">
-        <v>0</v>
+        <v>-16.62376087109965</v>
       </c>
     </row>
     <row r="19">
@@ -4935,118 +4935,118 @@
         <v>8</v>
       </c>
       <c r="E19" t="n">
-        <v>0</v>
+        <v>125.2334006770803</v>
       </c>
       <c r="F19" t="n">
-        <v>0</v>
+        <v>26420.5486660507</v>
       </c>
       <c r="G19" t="n">
-        <v>0</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="H19" t="n">
-        <v>0</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="I19" t="n">
-        <v>0</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="J19" t="n">
-        <v>0</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="K19" t="n">
-        <v>0</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="L19" t="n">
-        <v>0</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="M19" t="n">
-        <v>0</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="N19" t="n">
-        <v>0</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="O19" t="n">
-        <v>0</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="P19" t="n">
-        <v>0</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="R19" t="n">
-        <v>0</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="S19" t="n">
-        <v>0</v>
+        <v>3.595119805277692</v>
       </c>
       <c r="T19" t="n">
-        <v>0</v>
+        <v>-5.264656732975187e-05</v>
       </c>
       <c r="U19" t="n">
-        <v>0</v>
+        <v>0.007516730126563006</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>5.817587439357226e-06</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>0.5733905572095976</v>
       </c>
       <c r="X19" t="n">
-        <v>0</v>
+        <v>-0.01497636114489171</v>
       </c>
       <c r="Y19" t="n">
-        <v>0</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="Z19" t="n">
-        <v>0</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="AA19" t="n">
-        <v>0</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="AB19" t="n">
-        <v>0</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="AC19" t="n">
-        <v>0</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="AD19" t="n">
-        <v>0</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="AE19" t="n">
-        <v>0</v>
+        <v>-125.233400677098</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
+        <v>12.48925291831083</v>
       </c>
       <c r="AG19" t="n">
-        <v>0</v>
+        <v>-475.9154605522502</v>
       </c>
       <c r="AH19" t="n">
-        <v>0</v>
+        <v>2.48366232994117e-05</v>
       </c>
       <c r="AI19" t="n">
-        <v>0</v>
+        <v>1903.485520698533</v>
       </c>
       <c r="AJ19" t="n">
-        <v>0</v>
+        <v>16.66630415556484</v>
       </c>
       <c r="AK19" t="n">
-        <v>0</v>
+        <v>125.233400677098</v>
       </c>
       <c r="AL19" t="n">
-        <v>0</v>
+        <v>-12.48925291831083</v>
       </c>
       <c r="AM19" t="n">
-        <v>0</v>
+        <v>475.9154605522502</v>
       </c>
       <c r="AN19" t="n">
-        <v>0</v>
+        <v>-2.48366232994117e-05</v>
       </c>
       <c r="AO19" t="n">
-        <v>0</v>
+        <v>1903.838163719469</v>
       </c>
       <c r="AP19" t="n">
-        <v>0</v>
+        <v>83.24771919092179</v>
       </c>
     </row>
     <row r="20">
@@ -5063,118 +5063,118 @@
         <v>8</v>
       </c>
       <c r="E20" t="n">
-        <v>0</v>
+        <v>12.47723624466572</v>
       </c>
       <c r="F20" t="n">
-        <v>0</v>
+        <v>2632.328321659435</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="H20" t="n">
-        <v>0</v>
+        <v>5.264656733141418e-05</v>
       </c>
       <c r="I20" t="n">
-        <v>0</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="K20" t="n">
-        <v>0</v>
+        <v>0.5737082536248554</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="M20" t="n">
-        <v>0</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="N20" t="n">
-        <v>0</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="O20" t="n">
-        <v>0</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="R20" t="n">
-        <v>0</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="S20" t="n">
-        <v>0</v>
+        <v>-5.264656733141418e-05</v>
       </c>
       <c r="T20" t="n">
-        <v>0</v>
+        <v>3.596176627224334</v>
       </c>
       <c r="U20" t="n">
-        <v>0</v>
+        <v>-0.007516730126563017</v>
       </c>
       <c r="V20" t="n">
-        <v>0</v>
+        <v>-0.5737082536248554</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-5.817587439646455e-06</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>0.04500689564371815</v>
       </c>
       <c r="Y20" t="n">
-        <v>0</v>
+        <v>5.264656553496323e-05</v>
       </c>
       <c r="Z20" t="n">
-        <v>0</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="AA20" t="n">
-        <v>0</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="AB20" t="n">
-        <v>0</v>
+        <v>-0.5737082536251945</v>
       </c>
       <c r="AC20" t="n">
-        <v>0</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="AD20" t="n">
-        <v>0</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="AE20" t="n">
-        <v>0</v>
+        <v>-12.47723624466572</v>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
+        <v>-100.000000000004</v>
       </c>
       <c r="AG20" t="n">
-        <v>0</v>
+        <v>1.285480819013252e-10</v>
       </c>
       <c r="AH20" t="n">
-        <v>0</v>
+        <v>7.238654120556021e-13</v>
       </c>
       <c r="AI20" t="n">
-        <v>0</v>
+        <v>-0.006457522400840577</v>
       </c>
       <c r="AJ20" t="n">
-        <v>0</v>
+        <v>-83.37567916907628</v>
       </c>
       <c r="AK20" t="n">
-        <v>0</v>
+        <v>12.47723624466572</v>
       </c>
       <c r="AL20" t="n">
-        <v>0</v>
+        <v>-99.99999999999602</v>
       </c>
       <c r="AM20" t="n">
-        <v>0</v>
+        <v>-1.285480819013252e-10</v>
       </c>
       <c r="AN20" t="n">
-        <v>0</v>
+        <v>-7.238654120556021e-13</v>
       </c>
       <c r="AO20" t="n">
-        <v>0</v>
+        <v>0.006457521372455919</v>
       </c>
       <c r="AP20" t="n">
-        <v>0</v>
+        <v>83.37567916904467</v>
       </c>
     </row>
     <row r="21">
@@ -5191,118 +5191,118 @@
         <v>8</v>
       </c>
       <c r="E21" t="n">
-        <v>0</v>
+        <v>125.2334006771329</v>
       </c>
       <c r="F21" t="n">
-        <v>0</v>
+        <v>26420.5486660618</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>3.596176627226205</v>
       </c>
       <c r="H21" t="n">
-        <v>0</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="I21" t="n">
-        <v>0</v>
+        <v>-0.00751673012656329</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>5.817587130890855e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>0</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>-0.04500689564325982</v>
       </c>
       <c r="M21" t="n">
-        <v>0</v>
+        <v>3.595119805279563</v>
       </c>
       <c r="N21" t="n">
-        <v>0</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>0.007516730126563289</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>-5.817587131184721e-06</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.01497636114535011</v>
       </c>
       <c r="S21" t="n">
-        <v>0</v>
+        <v>-3.596176627226205</v>
       </c>
       <c r="T21" t="n">
-        <v>0</v>
+        <v>-5.264656553496323e-05</v>
       </c>
       <c r="U21" t="n">
-        <v>0</v>
+        <v>0.00751673012656329</v>
       </c>
       <c r="V21" t="n">
-        <v>0</v>
+        <v>-5.817587130890855e-06</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5737082536251945</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>0.04500689564325982</v>
       </c>
       <c r="Y21" t="n">
-        <v>0</v>
+        <v>-3.595119805279563</v>
       </c>
       <c r="Z21" t="n">
-        <v>0</v>
+        <v>5.264656553662592e-05</v>
       </c>
       <c r="AA21" t="n">
-        <v>0</v>
+        <v>-0.007516730126563289</v>
       </c>
       <c r="AB21" t="n">
-        <v>0</v>
+        <v>5.817587131184721e-06</v>
       </c>
       <c r="AC21" t="n">
-        <v>0</v>
+        <v>0.5733905572099365</v>
       </c>
       <c r="AD21" t="n">
-        <v>0</v>
+        <v>-0.01497636114535011</v>
       </c>
       <c r="AE21" t="n">
-        <v>0</v>
+        <v>-125.233400677098</v>
       </c>
       <c r="AF21" t="n">
-        <v>0</v>
+        <v>12.48925291830278</v>
       </c>
       <c r="AG21" t="n">
-        <v>0</v>
+        <v>-475.9154605525324</v>
       </c>
       <c r="AH21" t="n">
-        <v>0</v>
+        <v>-2.483662198250748e-05</v>
       </c>
       <c r="AI21" t="n">
-        <v>0</v>
+        <v>1903.838163720598</v>
       </c>
       <c r="AJ21" t="n">
-        <v>0</v>
+        <v>83.24771919088963</v>
       </c>
       <c r="AK21" t="n">
-        <v>0</v>
+        <v>125.233400677098</v>
       </c>
       <c r="AL21" t="n">
-        <v>0</v>
+        <v>-12.48925291830278</v>
       </c>
       <c r="AM21" t="n">
-        <v>0</v>
+        <v>475.9154605525324</v>
       </c>
       <c r="AN21" t="n">
-        <v>0</v>
+        <v>2.483662198250748e-05</v>
       </c>
       <c r="AO21" t="n">
-        <v>0</v>
+        <v>1903.485520699661</v>
       </c>
       <c r="AP21" t="n">
-        <v>0</v>
+        <v>16.6663041555326</v>
       </c>
     </row>
     <row r="22">
@@ -5319,118 +5319,118 @@
         <v>8</v>
       </c>
       <c r="E22" t="n">
-        <v>0</v>
+        <v>-12.5013115238314</v>
       </c>
       <c r="F22" t="n">
-        <v>0</v>
+        <v>-2637.407494479197</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>8.113133295381624</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1.276246312356512e-06</v>
       </c>
       <c r="K22" t="n">
-        <v>0</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="M22" t="n">
-        <v>0</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="N22" t="n">
-        <v>0</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="S22" t="n">
-        <v>0</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="T22" t="n">
-        <v>0</v>
+        <v>-8.113133295381624</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>-1.276246312356512e-06</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="Y22" t="n">
-        <v>0</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="Z22" t="n">
-        <v>0</v>
+        <v>-8.113133295376661</v>
       </c>
       <c r="AA22" t="n">
-        <v>0</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="AB22" t="n">
-        <v>0</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="AC22" t="n">
-        <v>0</v>
+        <v>1.276246011702428e-06</v>
       </c>
       <c r="AD22" t="n">
-        <v>0</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="AE22" t="n">
-        <v>0</v>
+        <v>12.5013115238314</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
+        <v>-2.592059900052845e-11</v>
       </c>
       <c r="AG22" t="n">
-        <v>0</v>
+        <v>1.251894328219844e-10</v>
       </c>
       <c r="AH22" t="n">
-        <v>0</v>
+        <v>7.758238496080594e-13</v>
       </c>
       <c r="AI22" t="n">
-        <v>0</v>
+        <v>-0.001416633740610715</v>
       </c>
       <c r="AJ22" t="n">
-        <v>0</v>
+        <v>16.65564080088552</v>
       </c>
       <c r="AK22" t="n">
-        <v>0</v>
+        <v>-12.5013115238314</v>
       </c>
       <c r="AL22" t="n">
-        <v>0</v>
+        <v>2.592059900052845e-11</v>
       </c>
       <c r="AM22" t="n">
-        <v>0</v>
+        <v>-1.251894328219844e-10</v>
       </c>
       <c r="AN22" t="n">
-        <v>0</v>
+        <v>-7.758238496080594e-13</v>
       </c>
       <c r="AO22" t="n">
-        <v>0</v>
+        <v>0.001416632739095252</v>
       </c>
       <c r="AP22" t="n">
-        <v>0</v>
+        <v>-16.65564080109243</v>
       </c>
     </row>
     <row r="23">
@@ -5447,118 +5447,118 @@
         <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>123.4988281741627</v>
       </c>
       <c r="F23" t="n">
-        <v>0</v>
+        <v>26054.60510003432</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="H23" t="n">
-        <v>0</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="I23" t="n">
-        <v>0</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="K23" t="n">
-        <v>0</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="M23" t="n">
-        <v>0</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="N23" t="n">
-        <v>0</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="P23" t="n">
-        <v>0</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="Q23" t="n">
-        <v>0</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="R23" t="n">
-        <v>0</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="S23" t="n">
-        <v>0</v>
+        <v>8.113133295376661</v>
       </c>
       <c r="T23" t="n">
-        <v>0</v>
+        <v>-5.274815211736379e-05</v>
       </c>
       <c r="U23" t="n">
-        <v>0</v>
+        <v>0.01202133708507298</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-1.276246011702428e-06</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.4768655535130946</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.01500508180210351</v>
       </c>
       <c r="Y23" t="n">
-        <v>0</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="Z23" t="n">
-        <v>0</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="AA23" t="n">
-        <v>0</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="AB23" t="n">
-        <v>0</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="AC23" t="n">
-        <v>0</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="AD23" t="n">
-        <v>0</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="AE23" t="n">
-        <v>0</v>
+        <v>-123.4988281741971</v>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
+        <v>12.49725030898538</v>
       </c>
       <c r="AG23" t="n">
-        <v>0</v>
+        <v>-394.0773917252354</v>
       </c>
       <c r="AH23" t="n">
-        <v>0</v>
+        <v>-5.448588741532367e-06</v>
       </c>
       <c r="AI23" t="n">
-        <v>0</v>
+        <v>1576.857887959055</v>
       </c>
       <c r="AJ23" t="n">
-        <v>0</v>
+        <v>16.65572241141295</v>
       </c>
       <c r="AK23" t="n">
-        <v>0</v>
+        <v>123.4988281741971</v>
       </c>
       <c r="AL23" t="n">
-        <v>0</v>
+        <v>-12.49725030898538</v>
       </c>
       <c r="AM23" t="n">
-        <v>0</v>
+        <v>394.0773917252354</v>
       </c>
       <c r="AN23" t="n">
-        <v>0</v>
+        <v>5.448588741532367e-06</v>
       </c>
       <c r="AO23" t="n">
-        <v>0</v>
+        <v>1575.761245842828</v>
       </c>
       <c r="AP23" t="n">
-        <v>0</v>
+        <v>83.32228006047011</v>
       </c>
     </row>
     <row r="24">
@@ -5575,118 +5575,118 @@
         <v>8</v>
       </c>
       <c r="E24" t="n">
-        <v>0</v>
+        <v>12.50131152383139</v>
       </c>
       <c r="F24" t="n">
-        <v>0</v>
+        <v>2637.407494479197</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="H24" t="n">
-        <v>0</v>
+        <v>5.274815212167277e-05</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="K24" t="n">
-        <v>0</v>
+        <v>0.4758775876426199</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="M24" t="n">
-        <v>0</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="N24" t="n">
-        <v>-0</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="O24" t="n">
-        <v>0</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="P24" t="n">
-        <v>0</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="Q24" t="n">
-        <v>0</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="R24" t="n">
-        <v>0</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="S24" t="n">
-        <v>0</v>
+        <v>-5.274815212167277e-05</v>
       </c>
       <c r="T24" t="n">
-        <v>0</v>
+        <v>8.114175479580663</v>
       </c>
       <c r="U24" t="n">
-        <v>0</v>
+        <v>-0.012021337085073</v>
       </c>
       <c r="V24" t="n">
-        <v>0</v>
+        <v>-0.4758775876426199</v>
       </c>
       <c r="W24" t="n">
-        <v>0</v>
+        <v>1.27624601135778e-06</v>
       </c>
       <c r="X24" t="n">
-        <v>0</v>
+        <v>0.04505488004389391</v>
       </c>
       <c r="Y24" t="n">
-        <v>0</v>
+        <v>5.27481476574951e-05</v>
       </c>
       <c r="Z24" t="n">
-        <v>0</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="AA24" t="n">
-        <v>0</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="AB24" t="n">
-        <v>0</v>
+        <v>-0.475877587642983</v>
       </c>
       <c r="AC24" t="n">
-        <v>0</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="AD24" t="n">
-        <v>0</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="AE24" t="n">
-        <v>0</v>
+        <v>-12.50131152383139</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
+        <v>-100.0000000000263</v>
       </c>
       <c r="AG24" t="n">
-        <v>0</v>
+        <v>1.254654333985444e-10</v>
       </c>
       <c r="AH24" t="n">
-        <v>0</v>
+        <v>7.751577157932843e-13</v>
       </c>
       <c r="AI24" t="n">
-        <v>0</v>
+        <v>0.001416632737978864</v>
       </c>
       <c r="AJ24" t="n">
-        <v>0</v>
+        <v>-83.32241648536987</v>
       </c>
       <c r="AK24" t="n">
-        <v>0</v>
+        <v>12.50131152383139</v>
       </c>
       <c r="AL24" t="n">
-        <v>0</v>
+        <v>-99.99999999997374</v>
       </c>
       <c r="AM24" t="n">
-        <v>0</v>
+        <v>-1.254654333985444e-10</v>
       </c>
       <c r="AN24" t="n">
-        <v>0</v>
+        <v>-7.751577157932843e-13</v>
       </c>
       <c r="AO24" t="n">
-        <v>0</v>
+        <v>-0.00141663374170233</v>
       </c>
       <c r="AP24" t="n">
-        <v>0</v>
+        <v>83.32241648516023</v>
       </c>
     </row>
     <row r="25">
@@ -5703,118 +5703,118 @@
         <v>8</v>
       </c>
       <c r="E25" t="n">
-        <v>0</v>
+        <v>123.4988281741627</v>
       </c>
       <c r="F25" t="n">
-        <v>0</v>
+        <v>26054.60510003432</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>8.114175479585626</v>
       </c>
       <c r="H25" t="n">
-        <v>-0</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-1.276246312679776e-06</v>
       </c>
       <c r="K25" t="n">
-        <v>0</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>-0.04505488004271615</v>
       </c>
       <c r="M25" t="n">
-        <v>0</v>
+        <v>8.113133295381624</v>
       </c>
       <c r="N25" t="n">
-        <v>0</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="O25" t="n">
-        <v>0</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="P25" t="n">
-        <v>0</v>
+        <v>1.276246312356512e-06</v>
       </c>
       <c r="Q25" t="n">
-        <v>0</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="R25" t="n">
-        <v>0</v>
+        <v>0.01500508180328185</v>
       </c>
       <c r="S25" t="n">
-        <v>0</v>
+        <v>-8.114175479585626</v>
       </c>
       <c r="T25" t="n">
-        <v>0</v>
+        <v>-5.27481476574951e-05</v>
       </c>
       <c r="U25" t="n">
-        <v>0</v>
+        <v>0.01202133708507339</v>
       </c>
       <c r="V25" t="n">
-        <v>0</v>
+        <v>1.276246312679776e-06</v>
       </c>
       <c r="W25" t="n">
-        <v>0</v>
+        <v>0.475877587642983</v>
       </c>
       <c r="X25" t="n">
-        <v>0</v>
+        <v>0.04505488004271615</v>
       </c>
       <c r="Y25" t="n">
-        <v>0</v>
+        <v>-8.113133295381624</v>
       </c>
       <c r="Z25" t="n">
-        <v>0</v>
+        <v>5.27481476618041e-05</v>
       </c>
       <c r="AA25" t="n">
-        <v>0</v>
+        <v>-0.01202133708507339</v>
       </c>
       <c r="AB25" t="n">
-        <v>0</v>
+        <v>-1.276246312356512e-06</v>
       </c>
       <c r="AC25" t="n">
-        <v>0</v>
+        <v>0.4768655535134581</v>
       </c>
       <c r="AD25" t="n">
-        <v>0</v>
+        <v>-0.01500508180328185</v>
       </c>
       <c r="AE25" t="n">
-        <v>0</v>
+        <v>-123.4988281741971</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
+        <v>12.49725030893287</v>
       </c>
       <c r="AG25" t="n">
-        <v>0</v>
+        <v>-394.0773917255378</v>
       </c>
       <c r="AH25" t="n">
-        <v>0</v>
+        <v>5.448590026519767e-06</v>
       </c>
       <c r="AI25" t="n">
-        <v>0</v>
+        <v>1575.761245844037</v>
       </c>
       <c r="AJ25" t="n">
-        <v>0</v>
+        <v>83.32228006026035</v>
       </c>
       <c r="AK25" t="n">
-        <v>0</v>
+        <v>123.4988281741971</v>
       </c>
       <c r="AL25" t="n">
-        <v>0</v>
+        <v>-12.49725030893287</v>
       </c>
       <c r="AM25" t="n">
-        <v>0</v>
+        <v>394.0773917255378</v>
       </c>
       <c r="AN25" t="n">
-        <v>0</v>
+        <v>-5.448590026519767e-06</v>
       </c>
       <c r="AO25" t="n">
-        <v>0</v>
+        <v>1576.857887960265</v>
       </c>
       <c r="AP25" t="n">
-        <v>0</v>
+        <v>16.65572241120256</v>
       </c>
     </row>
     <row r="26">
@@ -5831,118 +5831,118 @@
         <v>8</v>
       </c>
       <c r="E26" t="n">
-        <v>0</v>
+        <v>-12.49639529366899</v>
       </c>
       <c r="F26" t="n">
-        <v>0</v>
+        <v>-2636.370315120039</v>
       </c>
       <c r="G26" t="n">
-        <v>0</v>
+        <v>11.24253477912758</v>
       </c>
       <c r="H26" t="n">
-        <v>0</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="J26" t="n">
-        <v>0</v>
+        <v>-2.886833036039658e-07</v>
       </c>
       <c r="K26" t="n">
-        <v>0</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="L26" t="n">
-        <v>0</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="M26" t="n">
-        <v>0</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="N26" t="n">
-        <v>-0</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="P26" t="n">
-        <v>0</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="Q26" t="n">
-        <v>0</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="R26" t="n">
-        <v>0</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="S26" t="n">
-        <v>0</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="T26" t="n">
-        <v>0</v>
+        <v>-11.24253477912758</v>
       </c>
       <c r="U26" t="n">
-        <v>0</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="V26" t="n">
-        <v>0</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="W26" t="n">
-        <v>0</v>
+        <v>2.886833036039658e-07</v>
       </c>
       <c r="X26" t="n">
-        <v>0</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="Y26" t="n">
-        <v>0</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="Z26" t="n">
-        <v>0</v>
+        <v>-11.2425347791201</v>
       </c>
       <c r="AA26" t="n">
-        <v>0</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="AB26" t="n">
-        <v>0</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="AC26" t="n">
-        <v>0</v>
+        <v>-2.886834930193329e-07</v>
       </c>
       <c r="AD26" t="n">
-        <v>0</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="AE26" t="n">
-        <v>0</v>
+        <v>12.49639529366899</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
+        <v>-4.843059286940843e-11</v>
       </c>
       <c r="AG26" t="n">
-        <v>0</v>
+        <v>7.886364625849396e-11</v>
       </c>
       <c r="AH26" t="n">
-        <v>0</v>
+        <v>4.087841176669826e-13</v>
       </c>
       <c r="AI26" t="n">
-        <v>0</v>
+        <v>0.0003204382566711034</v>
       </c>
       <c r="AJ26" t="n">
-        <v>0</v>
+        <v>16.65569270639389</v>
       </c>
       <c r="AK26" t="n">
-        <v>0</v>
+        <v>-12.49639529366899</v>
       </c>
       <c r="AL26" t="n">
-        <v>0</v>
+        <v>4.843059286940843e-11</v>
       </c>
       <c r="AM26" t="n">
-        <v>0</v>
+        <v>-7.886364625849396e-11</v>
       </c>
       <c r="AN26" t="n">
-        <v>0</v>
+        <v>-4.087841176669826e-13</v>
       </c>
       <c r="AO26" t="n">
-        <v>0</v>
+        <v>-0.0003204388875802733</v>
       </c>
       <c r="AP26" t="n">
-        <v>0</v>
+        <v>-16.65569270678225</v>
       </c>
     </row>
     <row r="27">
@@ -5959,118 +5959,118 @@
         <v>8</v>
       </c>
       <c r="E27" t="n">
-        <v>0</v>
+        <v>132.0124954287865</v>
       </c>
       <c r="F27" t="n">
-        <v>0</v>
+        <v>27850.73743223343</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="H27" t="n">
-        <v>-0</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="I27" t="n">
-        <v>0</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="K27" t="n">
-        <v>0</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="M27" t="n">
-        <v>0</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="O27" t="n">
-        <v>0</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="P27" t="n">
-        <v>0</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="Q27" t="n">
-        <v>0</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="R27" t="n">
-        <v>0</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="S27" t="n">
-        <v>0</v>
+        <v>11.2425347791201</v>
       </c>
       <c r="T27" t="n">
-        <v>0</v>
+        <v>-5.272740957680732e-05</v>
       </c>
       <c r="U27" t="n">
-        <v>0</v>
+        <v>0.01403178333646043</v>
       </c>
       <c r="V27" t="n">
-        <v>0</v>
+        <v>2.886834930193329e-07</v>
       </c>
       <c r="W27" t="n">
-        <v>0</v>
+        <v>0.2774101967679769</v>
       </c>
       <c r="X27" t="n">
-        <v>0</v>
+        <v>-0.01500512856361739</v>
       </c>
       <c r="Y27" t="n">
-        <v>0</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="Z27" t="n">
-        <v>0</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="AA27" t="n">
-        <v>0</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="AB27" t="n">
-        <v>0</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="AC27" t="n">
-        <v>0</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="AD27" t="n">
-        <v>0</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="AE27" t="n">
-        <v>0</v>
+        <v>-132.0124954287894</v>
       </c>
       <c r="AF27" t="n">
-        <v>0</v>
+        <v>12.49725652639148</v>
       </c>
       <c r="AG27" t="n">
-        <v>0</v>
+        <v>-229.8566828605958</v>
       </c>
       <c r="AH27" t="n">
-        <v>0</v>
+        <v>1.232456451699434e-06</v>
       </c>
       <c r="AI27" t="n">
-        <v>0</v>
+        <v>916.9826528315087</v>
       </c>
       <c r="AJ27" t="n">
-        <v>0</v>
+        <v>16.65569284193676</v>
       </c>
       <c r="AK27" t="n">
-        <v>0</v>
+        <v>132.0124954287894</v>
       </c>
       <c r="AL27" t="n">
-        <v>0</v>
+        <v>-12.49725652639148</v>
       </c>
       <c r="AM27" t="n">
-        <v>0</v>
+        <v>229.8566828605958</v>
       </c>
       <c r="AN27" t="n">
-        <v>0</v>
+        <v>-1.232456451699434e-06</v>
       </c>
       <c r="AO27" t="n">
-        <v>0</v>
+        <v>921.8708100532576</v>
       </c>
       <c r="AP27" t="n">
-        <v>0</v>
+        <v>83.32235936919508</v>
       </c>
     </row>
     <row r="28">
@@ -6087,118 +6087,118 @@
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>0</v>
+        <v>12.49639529366798</v>
       </c>
       <c r="F28" t="n">
-        <v>0</v>
+        <v>2636.370315119826</v>
       </c>
       <c r="G28" t="n">
-        <v>0</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="H28" t="n">
-        <v>0</v>
+        <v>5.272740958393851e-05</v>
       </c>
       <c r="I28" t="n">
-        <v>0</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="J28" t="n">
-        <v>0</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="K28" t="n">
-        <v>0</v>
+        <v>0.2818139420127958</v>
       </c>
       <c r="L28" t="n">
-        <v>0</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="M28" t="n">
-        <v>0</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="N28" t="n">
-        <v>0</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="O28" t="n">
-        <v>0</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="P28" t="n">
-        <v>0</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="Q28" t="n">
-        <v>-0</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="R28" t="n">
-        <v>0</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="S28" t="n">
-        <v>0</v>
+        <v>-5.272740958393851e-05</v>
       </c>
       <c r="T28" t="n">
-        <v>0</v>
+        <v>11.24364880861739</v>
       </c>
       <c r="U28" t="n">
-        <v>0</v>
+        <v>-0.01403178333646046</v>
       </c>
       <c r="V28" t="n">
-        <v>0</v>
+        <v>-0.2818139420127958</v>
       </c>
       <c r="W28" t="n">
-        <v>0</v>
+        <v>-2.886834933623841e-07</v>
       </c>
       <c r="X28" t="n">
-        <v>0</v>
+        <v>0.04505493137084957</v>
       </c>
       <c r="Y28" t="n">
-        <v>0</v>
+        <v>5.272740302085454e-05</v>
       </c>
       <c r="Z28" t="n">
-        <v>0</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="AA28" t="n">
-        <v>0</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="AB28" t="n">
-        <v>0</v>
+        <v>-0.2818139420129872</v>
       </c>
       <c r="AC28" t="n">
-        <v>0</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="AD28" t="n">
-        <v>0</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="AE28" t="n">
-        <v>0</v>
+        <v>-12.49639529366798</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
+        <v>-100.0000000000475</v>
       </c>
       <c r="AG28" t="n">
-        <v>0</v>
+        <v>7.919405605740729e-11</v>
       </c>
       <c r="AH28" t="n">
-        <v>0</v>
+        <v>4.084510507595951e-13</v>
       </c>
       <c r="AI28" t="n">
-        <v>0</v>
+        <v>-0.0003204388888398558</v>
       </c>
       <c r="AJ28" t="n">
-        <v>0</v>
+        <v>-83.32235951285415</v>
       </c>
       <c r="AK28" t="n">
-        <v>0</v>
+        <v>12.49639529366798</v>
       </c>
       <c r="AL28" t="n">
-        <v>0</v>
+        <v>-99.99999999995248</v>
       </c>
       <c r="AM28" t="n">
-        <v>0</v>
+        <v>-7.919405605740729e-11</v>
       </c>
       <c r="AN28" t="n">
-        <v>0</v>
+        <v>-4.084510507595951e-13</v>
       </c>
       <c r="AO28" t="n">
-        <v>0</v>
+        <v>0.0003204382552865191</v>
       </c>
       <c r="AP28" t="n">
-        <v>0</v>
+        <v>83.32235951247489</v>
       </c>
     </row>
     <row r="29">
@@ -6215,118 +6215,118 @@
         <v>8</v>
       </c>
       <c r="E29" t="n">
-        <v>0</v>
+        <v>132.0124954283655</v>
       </c>
       <c r="F29" t="n">
-        <v>0</v>
+        <v>27850.73743214461</v>
       </c>
       <c r="G29" t="n">
-        <v>0</v>
+        <v>11.24364880862486</v>
       </c>
       <c r="H29" t="n">
-        <v>0</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>-0.01403178333646063</v>
       </c>
       <c r="J29" t="n">
-        <v>0</v>
+        <v>2.886833031477993e-07</v>
       </c>
       <c r="K29" t="n">
-        <v>-0</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="L29" t="n">
-        <v>0</v>
+        <v>-0.04505493136909523</v>
       </c>
       <c r="M29" t="n">
-        <v>0</v>
+        <v>11.24253477912758</v>
       </c>
       <c r="N29" t="n">
-        <v>0</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="O29" t="n">
-        <v>0</v>
+        <v>0.01403178333646062</v>
       </c>
       <c r="P29" t="n">
-        <v>0</v>
+        <v>-2.886833036039658e-07</v>
       </c>
       <c r="Q29" t="n">
-        <v>0</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="R29" t="n">
-        <v>0</v>
+        <v>0.01500512856537014</v>
       </c>
       <c r="S29" t="n">
-        <v>0</v>
+        <v>-11.24364880862486</v>
       </c>
       <c r="T29" t="n">
-        <v>0</v>
+        <v>-5.272740302085454e-05</v>
       </c>
       <c r="U29" t="n">
-        <v>0</v>
+        <v>0.01403178333646063</v>
       </c>
       <c r="V29" t="n">
-        <v>0</v>
+        <v>-2.886833031477993e-07</v>
       </c>
       <c r="W29" t="n">
-        <v>0</v>
+        <v>0.2818139420129872</v>
       </c>
       <c r="X29" t="n">
-        <v>0</v>
+        <v>0.04505493136909523</v>
       </c>
       <c r="Y29" t="n">
-        <v>0</v>
+        <v>-11.24253477912758</v>
       </c>
       <c r="Z29" t="n">
-        <v>0</v>
+        <v>5.272740302799424e-05</v>
       </c>
       <c r="AA29" t="n">
-        <v>0</v>
+        <v>-0.01403178333646062</v>
       </c>
       <c r="AB29" t="n">
-        <v>0</v>
+        <v>2.886833036039658e-07</v>
       </c>
       <c r="AC29" t="n">
-        <v>0</v>
+        <v>0.2774101967681684</v>
       </c>
       <c r="AD29" t="n">
-        <v>0</v>
+        <v>-0.01500512856537014</v>
       </c>
       <c r="AE29" t="n">
-        <v>0</v>
+        <v>-132.0124954283237</v>
       </c>
       <c r="AF29" t="n">
-        <v>0</v>
+        <v>12.49725652629611</v>
       </c>
       <c r="AG29" t="n">
-        <v>0</v>
+        <v>-229.8566828607552</v>
       </c>
       <c r="AH29" t="n">
-        <v>0</v>
+        <v>-1.232455641335499e-06</v>
       </c>
       <c r="AI29" t="n">
-        <v>0</v>
+        <v>921.870810053895</v>
       </c>
       <c r="AJ29" t="n">
-        <v>0</v>
+        <v>83.32235936881273</v>
       </c>
       <c r="AK29" t="n">
-        <v>0</v>
+        <v>132.0124954283237</v>
       </c>
       <c r="AL29" t="n">
-        <v>0</v>
+        <v>-12.49725652629611</v>
       </c>
       <c r="AM29" t="n">
-        <v>0</v>
+        <v>229.8566828607552</v>
       </c>
       <c r="AN29" t="n">
-        <v>0</v>
+        <v>1.232455641335499e-06</v>
       </c>
       <c r="AO29" t="n">
-        <v>0</v>
+        <v>916.9826528321462</v>
       </c>
       <c r="AP29" t="n">
-        <v>0</v>
+        <v>16.65569284155616</v>
       </c>
     </row>
     <row r="30">
@@ -6343,118 +6343,118 @@
         <v>8</v>
       </c>
       <c r="E30" t="n">
-        <v>0</v>
+        <v>-12.49739186091401</v>
       </c>
       <c r="F30" t="n">
-        <v>0</v>
+        <v>-2636.580561374263</v>
       </c>
       <c r="G30" t="n">
-        <v>0</v>
+        <v>12.7636275507655</v>
       </c>
       <c r="H30" t="n">
-        <v>0</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="I30" t="n">
-        <v>0</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="J30" t="n">
-        <v>0</v>
+        <v>1.041020896839185e-07</v>
       </c>
       <c r="K30" t="n">
-        <v>0</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="L30" t="n">
-        <v>0</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="M30" t="n">
-        <v>0</v>
+        <v>12.76362755075735</v>
       </c>
       <c r="N30" t="n">
-        <v>0</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="O30" t="n">
-        <v>0</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="P30" t="n">
-        <v>0</v>
+        <v>-1.041020131429611e-07</v>
       </c>
       <c r="Q30" t="n">
-        <v>0</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="R30" t="n">
-        <v>0</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="S30" t="n">
-        <v>0</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="T30" t="n">
-        <v>0</v>
+        <v>-12.7636275507655</v>
       </c>
       <c r="U30" t="n">
-        <v>0</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="V30" t="n">
-        <v>0</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="W30" t="n">
-        <v>0</v>
+        <v>-1.041020896839185e-07</v>
       </c>
       <c r="X30" t="n">
-        <v>0</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="Y30" t="n">
-        <v>0</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="Z30" t="n">
-        <v>0</v>
+        <v>-12.76362755075735</v>
       </c>
       <c r="AA30" t="n">
-        <v>0</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="AB30" t="n">
-        <v>0</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="AC30" t="n">
-        <v>0</v>
+        <v>1.041020131429611e-07</v>
       </c>
       <c r="AD30" t="n">
-        <v>0</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="AE30" t="n">
-        <v>0</v>
+        <v>12.49739186091401</v>
       </c>
       <c r="AF30" t="n">
-        <v>0</v>
+        <v>-2.91038304567337e-11</v>
       </c>
       <c r="AG30" t="n">
-        <v>0</v>
+        <v>3.185670624457392e-11</v>
       </c>
       <c r="AH30" t="n">
-        <v>0</v>
+        <v>7.083222897108499e-14</v>
       </c>
       <c r="AI30" t="n">
-        <v>0</v>
+        <v>-0.000115553404494969</v>
       </c>
       <c r="AJ30" t="n">
-        <v>0</v>
+        <v>16.65569190043516</v>
       </c>
       <c r="AK30" t="n">
-        <v>0</v>
+        <v>-12.49739186091401</v>
       </c>
       <c r="AL30" t="n">
-        <v>0</v>
+        <v>2.91038304567337e-11</v>
       </c>
       <c r="AM30" t="n">
-        <v>0</v>
+        <v>-3.185670624457392e-11</v>
       </c>
       <c r="AN30" t="n">
-        <v>0</v>
+        <v>-7.083222897108499e-14</v>
       </c>
       <c r="AO30" t="n">
-        <v>0</v>
+        <v>0.0001155531496422071</v>
       </c>
       <c r="AP30" t="n">
-        <v>0</v>
+        <v>-16.65569190066799</v>
       </c>
     </row>
     <row r="31">
@@ -6471,118 +6471,118 @@
         <v>8</v>
       </c>
       <c r="E31" t="n">
-        <v>0</v>
+        <v>81.74248202006939</v>
       </c>
       <c r="F31" t="n">
-        <v>0</v>
+        <v>17245.24937132265</v>
       </c>
       <c r="G31" t="n">
-        <v>0</v>
+        <v>12.76362755075735</v>
       </c>
       <c r="H31" t="n">
-        <v>0</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="I31" t="n">
-        <v>0</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="J31" t="n">
-        <v>0</v>
+        <v>-1.041020131429611e-07</v>
       </c>
       <c r="K31" t="n">
-        <v>0</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="L31" t="n">
-        <v>0</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="M31" t="n">
-        <v>-0</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="O31" t="n">
-        <v>0</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="P31" t="n">
-        <v>0</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="Q31" t="n">
-        <v>-0</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="R31" t="n">
-        <v>-0</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="S31" t="n">
-        <v>0</v>
+        <v>12.76362755075735</v>
       </c>
       <c r="T31" t="n">
-        <v>0</v>
+        <v>-5.273161501681668e-05</v>
       </c>
       <c r="U31" t="n">
-        <v>0</v>
+        <v>0.01458744045581829</v>
       </c>
       <c r="V31" t="n">
-        <v>0</v>
+        <v>-1.041020131429611e-07</v>
       </c>
       <c r="W31" t="n">
-        <v>0</v>
+        <v>0.1191579135705384</v>
       </c>
       <c r="X31" t="n">
-        <v>0</v>
+        <v>-0.01500512783735091</v>
       </c>
       <c r="Y31" t="n">
-        <v>0</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="Z31" t="n">
-        <v>0</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="AA31" t="n">
-        <v>0</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="AB31" t="n">
-        <v>0</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="AC31" t="n">
-        <v>0</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="AD31" t="n">
-        <v>0</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="AE31" t="n">
-        <v>0</v>
+        <v>-81.74248202005401</v>
       </c>
       <c r="AF31" t="n">
-        <v>0</v>
+        <v>12.49725630796159</v>
       </c>
       <c r="AG31" t="n">
-        <v>0</v>
+        <v>-87.79382485851036</v>
       </c>
       <c r="AH31" t="n">
-        <v>0</v>
+        <v>-4.444355165871917e-07</v>
       </c>
       <c r="AI31" t="n">
-        <v>0</v>
+        <v>362.3341356261689</v>
       </c>
       <c r="AJ31" t="n">
-        <v>0</v>
+        <v>16.65569189860274</v>
       </c>
       <c r="AK31" t="n">
-        <v>0</v>
+        <v>81.74248202005401</v>
       </c>
       <c r="AL31" t="n">
-        <v>0</v>
+        <v>-12.49725630796159</v>
       </c>
       <c r="AM31" t="n">
-        <v>0</v>
+        <v>87.79382485851036</v>
       </c>
       <c r="AN31" t="n">
-        <v>0</v>
+        <v>4.444355165871917e-07</v>
       </c>
       <c r="AO31" t="n">
-        <v>0</v>
+        <v>340.0164632419138</v>
       </c>
       <c r="AP31" t="n">
-        <v>0</v>
+        <v>83.32235856509004</v>
       </c>
     </row>
     <row r="32">
@@ -6599,118 +6599,118 @@
         <v>8</v>
       </c>
       <c r="E32" t="n">
-        <v>0</v>
+        <v>12.49739186091453</v>
       </c>
       <c r="F32" t="n">
-        <v>0</v>
+        <v>2636.580561374374</v>
       </c>
       <c r="G32" t="n">
-        <v>-0</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="H32" t="n">
-        <v>0</v>
+        <v>5.273161502770671e-05</v>
       </c>
       <c r="I32" t="n">
-        <v>0</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="J32" t="n">
-        <v>0</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="K32" t="n">
-        <v>-0</v>
+        <v>0.09905190241355175</v>
       </c>
       <c r="L32" t="n">
-        <v>-0</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="M32" t="n">
-        <v>-0</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="O32" t="n">
-        <v>0</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="P32" t="n">
-        <v>-0</v>
+        <v>-1.041020899760041e-07</v>
       </c>
       <c r="Q32" t="n">
-        <v>0</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="R32" t="n">
-        <v>0</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="S32" t="n">
-        <v>0</v>
+        <v>-5.273161502770671e-05</v>
       </c>
       <c r="T32" t="n">
-        <v>0</v>
+        <v>12.76431736073221</v>
       </c>
       <c r="U32" t="n">
-        <v>0</v>
+        <v>-0.01458744045581832</v>
       </c>
       <c r="V32" t="n">
-        <v>0</v>
+        <v>-0.09905190241355175</v>
       </c>
       <c r="W32" t="n">
-        <v>0</v>
+        <v>1.041020126456332e-07</v>
       </c>
       <c r="X32" t="n">
-        <v>0</v>
+        <v>0.04505493222254756</v>
       </c>
       <c r="Y32" t="n">
-        <v>0</v>
+        <v>5.273160742726827e-05</v>
       </c>
       <c r="Z32" t="n">
-        <v>0</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="AA32" t="n">
-        <v>0</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="AB32" t="n">
-        <v>0</v>
+        <v>-0.09905190241358573</v>
       </c>
       <c r="AC32" t="n">
-        <v>0</v>
+        <v>-1.041020899760041e-07</v>
       </c>
       <c r="AD32" t="n">
-        <v>0</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="AE32" t="n">
-        <v>0</v>
+        <v>-12.49739186091453</v>
       </c>
       <c r="AF32" t="n">
-        <v>0</v>
+        <v>-100.0000000000293</v>
       </c>
       <c r="AG32" t="n">
-        <v>0</v>
+        <v>3.218251569913049e-11</v>
       </c>
       <c r="AH32" t="n">
-        <v>0</v>
+        <v>7.255307465925398e-14</v>
       </c>
       <c r="AI32" t="n">
-        <v>0</v>
+        <v>0.0001155531482243991</v>
       </c>
       <c r="AJ32" t="n">
-        <v>0</v>
+        <v>-83.32235856751535</v>
       </c>
       <c r="AK32" t="n">
-        <v>0</v>
+        <v>12.49739186091453</v>
       </c>
       <c r="AL32" t="n">
-        <v>0</v>
+        <v>-99.99999999997067</v>
       </c>
       <c r="AM32" t="n">
-        <v>0</v>
+        <v>-3.218251569913049e-11</v>
       </c>
       <c r="AN32" t="n">
-        <v>0</v>
+        <v>-7.255307465925398e-14</v>
       </c>
       <c r="AO32" t="n">
-        <v>0</v>
+        <v>-0.0001155534056854128</v>
       </c>
       <c r="AP32" t="n">
-        <v>0</v>
+        <v>83.32235856727888</v>
       </c>
     </row>
     <row r="33">
@@ -6727,118 +6727,118 @@
         <v>8</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>81.74248202070089</v>
       </c>
       <c r="F33" t="n">
-        <v>0</v>
+        <v>17245.24937145588</v>
       </c>
       <c r="G33" t="n">
-        <v>-0</v>
+        <v>12.76431736074036</v>
       </c>
       <c r="H33" t="n">
-        <v>0</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="I33" t="n">
-        <v>0</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="J33" t="n">
-        <v>-0</v>
+        <v>-1.041020899760041e-07</v>
       </c>
       <c r="K33" t="n">
-        <v>0</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="L33" t="n">
-        <v>0</v>
+        <v>-0.04505493222058038</v>
       </c>
       <c r="M33" t="n">
-        <v>0</v>
+        <v>12.7636275507655</v>
       </c>
       <c r="N33" t="n">
-        <v>0</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="O33" t="n">
-        <v>0</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="P33" t="n">
-        <v>0</v>
+        <v>1.041020896839185e-07</v>
       </c>
       <c r="Q33" t="n">
-        <v>0</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="R33" t="n">
-        <v>0</v>
+        <v>0.01500512783931789</v>
       </c>
       <c r="S33" t="n">
-        <v>0</v>
+        <v>-12.76431736074036</v>
       </c>
       <c r="T33" t="n">
-        <v>0</v>
+        <v>-5.273160742726827e-05</v>
       </c>
       <c r="U33" t="n">
-        <v>0</v>
+        <v>0.01458744045581826</v>
       </c>
       <c r="V33" t="n">
-        <v>0</v>
+        <v>1.041020899760041e-07</v>
       </c>
       <c r="W33" t="n">
-        <v>0</v>
+        <v>0.09905190241358573</v>
       </c>
       <c r="X33" t="n">
-        <v>0</v>
+        <v>0.04505493222058038</v>
       </c>
       <c r="Y33" t="n">
-        <v>0</v>
+        <v>-12.7636275507655</v>
       </c>
       <c r="Z33" t="n">
-        <v>0</v>
+        <v>5.273160743815383e-05</v>
       </c>
       <c r="AA33" t="n">
-        <v>0</v>
+        <v>-0.01458744045581826</v>
       </c>
       <c r="AB33" t="n">
-        <v>0</v>
+        <v>-1.041020896839185e-07</v>
       </c>
       <c r="AC33" t="n">
-        <v>0</v>
+        <v>0.1191579135705716</v>
       </c>
       <c r="AD33" t="n">
-        <v>0</v>
+        <v>-0.01500512783931789</v>
       </c>
       <c r="AE33" t="n">
-        <v>0</v>
+        <v>-81.7424820207525</v>
       </c>
       <c r="AF33" t="n">
-        <v>0</v>
+        <v>12.49725630790358</v>
       </c>
       <c r="AG33" t="n">
-        <v>0</v>
+        <v>-87.79382485853831</v>
       </c>
       <c r="AH33" t="n">
-        <v>0</v>
+        <v>4.444358450432963e-07</v>
       </c>
       <c r="AI33" t="n">
-        <v>0</v>
+        <v>340.0164632420261</v>
       </c>
       <c r="AJ33" t="n">
-        <v>0</v>
+        <v>83.32235856485785</v>
       </c>
       <c r="AK33" t="n">
-        <v>0</v>
+        <v>81.7424820207525</v>
       </c>
       <c r="AL33" t="n">
-        <v>0</v>
+        <v>-12.49725630790358</v>
       </c>
       <c r="AM33" t="n">
-        <v>0</v>
+        <v>87.79382485853831</v>
       </c>
       <c r="AN33" t="n">
-        <v>0</v>
+        <v>-4.444358450432963e-07</v>
       </c>
       <c r="AO33" t="n">
-        <v>0</v>
+        <v>362.3341356262804</v>
       </c>
       <c r="AP33" t="n">
-        <v>0</v>
+        <v>16.65569189837078</v>
       </c>
     </row>
   </sheetData>

--- a/examples/validation_results/validation_frame_member_loads.xlsx
+++ b/examples/validation_results/validation_frame_member_loads.xlsx
@@ -10,8 +10,8 @@
     <sheet name="Node Displacements" sheetId="1" state="visible" r:id="rId1"/>
     <sheet name="Maximum Displacement Summary" sheetId="2" state="visible" r:id="rId2"/>
     <sheet name="Reaction Forces" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Member Summary" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Member Full Results" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Frame Member Summary" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Frame Member Full Results" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1345,32 +1345,32 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Fx ()</t>
+          <t>Fx (KN)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>Fy ()</t>
+          <t>Fy (KN)</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>Fz ()</t>
+          <t>Fz (KN)</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>Mx (·)</t>
+          <t>Mx (KN*M)</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>My (·)</t>
+          <t>My (KN*M)</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Mz (·)</t>
+          <t>Mz (KN*M)</t>
         </is>
       </c>
     </row>
@@ -1477,7 +1477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I33"/>
+  <dimension ref="A1:U33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1518,12 +1518,72 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>N_tension (+) (KN)</t>
+          <t>N (KN)</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
           <t>sigma (KN/M^2)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_i (KN)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_i (KN)</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_i (KN)</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_i (KN*M)</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>My_i (KN*M)</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_i (KN*M)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Fx_j (KN)</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Fy_j (KN)</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>Fz_j (KN)</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>Mx_j (KN*M)</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>My_j (KN*M)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>Mz_j (KN*M)</t>
         </is>
       </c>
     </row>
@@ -1557,6 +1617,42 @@
       <c r="I2" t="n">
         <v>250557.670885443</v>
       </c>
+      <c r="J2" t="n">
+        <v>-1187.643359997</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.008681138355291034</v>
+      </c>
+      <c r="L2" t="n">
+        <v>462.4872063002725</v>
+      </c>
+      <c r="M2" t="n">
+        <v>-0.04262502787522724</v>
+      </c>
+      <c r="N2" t="n">
+        <v>-1811.770631236171</v>
+      </c>
+      <c r="O2" t="n">
+        <v>-0.03034842954294979</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1187.643359997</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.008681138355291034</v>
+      </c>
+      <c r="R2" t="n">
+        <v>-462.4872063002725</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.04262502787522724</v>
+      </c>
+      <c r="T2" t="n">
+        <v>-963.1526065654646</v>
+      </c>
+      <c r="U2" t="n">
+        <v>-0.02173840058879641</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -1588,6 +1684,42 @@
       <c r="I3" t="n">
         <v>250557.6708854335</v>
       </c>
+      <c r="J3" t="n">
+        <v>-1187.643359996955</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.00868113856954778</v>
+      </c>
+      <c r="L3" t="n">
+        <v>462.4872063000618</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.04262502787392255</v>
+      </c>
+      <c r="N3" t="n">
+        <v>-1811.770631235287</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0.03034843041376769</v>
+      </c>
+      <c r="P3" t="n">
+        <v>1187.643359996955</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>-0.00868113856954778</v>
+      </c>
+      <c r="R3" t="n">
+        <v>-462.4872063000618</v>
+      </c>
+      <c r="S3" t="n">
+        <v>-0.04262502787392255</v>
+      </c>
+      <c r="T3" t="n">
+        <v>-963.1526065650828</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.021738401003519</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1619,6 +1751,42 @@
       <c r="I4" t="n">
         <v>-250557.6708854339</v>
       </c>
+      <c r="J4" t="n">
+        <v>1187.643359996957</v>
+      </c>
+      <c r="K4" t="n">
+        <v>-0.008681138569743792</v>
+      </c>
+      <c r="L4" t="n">
+        <v>537.5127936996093</v>
+      </c>
+      <c r="M4" t="n">
+        <v>-0.1280965491398132</v>
+      </c>
+      <c r="N4" t="n">
+        <v>-1887.082488781221</v>
+      </c>
+      <c r="O4" t="n">
+        <v>-0.03034843041456974</v>
+      </c>
+      <c r="P4" t="n">
+        <v>-1187.643359996957</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.008681138569743792</v>
+      </c>
+      <c r="R4" t="n">
+        <v>-387.5127936996093</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.1280965491398132</v>
+      </c>
+      <c r="T4" t="n">
+        <v>-887.9942734164347</v>
+      </c>
+      <c r="U4" t="n">
+        <v>-0.02173840100389299</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1650,6 +1818,42 @@
       <c r="I5" t="n">
         <v>-250557.670885443</v>
       </c>
+      <c r="J5" t="n">
+        <v>1187.643359997</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.008681138355098365</v>
+      </c>
+      <c r="L5" t="n">
+        <v>537.51279369982</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.1280965491385087</v>
+      </c>
+      <c r="N5" t="n">
+        <v>-1887.082488782104</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0.03034842954215432</v>
+      </c>
+      <c r="P5" t="n">
+        <v>-1187.643359997</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>-0.008681138355098365</v>
+      </c>
+      <c r="R5" t="n">
+        <v>-387.51279369982</v>
+      </c>
+      <c r="S5" t="n">
+        <v>-0.1280965491385087</v>
+      </c>
+      <c r="T5" t="n">
+        <v>-887.9942734168162</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.02173840058843586</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1681,6 +1885,42 @@
       <c r="I6" t="n">
         <v>150153.5652836699</v>
       </c>
+      <c r="J6" t="n">
+        <v>-711.7278994445956</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.003335535281722257</v>
+      </c>
+      <c r="L6" t="n">
+        <v>337.2538056231967</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-8.174341103647093e-05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>-940.3329141341959</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0.01525604259338728</v>
+      </c>
+      <c r="P6" t="n">
+        <v>711.7278994445956</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>-0.003335535281722257</v>
+      </c>
+      <c r="R6" t="n">
+        <v>-337.2538056231967</v>
+      </c>
+      <c r="S6" t="n">
+        <v>8.174341103647093e-05</v>
+      </c>
+      <c r="T6" t="n">
+        <v>-1083.189919604984</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.004757169096946262</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1712,6 +1952,42 @@
       <c r="I7" t="n">
         <v>150153.5652836659</v>
       </c>
+      <c r="J7" t="n">
+        <v>-711.7278994445767</v>
+      </c>
+      <c r="K7" t="n">
+        <v>-0.003335535075520275</v>
+      </c>
+      <c r="L7" t="n">
+        <v>337.2538056229537</v>
+      </c>
+      <c r="M7" t="n">
+        <v>8.174340898744331e-05</v>
+      </c>
+      <c r="N7" t="n">
+        <v>-940.3329141334489</v>
+      </c>
+      <c r="O7" t="n">
+        <v>-0.01525604198034497</v>
+      </c>
+      <c r="P7" t="n">
+        <v>711.7278994445767</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0.003335535075520275</v>
+      </c>
+      <c r="R7" t="n">
+        <v>-337.2538056229537</v>
+      </c>
+      <c r="S7" t="n">
+        <v>-8.174340898744331e-05</v>
+      </c>
+      <c r="T7" t="n">
+        <v>-1083.189919604273</v>
+      </c>
+      <c r="U7" t="n">
+        <v>-0.004757168472776685</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1743,6 +2019,42 @@
       <c r="I8" t="n">
         <v>-150153.5652836662</v>
       </c>
+      <c r="J8" t="n">
+        <v>711.7278994445778</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.003335535075336502</v>
+      </c>
+      <c r="L8" t="n">
+        <v>412.7461943766295</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.0001365709851156582</v>
+      </c>
+      <c r="N8" t="n">
+        <v>-1015.843890303033</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0.01525604197975264</v>
+      </c>
+      <c r="P8" t="n">
+        <v>-711.7278994445778</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>-0.003335535075336502</v>
+      </c>
+      <c r="R8" t="n">
+        <v>-262.7461943766295</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.0001365709851156582</v>
+      </c>
+      <c r="T8" t="n">
+        <v>-1010.633275956742</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.004757168472266371</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1774,6 +2086,42 @@
       <c r="I9" t="n">
         <v>-150153.56528367</v>
       </c>
+      <c r="J9" t="n">
+        <v>711.7278994445958</v>
+      </c>
+      <c r="K9" t="n">
+        <v>-0.003335535281918336</v>
+      </c>
+      <c r="L9" t="n">
+        <v>412.7461943768724</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.0001365709830680184</v>
+      </c>
+      <c r="N9" t="n">
+        <v>-1015.843890303781</v>
+      </c>
+      <c r="O9" t="n">
+        <v>-0.01525604259399728</v>
+      </c>
+      <c r="P9" t="n">
+        <v>-711.7278994445958</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>0.003335535281918336</v>
+      </c>
+      <c r="R9" t="n">
+        <v>-262.7461943768724</v>
+      </c>
+      <c r="S9" t="n">
+        <v>-0.0001365709830680184</v>
+      </c>
+      <c r="T9" t="n">
+        <v>-1010.633275957454</v>
+      </c>
+      <c r="U9" t="n">
+        <v>-0.00475716909751274</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1805,6 +2153,42 @@
       <c r="I10" t="n">
         <v>67014.8750462411</v>
       </c>
+      <c r="J10" t="n">
+        <v>-317.6505077191828</v>
+      </c>
+      <c r="K10" t="n">
+        <v>-0.000725679616803785</v>
+      </c>
+      <c r="L10" t="n">
+        <v>213.7549774489315</v>
+      </c>
+      <c r="M10" t="n">
+        <v>-1.330920974471073e-07</v>
+      </c>
+      <c r="N10" t="n">
+        <v>-493.6679683552808</v>
+      </c>
+      <c r="O10" t="n">
+        <v>-0.003335086766222121</v>
+      </c>
+      <c r="P10" t="n">
+        <v>317.6505077191828</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0.000725679616803785</v>
+      </c>
+      <c r="R10" t="n">
+        <v>-213.7549774489315</v>
+      </c>
+      <c r="S10" t="n">
+        <v>1.330920974471073e-07</v>
+      </c>
+      <c r="T10" t="n">
+        <v>-788.861896338309</v>
+      </c>
+      <c r="U10" t="n">
+        <v>-0.00101899093460061</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1836,6 +2220,42 @@
       <c r="I11" t="n">
         <v>67014.87504624833</v>
       </c>
+      <c r="J11" t="n">
+        <v>-317.6505077192171</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.0007256797704882252</v>
+      </c>
+      <c r="L11" t="n">
+        <v>213.7549774487221</v>
+      </c>
+      <c r="M11" t="n">
+        <v>1.330904625743146e-07</v>
+      </c>
+      <c r="N11" t="n">
+        <v>-493.6679683547802</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0.003335087144958782</v>
+      </c>
+      <c r="P11" t="n">
+        <v>317.6505077192171</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>-0.0007256797704882252</v>
+      </c>
+      <c r="R11" t="n">
+        <v>-213.7549774487221</v>
+      </c>
+      <c r="S11" t="n">
+        <v>-1.330904625743146e-07</v>
+      </c>
+      <c r="T11" t="n">
+        <v>-788.8618963375543</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.001018991477970577</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1867,6 +2287,42 @@
       <c r="I12" t="n">
         <v>-67014.8750462485</v>
       </c>
+      <c r="J12" t="n">
+        <v>317.6505077192182</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-0.0007256797706754747</v>
+      </c>
+      <c r="L12" t="n">
+        <v>286.2450225507185</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-1.460844122613825e-07</v>
+      </c>
+      <c r="N12" t="n">
+        <v>-565.1279698860859</v>
+      </c>
+      <c r="O12" t="n">
+        <v>-0.003335087145519354</v>
+      </c>
+      <c r="P12" t="n">
+        <v>-317.6505077192182</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>0.0007256797706754747</v>
+      </c>
+      <c r="R12" t="n">
+        <v>-136.2450225507185</v>
+      </c>
+      <c r="S12" t="n">
+        <v>1.460844122613825e-07</v>
+      </c>
+      <c r="T12" t="n">
+        <v>-702.342165418225</v>
+      </c>
+      <c r="U12" t="n">
+        <v>-0.001018991478533501</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1898,6 +2354,42 @@
       <c r="I13" t="n">
         <v>-67014.87504624121</v>
       </c>
+      <c r="J13" t="n">
+        <v>317.6505077191835</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.0007256796166823266</v>
+      </c>
+      <c r="L13" t="n">
+        <v>286.245022550927</v>
+      </c>
+      <c r="M13" t="n">
+        <v>1.460827712407298e-07</v>
+      </c>
+      <c r="N13" t="n">
+        <v>-565.127969886584</v>
+      </c>
+      <c r="O13" t="n">
+        <v>0.003335086765759374</v>
+      </c>
+      <c r="P13" t="n">
+        <v>-317.6505077191835</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>-0.0007256796166823266</v>
+      </c>
+      <c r="R13" t="n">
+        <v>-136.245022550927</v>
+      </c>
+      <c r="S13" t="n">
+        <v>-1.460827712407298e-07</v>
+      </c>
+      <c r="T13" t="n">
+        <v>-702.3421654189774</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.001018990934334565</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1929,6 +2421,42 @@
       <c r="I14" t="n">
         <v>18521.90397858804</v>
       </c>
+      <c r="J14" t="n">
+        <v>-87.79382485850738</v>
+      </c>
+      <c r="K14" t="n">
+        <v>0.000135553010461472</v>
+      </c>
+      <c r="L14" t="n">
+        <v>81.74248202001982</v>
+      </c>
+      <c r="M14" t="n">
+        <v>2.066456408766904e-09</v>
+      </c>
+      <c r="N14" t="n">
+        <v>-128.1207564938366</v>
+      </c>
+      <c r="O14" t="n">
+        <v>0.0006973202224174468</v>
+      </c>
+      <c r="P14" t="n">
+        <v>87.79382485850738</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>-0.000135553010461472</v>
+      </c>
+      <c r="R14" t="n">
+        <v>-81.74248202001982</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-2.066456408766904e-09</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-362.3341356262787</v>
+      </c>
+      <c r="U14" t="n">
+        <v>0.0001159978403513784</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -1960,6 +2488,42 @@
       <c r="I15" t="n">
         <v>18521.90397859538</v>
       </c>
+      <c r="J15" t="n">
+        <v>-87.79382485854194</v>
+      </c>
+      <c r="K15" t="n">
+        <v>-0.0001355529532395382</v>
+      </c>
+      <c r="L15" t="n">
+        <v>81.74248202002072</v>
+      </c>
+      <c r="M15" t="n">
+        <v>-2.06706612937424e-09</v>
+      </c>
+      <c r="N15" t="n">
+        <v>-128.1207564939566</v>
+      </c>
+      <c r="O15" t="n">
+        <v>-0.0006973201342787144</v>
+      </c>
+      <c r="P15" t="n">
+        <v>87.79382485854194</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0.0001355529532395382</v>
+      </c>
+      <c r="R15" t="n">
+        <v>-81.74248202002072</v>
+      </c>
+      <c r="S15" t="n">
+        <v>2.06706612937424e-09</v>
+      </c>
+      <c r="T15" t="n">
+        <v>-362.3341356261658</v>
+      </c>
+      <c r="U15" t="n">
+        <v>-0.0001159975851585185</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -1991,6 +2555,42 @@
       <c r="I16" t="n">
         <v>-18521.9039785955</v>
       </c>
+      <c r="J16" t="n">
+        <v>87.79382485854239</v>
+      </c>
+      <c r="K16" t="n">
+        <v>0.0001355529529342408</v>
+      </c>
+      <c r="L16" t="n">
+        <v>168.2575179794908</v>
+      </c>
+      <c r="M16" t="n">
+        <v>-2.424063477723948e-09</v>
+      </c>
+      <c r="N16" t="n">
+        <v>-219.5286446350328</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0.0006973201332486564</v>
+      </c>
+      <c r="P16" t="n">
+        <v>-87.79382485854239</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>-0.0001355529529342408</v>
+      </c>
+      <c r="R16" t="n">
+        <v>-18.25751797949079</v>
+      </c>
+      <c r="S16" t="n">
+        <v>2.424063477723948e-09</v>
+      </c>
+      <c r="T16" t="n">
+        <v>-340.0164632419128</v>
+      </c>
+      <c r="U16" t="n">
+        <v>0.0001159975843567848</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2022,6 +2622,42 @@
       <c r="I17" t="n">
         <v>-18521.90397858792</v>
       </c>
+      <c r="J17" t="n">
+        <v>87.79382485850692</v>
+      </c>
+      <c r="K17" t="n">
+        <v>-0.0001355530108317436</v>
+      </c>
+      <c r="L17" t="n">
+        <v>168.2575179794911</v>
+      </c>
+      <c r="M17" t="n">
+        <v>2.423457712286137e-09</v>
+      </c>
+      <c r="N17" t="n">
+        <v>-219.528644634917</v>
+      </c>
+      <c r="O17" t="n">
+        <v>-0.000697320223406836</v>
+      </c>
+      <c r="P17" t="n">
+        <v>-87.79382485850692</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0.0001355530108317436</v>
+      </c>
+      <c r="R17" t="n">
+        <v>-18.2575179794911</v>
+      </c>
+      <c r="S17" t="n">
+        <v>-2.423457712286137e-09</v>
+      </c>
+      <c r="T17" t="n">
+        <v>-340.0164632420323</v>
+      </c>
+      <c r="U17" t="n">
+        <v>-0.0001159978415836149</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2053,6 +2689,42 @@
       <c r="I18" t="n">
         <v>-2632.328321659445</v>
       </c>
+      <c r="J18" t="n">
+        <v>12.47723624466577</v>
+      </c>
+      <c r="K18" t="n">
+        <v>-3.865352482534945e-12</v>
+      </c>
+      <c r="L18" t="n">
+        <v>1.28306291372754e-10</v>
+      </c>
+      <c r="M18" t="n">
+        <v>7.23199278240827e-13</v>
+      </c>
+      <c r="N18" t="n">
+        <v>0.006457521373425529</v>
+      </c>
+      <c r="O18" t="n">
+        <v>16.62376087106873</v>
+      </c>
+      <c r="P18" t="n">
+        <v>-12.47723624466577</v>
+      </c>
+      <c r="Q18" t="n">
+        <v>3.865352482534945e-12</v>
+      </c>
+      <c r="R18" t="n">
+        <v>-1.28306291372754e-10</v>
+      </c>
+      <c r="S18" t="n">
+        <v>-7.23199278240827e-13</v>
+      </c>
+      <c r="T18" t="n">
+        <v>-0.006457522399876302</v>
+      </c>
+      <c r="U18" t="n">
+        <v>-16.62376087109965</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2084,6 +2756,42 @@
       <c r="I19" t="n">
         <v>26420.5486660507</v>
       </c>
+      <c r="J19" t="n">
+        <v>-125.233400677098</v>
+      </c>
+      <c r="K19" t="n">
+        <v>12.48925291831083</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-475.9154605522502</v>
+      </c>
+      <c r="M19" t="n">
+        <v>2.48366232994117e-05</v>
+      </c>
+      <c r="N19" t="n">
+        <v>1903.485520698533</v>
+      </c>
+      <c r="O19" t="n">
+        <v>16.66630415556484</v>
+      </c>
+      <c r="P19" t="n">
+        <v>125.233400677098</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>-12.48925291831083</v>
+      </c>
+      <c r="R19" t="n">
+        <v>475.9154605522502</v>
+      </c>
+      <c r="S19" t="n">
+        <v>-2.48366232994117e-05</v>
+      </c>
+      <c r="T19" t="n">
+        <v>1903.838163719469</v>
+      </c>
+      <c r="U19" t="n">
+        <v>83.24771919092179</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2115,6 +2823,42 @@
       <c r="I20" t="n">
         <v>2632.328321659435</v>
       </c>
+      <c r="J20" t="n">
+        <v>-12.47723624466572</v>
+      </c>
+      <c r="K20" t="n">
+        <v>-100.000000000004</v>
+      </c>
+      <c r="L20" t="n">
+        <v>1.285480819013252e-10</v>
+      </c>
+      <c r="M20" t="n">
+        <v>7.238654120556021e-13</v>
+      </c>
+      <c r="N20" t="n">
+        <v>-0.006457522400840577</v>
+      </c>
+      <c r="O20" t="n">
+        <v>-83.37567916907628</v>
+      </c>
+      <c r="P20" t="n">
+        <v>12.47723624466572</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>-99.99999999999602</v>
+      </c>
+      <c r="R20" t="n">
+        <v>-1.285480819013252e-10</v>
+      </c>
+      <c r="S20" t="n">
+        <v>-7.238654120556021e-13</v>
+      </c>
+      <c r="T20" t="n">
+        <v>0.006457521372455919</v>
+      </c>
+      <c r="U20" t="n">
+        <v>83.37567916904467</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2146,6 +2890,42 @@
       <c r="I21" t="n">
         <v>26420.5486660618</v>
       </c>
+      <c r="J21" t="n">
+        <v>-125.233400677098</v>
+      </c>
+      <c r="K21" t="n">
+        <v>12.48925291830278</v>
+      </c>
+      <c r="L21" t="n">
+        <v>-475.9154605525324</v>
+      </c>
+      <c r="M21" t="n">
+        <v>-2.483662198250748e-05</v>
+      </c>
+      <c r="N21" t="n">
+        <v>1903.838163720598</v>
+      </c>
+      <c r="O21" t="n">
+        <v>83.24771919088963</v>
+      </c>
+      <c r="P21" t="n">
+        <v>125.233400677098</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>-12.48925291830278</v>
+      </c>
+      <c r="R21" t="n">
+        <v>475.9154605525324</v>
+      </c>
+      <c r="S21" t="n">
+        <v>2.483662198250748e-05</v>
+      </c>
+      <c r="T21" t="n">
+        <v>1903.485520699661</v>
+      </c>
+      <c r="U21" t="n">
+        <v>16.6663041555326</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2177,6 +2957,42 @@
       <c r="I22" t="n">
         <v>-2637.407494479197</v>
       </c>
+      <c r="J22" t="n">
+        <v>12.5013115238314</v>
+      </c>
+      <c r="K22" t="n">
+        <v>-2.592059900052845e-11</v>
+      </c>
+      <c r="L22" t="n">
+        <v>1.251894328219844e-10</v>
+      </c>
+      <c r="M22" t="n">
+        <v>7.758238496080594e-13</v>
+      </c>
+      <c r="N22" t="n">
+        <v>-0.001416633740610715</v>
+      </c>
+      <c r="O22" t="n">
+        <v>16.65564080088552</v>
+      </c>
+      <c r="P22" t="n">
+        <v>-12.5013115238314</v>
+      </c>
+      <c r="Q22" t="n">
+        <v>2.592059900052845e-11</v>
+      </c>
+      <c r="R22" t="n">
+        <v>-1.251894328219844e-10</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-7.758238496080594e-13</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.001416632739095252</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-16.65564080109243</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2208,6 +3024,42 @@
       <c r="I23" t="n">
         <v>26054.60510003432</v>
       </c>
+      <c r="J23" t="n">
+        <v>-123.4988281741971</v>
+      </c>
+      <c r="K23" t="n">
+        <v>12.49725030898538</v>
+      </c>
+      <c r="L23" t="n">
+        <v>-394.0773917252354</v>
+      </c>
+      <c r="M23" t="n">
+        <v>-5.448588741532367e-06</v>
+      </c>
+      <c r="N23" t="n">
+        <v>1576.857887959055</v>
+      </c>
+      <c r="O23" t="n">
+        <v>16.65572241141295</v>
+      </c>
+      <c r="P23" t="n">
+        <v>123.4988281741971</v>
+      </c>
+      <c r="Q23" t="n">
+        <v>-12.49725030898538</v>
+      </c>
+      <c r="R23" t="n">
+        <v>394.0773917252354</v>
+      </c>
+      <c r="S23" t="n">
+        <v>5.448588741532367e-06</v>
+      </c>
+      <c r="T23" t="n">
+        <v>1575.761245842828</v>
+      </c>
+      <c r="U23" t="n">
+        <v>83.32228006047011</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2239,6 +3091,42 @@
       <c r="I24" t="n">
         <v>2637.407494479197</v>
       </c>
+      <c r="J24" t="n">
+        <v>-12.50131152383139</v>
+      </c>
+      <c r="K24" t="n">
+        <v>-100.0000000000263</v>
+      </c>
+      <c r="L24" t="n">
+        <v>1.254654333985444e-10</v>
+      </c>
+      <c r="M24" t="n">
+        <v>7.751577157932843e-13</v>
+      </c>
+      <c r="N24" t="n">
+        <v>0.001416632737978864</v>
+      </c>
+      <c r="O24" t="n">
+        <v>-83.32241648536987</v>
+      </c>
+      <c r="P24" t="n">
+        <v>12.50131152383139</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>-99.99999999997374</v>
+      </c>
+      <c r="R24" t="n">
+        <v>-1.254654333985444e-10</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-7.751577157932843e-13</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.00141663374170233</v>
+      </c>
+      <c r="U24" t="n">
+        <v>83.32241648516023</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -2270,6 +3158,42 @@
       <c r="I25" t="n">
         <v>26054.60510003432</v>
       </c>
+      <c r="J25" t="n">
+        <v>-123.4988281741971</v>
+      </c>
+      <c r="K25" t="n">
+        <v>12.49725030893287</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-394.0773917255378</v>
+      </c>
+      <c r="M25" t="n">
+        <v>5.448590026519767e-06</v>
+      </c>
+      <c r="N25" t="n">
+        <v>1575.761245844037</v>
+      </c>
+      <c r="O25" t="n">
+        <v>83.32228006026035</v>
+      </c>
+      <c r="P25" t="n">
+        <v>123.4988281741971</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-12.49725030893287</v>
+      </c>
+      <c r="R25" t="n">
+        <v>394.0773917255378</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-5.448590026519767e-06</v>
+      </c>
+      <c r="T25" t="n">
+        <v>1576.857887960265</v>
+      </c>
+      <c r="U25" t="n">
+        <v>16.65572241120256</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -2301,6 +3225,42 @@
       <c r="I26" t="n">
         <v>-2636.370315120039</v>
       </c>
+      <c r="J26" t="n">
+        <v>12.49639529366899</v>
+      </c>
+      <c r="K26" t="n">
+        <v>-4.843059286940843e-11</v>
+      </c>
+      <c r="L26" t="n">
+        <v>7.886364625849396e-11</v>
+      </c>
+      <c r="M26" t="n">
+        <v>4.087841176669826e-13</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.0003204382566711034</v>
+      </c>
+      <c r="O26" t="n">
+        <v>16.65569270639389</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-12.49639529366899</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>4.843059286940843e-11</v>
+      </c>
+      <c r="R26" t="n">
+        <v>-7.886364625849396e-11</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-4.087841176669826e-13</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.0003204388875802733</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-16.65569270678225</v>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -2332,6 +3292,42 @@
       <c r="I27" t="n">
         <v>27850.73743223343</v>
       </c>
+      <c r="J27" t="n">
+        <v>-132.0124954287894</v>
+      </c>
+      <c r="K27" t="n">
+        <v>12.49725652639148</v>
+      </c>
+      <c r="L27" t="n">
+        <v>-229.8566828605958</v>
+      </c>
+      <c r="M27" t="n">
+        <v>1.232456451699434e-06</v>
+      </c>
+      <c r="N27" t="n">
+        <v>916.9826528315087</v>
+      </c>
+      <c r="O27" t="n">
+        <v>16.65569284193676</v>
+      </c>
+      <c r="P27" t="n">
+        <v>132.0124954287894</v>
+      </c>
+      <c r="Q27" t="n">
+        <v>-12.49725652639148</v>
+      </c>
+      <c r="R27" t="n">
+        <v>229.8566828605958</v>
+      </c>
+      <c r="S27" t="n">
+        <v>-1.232456451699434e-06</v>
+      </c>
+      <c r="T27" t="n">
+        <v>921.8708100532576</v>
+      </c>
+      <c r="U27" t="n">
+        <v>83.32235936919508</v>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -2363,6 +3359,42 @@
       <c r="I28" t="n">
         <v>2636.370315119826</v>
       </c>
+      <c r="J28" t="n">
+        <v>-12.49639529366798</v>
+      </c>
+      <c r="K28" t="n">
+        <v>-100.0000000000475</v>
+      </c>
+      <c r="L28" t="n">
+        <v>7.919405605740729e-11</v>
+      </c>
+      <c r="M28" t="n">
+        <v>4.084510507595951e-13</v>
+      </c>
+      <c r="N28" t="n">
+        <v>-0.0003204388888398558</v>
+      </c>
+      <c r="O28" t="n">
+        <v>-83.32235951285415</v>
+      </c>
+      <c r="P28" t="n">
+        <v>12.49639529366798</v>
+      </c>
+      <c r="Q28" t="n">
+        <v>-99.99999999995248</v>
+      </c>
+      <c r="R28" t="n">
+        <v>-7.919405605740729e-11</v>
+      </c>
+      <c r="S28" t="n">
+        <v>-4.084510507595951e-13</v>
+      </c>
+      <c r="T28" t="n">
+        <v>0.0003204382552865191</v>
+      </c>
+      <c r="U28" t="n">
+        <v>83.32235951247489</v>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -2394,6 +3426,42 @@
       <c r="I29" t="n">
         <v>27850.73743214461</v>
       </c>
+      <c r="J29" t="n">
+        <v>-132.0124954283237</v>
+      </c>
+      <c r="K29" t="n">
+        <v>12.49725652629611</v>
+      </c>
+      <c r="L29" t="n">
+        <v>-229.8566828607552</v>
+      </c>
+      <c r="M29" t="n">
+        <v>-1.232455641335499e-06</v>
+      </c>
+      <c r="N29" t="n">
+        <v>921.870810053895</v>
+      </c>
+      <c r="O29" t="n">
+        <v>83.32235936881273</v>
+      </c>
+      <c r="P29" t="n">
+        <v>132.0124954283237</v>
+      </c>
+      <c r="Q29" t="n">
+        <v>-12.49725652629611</v>
+      </c>
+      <c r="R29" t="n">
+        <v>229.8566828607552</v>
+      </c>
+      <c r="S29" t="n">
+        <v>1.232455641335499e-06</v>
+      </c>
+      <c r="T29" t="n">
+        <v>916.9826528321462</v>
+      </c>
+      <c r="U29" t="n">
+        <v>16.65569284155616</v>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -2425,6 +3493,42 @@
       <c r="I30" t="n">
         <v>-2636.580561374263</v>
       </c>
+      <c r="J30" t="n">
+        <v>12.49739186091401</v>
+      </c>
+      <c r="K30" t="n">
+        <v>-2.91038304567337e-11</v>
+      </c>
+      <c r="L30" t="n">
+        <v>3.185670624457392e-11</v>
+      </c>
+      <c r="M30" t="n">
+        <v>7.083222897108499e-14</v>
+      </c>
+      <c r="N30" t="n">
+        <v>-0.000115553404494969</v>
+      </c>
+      <c r="O30" t="n">
+        <v>16.65569190043516</v>
+      </c>
+      <c r="P30" t="n">
+        <v>-12.49739186091401</v>
+      </c>
+      <c r="Q30" t="n">
+        <v>2.91038304567337e-11</v>
+      </c>
+      <c r="R30" t="n">
+        <v>-3.185670624457392e-11</v>
+      </c>
+      <c r="S30" t="n">
+        <v>-7.083222897108499e-14</v>
+      </c>
+      <c r="T30" t="n">
+        <v>0.0001155531496422071</v>
+      </c>
+      <c r="U30" t="n">
+        <v>-16.65569190066799</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -2456,6 +3560,42 @@
       <c r="I31" t="n">
         <v>17245.24937132265</v>
       </c>
+      <c r="J31" t="n">
+        <v>-81.74248202005401</v>
+      </c>
+      <c r="K31" t="n">
+        <v>12.49725630796159</v>
+      </c>
+      <c r="L31" t="n">
+        <v>-87.79382485851036</v>
+      </c>
+      <c r="M31" t="n">
+        <v>-4.444355165871917e-07</v>
+      </c>
+      <c r="N31" t="n">
+        <v>362.3341356261689</v>
+      </c>
+      <c r="O31" t="n">
+        <v>16.65569189860274</v>
+      </c>
+      <c r="P31" t="n">
+        <v>81.74248202005401</v>
+      </c>
+      <c r="Q31" t="n">
+        <v>-12.49725630796159</v>
+      </c>
+      <c r="R31" t="n">
+        <v>87.79382485851036</v>
+      </c>
+      <c r="S31" t="n">
+        <v>4.444355165871917e-07</v>
+      </c>
+      <c r="T31" t="n">
+        <v>340.0164632419138</v>
+      </c>
+      <c r="U31" t="n">
+        <v>83.32235856509004</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -2487,6 +3627,42 @@
       <c r="I32" t="n">
         <v>2636.580561374374</v>
       </c>
+      <c r="J32" t="n">
+        <v>-12.49739186091453</v>
+      </c>
+      <c r="K32" t="n">
+        <v>-100.0000000000293</v>
+      </c>
+      <c r="L32" t="n">
+        <v>3.218251569913049e-11</v>
+      </c>
+      <c r="M32" t="n">
+        <v>7.255307465925398e-14</v>
+      </c>
+      <c r="N32" t="n">
+        <v>0.0001155531482243991</v>
+      </c>
+      <c r="O32" t="n">
+        <v>-83.32235856751535</v>
+      </c>
+      <c r="P32" t="n">
+        <v>12.49739186091453</v>
+      </c>
+      <c r="Q32" t="n">
+        <v>-99.99999999997067</v>
+      </c>
+      <c r="R32" t="n">
+        <v>-3.218251569913049e-11</v>
+      </c>
+      <c r="S32" t="n">
+        <v>-7.255307465925398e-14</v>
+      </c>
+      <c r="T32" t="n">
+        <v>-0.0001155534056854128</v>
+      </c>
+      <c r="U32" t="n">
+        <v>83.32235856727888</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -2517,6 +3693,42 @@
       </c>
       <c r="I33" t="n">
         <v>17245.24937145588</v>
+      </c>
+      <c r="J33" t="n">
+        <v>-81.7424820207525</v>
+      </c>
+      <c r="K33" t="n">
+        <v>12.49725630790358</v>
+      </c>
+      <c r="L33" t="n">
+        <v>-87.79382485853831</v>
+      </c>
+      <c r="M33" t="n">
+        <v>4.444358450432963e-07</v>
+      </c>
+      <c r="N33" t="n">
+        <v>340.0164632420261</v>
+      </c>
+      <c r="O33" t="n">
+        <v>83.32235856485785</v>
+      </c>
+      <c r="P33" t="n">
+        <v>81.7424820207525</v>
+      </c>
+      <c r="Q33" t="n">
+        <v>-12.49725630790358</v>
+      </c>
+      <c r="R33" t="n">
+        <v>87.79382485853831</v>
+      </c>
+      <c r="S33" t="n">
+        <v>-4.444358450432963e-07</v>
+      </c>
+      <c r="T33" t="n">
+        <v>362.3341356262804</v>
+      </c>
+      <c r="U33" t="n">
+        <v>16.65569189837078</v>
       </c>
     </row>
   </sheetData>
@@ -2530,7 +3742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AP33"/>
+  <dimension ref="A1:AS33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2541,205 +3753,220 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>i</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>j</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>L (M)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>N_tension (+) (KN)</t>
-        </is>
-      </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>Δu_local_x (M)</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>axial strain</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>N (KN)</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>sigma (KN/M^2)</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>u_g_1 (M)</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>u_g_2 (M)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>u_g_3 (M)</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>u_g_4 (rad)</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>u_g_5 (rad)</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>u_g_6 (rad)</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>u_g_7 (M)</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>u_g_8 (M)</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>u_g_9 (M)</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>u_g_10 (rad)</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>u_g_11 (rad)</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>u_g_12 (rad)</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>u_l_1 (M)</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>u_l_2 (M)</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="X1" s="1" t="inlineStr">
         <is>
           <t>u_l_3 (M)</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="Y1" s="1" t="inlineStr">
         <is>
           <t>u_l_4 (rad)</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="Z1" s="1" t="inlineStr">
         <is>
           <t>u_l_5 (rad)</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>u_l_6 (rad)</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>u_l_7 (M)</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>u_l_8 (M)</t>
         </is>
       </c>
-      <c r="AA1" s="1" t="inlineStr">
+      <c r="AD1" s="1" t="inlineStr">
         <is>
           <t>u_l_9 (M)</t>
         </is>
       </c>
-      <c r="AB1" s="1" t="inlineStr">
+      <c r="AE1" s="1" t="inlineStr">
         <is>
           <t>u_l_10 (rad)</t>
         </is>
       </c>
-      <c r="AC1" s="1" t="inlineStr">
+      <c r="AF1" s="1" t="inlineStr">
         <is>
           <t>u_l_11 (rad)</t>
         </is>
       </c>
-      <c r="AD1" s="1" t="inlineStr">
+      <c r="AG1" s="1" t="inlineStr">
         <is>
           <t>u_l_12 (rad)</t>
         </is>
       </c>
-      <c r="AE1" s="1" t="inlineStr">
+      <c r="AH1" s="1" t="inlineStr">
         <is>
           <t>q_l_1 (KN)</t>
         </is>
       </c>
-      <c r="AF1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>q_l_2 (KN)</t>
         </is>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>q_l_3 (KN)</t>
         </is>
       </c>
-      <c r="AH1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>q_l_4 (KN*M)</t>
         </is>
       </c>
-      <c r="AI1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>q_l_5 (KN*M)</t>
         </is>
       </c>
-      <c r="AJ1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>q_l_6 (KN*M)</t>
         </is>
       </c>
-      <c r="AK1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>q_l_7 (KN)</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>q_l_8 (KN)</t>
         </is>
       </c>
-      <c r="AM1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>q_l_9 (KN)</t>
         </is>
       </c>
-      <c r="AN1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>q_l_10 (KN*M)</t>
         </is>
       </c>
-      <c r="AO1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>q_l_11 (KN*M)</t>
         </is>
       </c>
-      <c r="AP1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>q_l_12 (KN*M)</t>
         </is>
@@ -2749,30 +3976,32 @@
       <c r="A2" t="n">
         <v>1</v>
       </c>
-      <c r="B2" t="n">
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
         <v>1</v>
       </c>
-      <c r="C2" t="n">
+      <c r="D2" t="n">
         <v>5</v>
       </c>
-      <c r="D2" t="n">
+      <c r="E2" t="n">
         <v>6</v>
       </c>
-      <c r="E2" t="n">
+      <c r="F2" t="n">
+        <v>0.007516730126563289</v>
+      </c>
+      <c r="G2" t="n">
+        <v>0.001252788354427215</v>
+      </c>
+      <c r="H2" t="n">
         <v>1187.643359997</v>
       </c>
-      <c r="F2" t="n">
+      <c r="I2" t="n">
         <v>250557.670885443</v>
       </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
-      <c r="H2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I2" t="n">
-        <v>0</v>
-      </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
@@ -2783,32 +4012,32 @@
         <v>0</v>
       </c>
       <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>0</v>
+      </c>
+      <c r="P2" t="n">
         <v>3.595119805279563</v>
       </c>
-      <c r="N2" t="n">
+      <c r="Q2" t="n">
         <v>5.264656553662592e-05</v>
       </c>
-      <c r="O2" t="n">
+      <c r="R2" t="n">
         <v>0.007516730126563289</v>
       </c>
-      <c r="P2" t="n">
+      <c r="S2" t="n">
         <v>-5.817587131184721e-06</v>
       </c>
-      <c r="Q2" t="n">
+      <c r="T2" t="n">
         <v>0.5733905572099365</v>
       </c>
-      <c r="R2" t="n">
+      <c r="U2" t="n">
         <v>0.01497636114535011</v>
       </c>
-      <c r="S2" t="n">
-        <v>0</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0</v>
-      </c>
       <c r="V2" t="n">
         <v>0</v>
       </c>
@@ -2819,57 +4048,66 @@
         <v>0</v>
       </c>
       <c r="Y2" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="n">
         <v>0.007516730126563289</v>
       </c>
-      <c r="Z2" t="n">
+      <c r="AC2" t="n">
         <v>5.264656553662592e-05</v>
       </c>
-      <c r="AA2" t="n">
+      <c r="AD2" t="n">
         <v>-3.595119805279563</v>
       </c>
-      <c r="AB2" t="n">
+      <c r="AE2" t="n">
         <v>0.01497636114535011</v>
       </c>
-      <c r="AC2" t="n">
+      <c r="AF2" t="n">
         <v>0.5733905572099365</v>
       </c>
-      <c r="AD2" t="n">
+      <c r="AG2" t="n">
         <v>5.817587131184721e-06</v>
       </c>
-      <c r="AE2" t="n">
+      <c r="AH2" t="n">
         <v>-1187.643359997</v>
       </c>
-      <c r="AF2" t="n">
+      <c r="AI2" t="n">
         <v>-0.008681138355291034</v>
       </c>
-      <c r="AG2" t="n">
+      <c r="AJ2" t="n">
         <v>462.4872063002725</v>
       </c>
-      <c r="AH2" t="n">
+      <c r="AK2" t="n">
         <v>-0.04262502787522724</v>
       </c>
-      <c r="AI2" t="n">
+      <c r="AL2" t="n">
         <v>-1811.770631236171</v>
       </c>
-      <c r="AJ2" t="n">
+      <c r="AM2" t="n">
         <v>-0.03034842954294979</v>
       </c>
-      <c r="AK2" t="n">
+      <c r="AN2" t="n">
         <v>1187.643359997</v>
       </c>
-      <c r="AL2" t="n">
+      <c r="AO2" t="n">
         <v>0.008681138355291034</v>
       </c>
-      <c r="AM2" t="n">
+      <c r="AP2" t="n">
         <v>-462.4872063002725</v>
       </c>
-      <c r="AN2" t="n">
+      <c r="AQ2" t="n">
         <v>0.04262502787522724</v>
       </c>
-      <c r="AO2" t="n">
+      <c r="AR2" t="n">
         <v>-963.1526065654646</v>
       </c>
-      <c r="AP2" t="n">
+      <c r="AS2" t="n">
         <v>-0.02173840058879641</v>
       </c>
     </row>
@@ -2877,30 +4115,32 @@
       <c r="A3" t="n">
         <v>2</v>
       </c>
-      <c r="B3" t="n">
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
         <v>2</v>
-      </c>
-      <c r="C3" t="n">
-        <v>6</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
+        <v>6</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.007516730126563006</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0.001252788354427168</v>
+      </c>
+      <c r="H3" t="n">
         <v>1187.643359996955</v>
       </c>
-      <c r="F3" t="n">
+      <c r="I3" t="n">
         <v>250557.6708854335</v>
       </c>
-      <c r="G3" t="n">
-        <v>0</v>
-      </c>
-      <c r="H3" t="n">
-        <v>0</v>
-      </c>
-      <c r="I3" t="n">
-        <v>0</v>
-      </c>
       <c r="J3" t="n">
         <v>0</v>
       </c>
@@ -2911,32 +4151,32 @@
         <v>0</v>
       </c>
       <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>0</v>
+      </c>
+      <c r="P3" t="n">
         <v>3.595119805277692</v>
       </c>
-      <c r="N3" t="n">
+      <c r="Q3" t="n">
         <v>-5.264656732975187e-05</v>
       </c>
-      <c r="O3" t="n">
+      <c r="R3" t="n">
         <v>0.007516730126563006</v>
       </c>
-      <c r="P3" t="n">
+      <c r="S3" t="n">
         <v>5.817587439357226e-06</v>
       </c>
-      <c r="Q3" t="n">
+      <c r="T3" t="n">
         <v>0.5733905572095976</v>
       </c>
-      <c r="R3" t="n">
+      <c r="U3" t="n">
         <v>-0.01497636114489171</v>
       </c>
-      <c r="S3" t="n">
-        <v>0</v>
-      </c>
-      <c r="T3" t="n">
-        <v>0</v>
-      </c>
-      <c r="U3" t="n">
-        <v>0</v>
-      </c>
       <c r="V3" t="n">
         <v>0</v>
       </c>
@@ -2947,57 +4187,66 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB3" t="n">
         <v>0.007516730126563006</v>
       </c>
-      <c r="Z3" t="n">
+      <c r="AC3" t="n">
         <v>-5.264656732975187e-05</v>
       </c>
-      <c r="AA3" t="n">
+      <c r="AD3" t="n">
         <v>-3.595119805277692</v>
       </c>
-      <c r="AB3" t="n">
+      <c r="AE3" t="n">
         <v>-0.01497636114489171</v>
       </c>
-      <c r="AC3" t="n">
+      <c r="AF3" t="n">
         <v>0.5733905572095976</v>
       </c>
-      <c r="AD3" t="n">
+      <c r="AG3" t="n">
         <v>-5.817587439357226e-06</v>
       </c>
-      <c r="AE3" t="n">
+      <c r="AH3" t="n">
         <v>-1187.643359996955</v>
       </c>
-      <c r="AF3" t="n">
+      <c r="AI3" t="n">
         <v>0.00868113856954778</v>
       </c>
-      <c r="AG3" t="n">
+      <c r="AJ3" t="n">
         <v>462.4872063000618</v>
       </c>
-      <c r="AH3" t="n">
+      <c r="AK3" t="n">
         <v>0.04262502787392255</v>
       </c>
-      <c r="AI3" t="n">
+      <c r="AL3" t="n">
         <v>-1811.770631235287</v>
       </c>
-      <c r="AJ3" t="n">
+      <c r="AM3" t="n">
         <v>0.03034843041376769</v>
       </c>
-      <c r="AK3" t="n">
+      <c r="AN3" t="n">
         <v>1187.643359996955</v>
       </c>
-      <c r="AL3" t="n">
+      <c r="AO3" t="n">
         <v>-0.00868113856954778</v>
       </c>
-      <c r="AM3" t="n">
+      <c r="AP3" t="n">
         <v>-462.4872063000618</v>
       </c>
-      <c r="AN3" t="n">
+      <c r="AQ3" t="n">
         <v>-0.04262502787392255</v>
       </c>
-      <c r="AO3" t="n">
+      <c r="AR3" t="n">
         <v>-963.1526065650828</v>
       </c>
-      <c r="AP3" t="n">
+      <c r="AS3" t="n">
         <v>0.021738401003519</v>
       </c>
     </row>
@@ -3005,30 +4254,32 @@
       <c r="A4" t="n">
         <v>3</v>
       </c>
-      <c r="B4" t="n">
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
         <v>3</v>
       </c>
-      <c r="C4" t="n">
+      <c r="D4" t="n">
         <v>7</v>
       </c>
-      <c r="D4" t="n">
+      <c r="E4" t="n">
         <v>6</v>
       </c>
-      <c r="E4" t="n">
+      <c r="F4" t="n">
+        <v>-0.007516730126563017</v>
+      </c>
+      <c r="G4" t="n">
+        <v>-0.00125278835442717</v>
+      </c>
+      <c r="H4" t="n">
         <v>-1187.643359996957</v>
       </c>
-      <c r="F4" t="n">
+      <c r="I4" t="n">
         <v>-250557.6708854339</v>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
       <c r="J4" t="n">
         <v>0</v>
       </c>
@@ -3039,32 +4290,32 @@
         <v>0</v>
       </c>
       <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
         <v>3.596176627224334</v>
       </c>
-      <c r="N4" t="n">
+      <c r="Q4" t="n">
         <v>5.264656733141418e-05</v>
       </c>
-      <c r="O4" t="n">
+      <c r="R4" t="n">
         <v>-0.007516730126563017</v>
       </c>
-      <c r="P4" t="n">
+      <c r="S4" t="n">
         <v>-5.817587439646455e-06</v>
       </c>
-      <c r="Q4" t="n">
+      <c r="T4" t="n">
         <v>0.5737082536248554</v>
       </c>
-      <c r="R4" t="n">
+      <c r="U4" t="n">
         <v>0.04500689564371815</v>
       </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
       <c r="V4" t="n">
         <v>0</v>
       </c>
@@ -3075,57 +4326,66 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
         <v>-0.007516730126563017</v>
       </c>
-      <c r="Z4" t="n">
+      <c r="AC4" t="n">
         <v>5.264656733141418e-05</v>
       </c>
-      <c r="AA4" t="n">
+      <c r="AD4" t="n">
         <v>-3.596176627224334</v>
       </c>
-      <c r="AB4" t="n">
+      <c r="AE4" t="n">
         <v>0.04500689564371815</v>
       </c>
-      <c r="AC4" t="n">
+      <c r="AF4" t="n">
         <v>0.5737082536248554</v>
       </c>
-      <c r="AD4" t="n">
+      <c r="AG4" t="n">
         <v>5.817587439646455e-06</v>
       </c>
-      <c r="AE4" t="n">
+      <c r="AH4" t="n">
         <v>1187.643359996957</v>
       </c>
-      <c r="AF4" t="n">
+      <c r="AI4" t="n">
         <v>-0.008681138569743792</v>
       </c>
-      <c r="AG4" t="n">
+      <c r="AJ4" t="n">
         <v>537.5127936996093</v>
       </c>
-      <c r="AH4" t="n">
+      <c r="AK4" t="n">
         <v>-0.1280965491398132</v>
       </c>
-      <c r="AI4" t="n">
+      <c r="AL4" t="n">
         <v>-1887.082488781221</v>
       </c>
-      <c r="AJ4" t="n">
+      <c r="AM4" t="n">
         <v>-0.03034843041456974</v>
       </c>
-      <c r="AK4" t="n">
+      <c r="AN4" t="n">
         <v>-1187.643359996957</v>
       </c>
-      <c r="AL4" t="n">
+      <c r="AO4" t="n">
         <v>0.008681138569743792</v>
       </c>
-      <c r="AM4" t="n">
+      <c r="AP4" t="n">
         <v>-387.5127936996093</v>
       </c>
-      <c r="AN4" t="n">
+      <c r="AQ4" t="n">
         <v>0.1280965491398132</v>
       </c>
-      <c r="AO4" t="n">
+      <c r="AR4" t="n">
         <v>-887.9942734164347</v>
       </c>
-      <c r="AP4" t="n">
+      <c r="AS4" t="n">
         <v>-0.02173840100389299</v>
       </c>
     </row>
@@ -3133,30 +4393,32 @@
       <c r="A5" t="n">
         <v>4</v>
       </c>
-      <c r="B5" t="n">
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
         <v>4</v>
       </c>
-      <c r="C5" t="n">
+      <c r="D5" t="n">
         <v>8</v>
       </c>
-      <c r="D5" t="n">
+      <c r="E5" t="n">
         <v>6</v>
       </c>
-      <c r="E5" t="n">
+      <c r="F5" t="n">
+        <v>-0.00751673012656329</v>
+      </c>
+      <c r="G5" t="n">
+        <v>-0.001252788354427215</v>
+      </c>
+      <c r="H5" t="n">
         <v>-1187.643359997</v>
       </c>
-      <c r="F5" t="n">
+      <c r="I5" t="n">
         <v>-250557.670885443</v>
       </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" t="n">
-        <v>0</v>
-      </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
@@ -3167,32 +4429,32 @@
         <v>0</v>
       </c>
       <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
         <v>3.596176627226205</v>
       </c>
-      <c r="N5" t="n">
+      <c r="Q5" t="n">
         <v>-5.264656553496323e-05</v>
       </c>
-      <c r="O5" t="n">
+      <c r="R5" t="n">
         <v>-0.00751673012656329</v>
       </c>
-      <c r="P5" t="n">
+      <c r="S5" t="n">
         <v>5.817587130890855e-06</v>
       </c>
-      <c r="Q5" t="n">
+      <c r="T5" t="n">
         <v>0.5737082536251945</v>
       </c>
-      <c r="R5" t="n">
+      <c r="U5" t="n">
         <v>-0.04500689564325982</v>
       </c>
-      <c r="S5" t="n">
-        <v>0</v>
-      </c>
-      <c r="T5" t="n">
-        <v>0</v>
-      </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
@@ -3203,57 +4465,66 @@
         <v>0</v>
       </c>
       <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
         <v>-0.00751673012656329</v>
       </c>
-      <c r="Z5" t="n">
+      <c r="AC5" t="n">
         <v>-5.264656553496323e-05</v>
       </c>
-      <c r="AA5" t="n">
+      <c r="AD5" t="n">
         <v>-3.596176627226205</v>
       </c>
-      <c r="AB5" t="n">
+      <c r="AE5" t="n">
         <v>-0.04500689564325982</v>
       </c>
-      <c r="AC5" t="n">
+      <c r="AF5" t="n">
         <v>0.5737082536251945</v>
       </c>
-      <c r="AD5" t="n">
+      <c r="AG5" t="n">
         <v>-5.817587130890855e-06</v>
       </c>
-      <c r="AE5" t="n">
+      <c r="AH5" t="n">
         <v>1187.643359997</v>
       </c>
-      <c r="AF5" t="n">
+      <c r="AI5" t="n">
         <v>0.008681138355098365</v>
       </c>
-      <c r="AG5" t="n">
+      <c r="AJ5" t="n">
         <v>537.51279369982</v>
       </c>
-      <c r="AH5" t="n">
+      <c r="AK5" t="n">
         <v>0.1280965491385087</v>
       </c>
-      <c r="AI5" t="n">
+      <c r="AL5" t="n">
         <v>-1887.082488782104</v>
       </c>
-      <c r="AJ5" t="n">
+      <c r="AM5" t="n">
         <v>0.03034842954215432</v>
       </c>
-      <c r="AK5" t="n">
+      <c r="AN5" t="n">
         <v>-1187.643359997</v>
       </c>
-      <c r="AL5" t="n">
+      <c r="AO5" t="n">
         <v>-0.008681138355098365</v>
       </c>
-      <c r="AM5" t="n">
+      <c r="AP5" t="n">
         <v>-387.51279369982</v>
       </c>
-      <c r="AN5" t="n">
+      <c r="AQ5" t="n">
         <v>-0.1280965491385087</v>
       </c>
-      <c r="AO5" t="n">
+      <c r="AR5" t="n">
         <v>-887.9942734168162</v>
       </c>
-      <c r="AP5" t="n">
+      <c r="AS5" t="n">
         <v>0.02173840058843586</v>
       </c>
     </row>
@@ -3261,127 +4532,138 @@
       <c r="A6" t="n">
         <v>5</v>
       </c>
-      <c r="B6" t="n">
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
         <v>5</v>
       </c>
-      <c r="C6" t="n">
+      <c r="D6" t="n">
         <v>9</v>
       </c>
-      <c r="D6" t="n">
+      <c r="E6" t="n">
         <v>6</v>
       </c>
-      <c r="E6" t="n">
+      <c r="F6" t="n">
+        <v>0.004504606958510098</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0.0007507678264183497</v>
+      </c>
+      <c r="H6" t="n">
         <v>711.7278994445956</v>
       </c>
-      <c r="F6" t="n">
+      <c r="I6" t="n">
         <v>150153.5652836699</v>
       </c>
-      <c r="G6" t="n">
+      <c r="J6" t="n">
         <v>3.595119805279563</v>
       </c>
-      <c r="H6" t="n">
+      <c r="K6" t="n">
         <v>5.264656553662592e-05</v>
       </c>
-      <c r="I6" t="n">
+      <c r="L6" t="n">
         <v>0.007516730126563289</v>
       </c>
-      <c r="J6" t="n">
+      <c r="M6" t="n">
         <v>-5.817587131184721e-06</v>
       </c>
-      <c r="K6" t="n">
+      <c r="N6" t="n">
         <v>0.5733905572099365</v>
       </c>
-      <c r="L6" t="n">
+      <c r="O6" t="n">
         <v>0.01497636114535011</v>
       </c>
-      <c r="M6" t="n">
+      <c r="P6" t="n">
         <v>8.113133295381624</v>
       </c>
-      <c r="N6" t="n">
+      <c r="Q6" t="n">
         <v>5.27481476618041e-05</v>
       </c>
-      <c r="O6" t="n">
+      <c r="R6" t="n">
         <v>0.01202133708507339</v>
       </c>
-      <c r="P6" t="n">
+      <c r="S6" t="n">
         <v>1.276246312356512e-06</v>
       </c>
-      <c r="Q6" t="n">
+      <c r="T6" t="n">
         <v>0.4768655535134581</v>
       </c>
-      <c r="R6" t="n">
+      <c r="U6" t="n">
         <v>0.01500508180328185</v>
       </c>
-      <c r="S6" t="n">
+      <c r="V6" t="n">
         <v>0.007516730126563289</v>
       </c>
-      <c r="T6" t="n">
+      <c r="W6" t="n">
         <v>5.264656553662592e-05</v>
       </c>
-      <c r="U6" t="n">
+      <c r="X6" t="n">
         <v>-3.595119805279563</v>
       </c>
-      <c r="V6" t="n">
+      <c r="Y6" t="n">
         <v>0.01497636114535011</v>
       </c>
-      <c r="W6" t="n">
+      <c r="Z6" t="n">
         <v>0.5733905572099365</v>
       </c>
-      <c r="X6" t="n">
+      <c r="AA6" t="n">
         <v>5.817587131184721e-06</v>
       </c>
-      <c r="Y6" t="n">
+      <c r="AB6" t="n">
         <v>0.01202133708507339</v>
       </c>
-      <c r="Z6" t="n">
+      <c r="AC6" t="n">
         <v>5.27481476618041e-05</v>
       </c>
-      <c r="AA6" t="n">
+      <c r="AD6" t="n">
         <v>-8.113133295381624</v>
       </c>
-      <c r="AB6" t="n">
+      <c r="AE6" t="n">
         <v>0.01500508180328185</v>
       </c>
-      <c r="AC6" t="n">
+      <c r="AF6" t="n">
         <v>0.4768655535134581</v>
       </c>
-      <c r="AD6" t="n">
+      <c r="AG6" t="n">
         <v>-1.276246312356512e-06</v>
       </c>
-      <c r="AE6" t="n">
+      <c r="AH6" t="n">
         <v>-711.7278994445956</v>
       </c>
-      <c r="AF6" t="n">
+      <c r="AI6" t="n">
         <v>0.003335535281722257</v>
       </c>
-      <c r="AG6" t="n">
+      <c r="AJ6" t="n">
         <v>337.2538056231967</v>
       </c>
-      <c r="AH6" t="n">
+      <c r="AK6" t="n">
         <v>-8.174341103647093e-05</v>
       </c>
-      <c r="AI6" t="n">
+      <c r="AL6" t="n">
         <v>-940.3329141341959</v>
       </c>
-      <c r="AJ6" t="n">
+      <c r="AM6" t="n">
         <v>0.01525604259338728</v>
       </c>
-      <c r="AK6" t="n">
+      <c r="AN6" t="n">
         <v>711.7278994445956</v>
       </c>
-      <c r="AL6" t="n">
+      <c r="AO6" t="n">
         <v>-0.003335535281722257</v>
       </c>
-      <c r="AM6" t="n">
+      <c r="AP6" t="n">
         <v>-337.2538056231967</v>
       </c>
-      <c r="AN6" t="n">
+      <c r="AQ6" t="n">
         <v>8.174341103647093e-05</v>
       </c>
-      <c r="AO6" t="n">
+      <c r="AR6" t="n">
         <v>-1083.189919604984</v>
       </c>
-      <c r="AP6" t="n">
+      <c r="AS6" t="n">
         <v>0.004757169096946262</v>
       </c>
     </row>
@@ -3389,127 +4671,138 @@
       <c r="A7" t="n">
         <v>6</v>
       </c>
-      <c r="B7" t="n">
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
         <v>6</v>
       </c>
-      <c r="C7" t="n">
+      <c r="D7" t="n">
         <v>10</v>
       </c>
-      <c r="D7" t="n">
+      <c r="E7" t="n">
         <v>6</v>
       </c>
-      <c r="E7" t="n">
+      <c r="F7" t="n">
+        <v>0.004504606958509978</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0.0007507678264183296</v>
+      </c>
+      <c r="H7" t="n">
         <v>711.7278994445765</v>
       </c>
-      <c r="F7" t="n">
+      <c r="I7" t="n">
         <v>150153.5652836659</v>
       </c>
-      <c r="G7" t="n">
+      <c r="J7" t="n">
         <v>3.595119805277692</v>
       </c>
-      <c r="H7" t="n">
+      <c r="K7" t="n">
         <v>-5.264656732975187e-05</v>
       </c>
-      <c r="I7" t="n">
+      <c r="L7" t="n">
         <v>0.007516730126563006</v>
       </c>
-      <c r="J7" t="n">
+      <c r="M7" t="n">
         <v>5.817587439357226e-06</v>
       </c>
-      <c r="K7" t="n">
+      <c r="N7" t="n">
         <v>0.5733905572095976</v>
       </c>
-      <c r="L7" t="n">
+      <c r="O7" t="n">
         <v>-0.01497636114489171</v>
       </c>
-      <c r="M7" t="n">
+      <c r="P7" t="n">
         <v>8.113133295376661</v>
       </c>
-      <c r="N7" t="n">
+      <c r="Q7" t="n">
         <v>-5.274815211736379e-05</v>
       </c>
-      <c r="O7" t="n">
+      <c r="R7" t="n">
         <v>0.01202133708507298</v>
       </c>
-      <c r="P7" t="n">
+      <c r="S7" t="n">
         <v>-1.276246011702428e-06</v>
       </c>
-      <c r="Q7" t="n">
+      <c r="T7" t="n">
         <v>0.4768655535130946</v>
       </c>
-      <c r="R7" t="n">
+      <c r="U7" t="n">
         <v>-0.01500508180210351</v>
       </c>
-      <c r="S7" t="n">
+      <c r="V7" t="n">
         <v>0.007516730126563006</v>
       </c>
-      <c r="T7" t="n">
+      <c r="W7" t="n">
         <v>-5.264656732975187e-05</v>
       </c>
-      <c r="U7" t="n">
+      <c r="X7" t="n">
         <v>-3.595119805277692</v>
       </c>
-      <c r="V7" t="n">
+      <c r="Y7" t="n">
         <v>-0.01497636114489171</v>
       </c>
-      <c r="W7" t="n">
+      <c r="Z7" t="n">
         <v>0.5733905572095976</v>
       </c>
-      <c r="X7" t="n">
+      <c r="AA7" t="n">
         <v>-5.817587439357226e-06</v>
       </c>
-      <c r="Y7" t="n">
+      <c r="AB7" t="n">
         <v>0.01202133708507298</v>
       </c>
-      <c r="Z7" t="n">
+      <c r="AC7" t="n">
         <v>-5.274815211736379e-05</v>
       </c>
-      <c r="AA7" t="n">
+      <c r="AD7" t="n">
         <v>-8.113133295376661</v>
       </c>
-      <c r="AB7" t="n">
+      <c r="AE7" t="n">
         <v>-0.01500508180210351</v>
       </c>
-      <c r="AC7" t="n">
+      <c r="AF7" t="n">
         <v>0.4768655535130946</v>
       </c>
-      <c r="AD7" t="n">
+      <c r="AG7" t="n">
         <v>1.276246011702428e-06</v>
       </c>
-      <c r="AE7" t="n">
+      <c r="AH7" t="n">
         <v>-711.7278994445767</v>
       </c>
-      <c r="AF7" t="n">
+      <c r="AI7" t="n">
         <v>-0.003335535075520275</v>
       </c>
-      <c r="AG7" t="n">
+      <c r="AJ7" t="n">
         <v>337.2538056229537</v>
       </c>
-      <c r="AH7" t="n">
+      <c r="AK7" t="n">
         <v>8.174340898744331e-05</v>
       </c>
-      <c r="AI7" t="n">
+      <c r="AL7" t="n">
         <v>-940.3329141334489</v>
       </c>
-      <c r="AJ7" t="n">
+      <c r="AM7" t="n">
         <v>-0.01525604198034497</v>
       </c>
-      <c r="AK7" t="n">
+      <c r="AN7" t="n">
         <v>711.7278994445767</v>
       </c>
-      <c r="AL7" t="n">
+      <c r="AO7" t="n">
         <v>0.003335535075520275</v>
       </c>
-      <c r="AM7" t="n">
+      <c r="AP7" t="n">
         <v>-337.2538056229537</v>
       </c>
-      <c r="AN7" t="n">
+      <c r="AQ7" t="n">
         <v>-8.174340898744331e-05</v>
       </c>
-      <c r="AO7" t="n">
+      <c r="AR7" t="n">
         <v>-1083.189919604273</v>
       </c>
-      <c r="AP7" t="n">
+      <c r="AS7" t="n">
         <v>-0.004757168472776685</v>
       </c>
     </row>
@@ -3517,127 +4810,138 @@
       <c r="A8" t="n">
         <v>7</v>
       </c>
-      <c r="B8" t="n">
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
         <v>7</v>
       </c>
-      <c r="C8" t="n">
+      <c r="D8" t="n">
         <v>11</v>
       </c>
-      <c r="D8" t="n">
+      <c r="E8" t="n">
         <v>6</v>
       </c>
-      <c r="E8" t="n">
+      <c r="F8" t="n">
+        <v>-0.004504606958509985</v>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.0007507678264183309</v>
+      </c>
+      <c r="H8" t="n">
         <v>-711.7278994445777</v>
       </c>
-      <c r="F8" t="n">
+      <c r="I8" t="n">
         <v>-150153.5652836662</v>
       </c>
-      <c r="G8" t="n">
+      <c r="J8" t="n">
         <v>3.596176627224334</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="n">
         <v>5.264656733141418e-05</v>
       </c>
-      <c r="I8" t="n">
+      <c r="L8" t="n">
         <v>-0.007516730126563017</v>
       </c>
-      <c r="J8" t="n">
+      <c r="M8" t="n">
         <v>-5.817587439646455e-06</v>
       </c>
-      <c r="K8" t="n">
+      <c r="N8" t="n">
         <v>0.5737082536248554</v>
       </c>
-      <c r="L8" t="n">
+      <c r="O8" t="n">
         <v>0.04500689564371815</v>
       </c>
-      <c r="M8" t="n">
+      <c r="P8" t="n">
         <v>8.114175479580663</v>
       </c>
-      <c r="N8" t="n">
+      <c r="Q8" t="n">
         <v>5.274815212167277e-05</v>
       </c>
-      <c r="O8" t="n">
+      <c r="R8" t="n">
         <v>-0.012021337085073</v>
       </c>
-      <c r="P8" t="n">
+      <c r="S8" t="n">
         <v>1.27624601135778e-06</v>
       </c>
-      <c r="Q8" t="n">
+      <c r="T8" t="n">
         <v>0.4758775876426199</v>
       </c>
-      <c r="R8" t="n">
+      <c r="U8" t="n">
         <v>0.04505488004389391</v>
       </c>
-      <c r="S8" t="n">
+      <c r="V8" t="n">
         <v>-0.007516730126563017</v>
       </c>
-      <c r="T8" t="n">
+      <c r="W8" t="n">
         <v>5.264656733141418e-05</v>
       </c>
-      <c r="U8" t="n">
+      <c r="X8" t="n">
         <v>-3.596176627224334</v>
       </c>
-      <c r="V8" t="n">
+      <c r="Y8" t="n">
         <v>0.04500689564371815</v>
       </c>
-      <c r="W8" t="n">
+      <c r="Z8" t="n">
         <v>0.5737082536248554</v>
       </c>
-      <c r="X8" t="n">
+      <c r="AA8" t="n">
         <v>5.817587439646455e-06</v>
       </c>
-      <c r="Y8" t="n">
+      <c r="AB8" t="n">
         <v>-0.012021337085073</v>
       </c>
-      <c r="Z8" t="n">
+      <c r="AC8" t="n">
         <v>5.274815212167277e-05</v>
       </c>
-      <c r="AA8" t="n">
+      <c r="AD8" t="n">
         <v>-8.114175479580663</v>
       </c>
-      <c r="AB8" t="n">
+      <c r="AE8" t="n">
         <v>0.04505488004389391</v>
       </c>
-      <c r="AC8" t="n">
+      <c r="AF8" t="n">
         <v>0.4758775876426199</v>
       </c>
-      <c r="AD8" t="n">
+      <c r="AG8" t="n">
         <v>-1.27624601135778e-06</v>
       </c>
-      <c r="AE8" t="n">
+      <c r="AH8" t="n">
         <v>711.7278994445778</v>
       </c>
-      <c r="AF8" t="n">
+      <c r="AI8" t="n">
         <v>0.003335535075336502</v>
       </c>
-      <c r="AG8" t="n">
+      <c r="AJ8" t="n">
         <v>412.7461943766295</v>
       </c>
-      <c r="AH8" t="n">
+      <c r="AK8" t="n">
         <v>-0.0001365709851156582</v>
       </c>
-      <c r="AI8" t="n">
+      <c r="AL8" t="n">
         <v>-1015.843890303033</v>
       </c>
-      <c r="AJ8" t="n">
+      <c r="AM8" t="n">
         <v>0.01525604197975264</v>
       </c>
-      <c r="AK8" t="n">
+      <c r="AN8" t="n">
         <v>-711.7278994445778</v>
       </c>
-      <c r="AL8" t="n">
+      <c r="AO8" t="n">
         <v>-0.003335535075336502</v>
       </c>
-      <c r="AM8" t="n">
+      <c r="AP8" t="n">
         <v>-262.7461943766295</v>
       </c>
-      <c r="AN8" t="n">
+      <c r="AQ8" t="n">
         <v>0.0001365709851156582</v>
       </c>
-      <c r="AO8" t="n">
+      <c r="AR8" t="n">
         <v>-1010.633275956742</v>
       </c>
-      <c r="AP8" t="n">
+      <c r="AS8" t="n">
         <v>0.004757168472266371</v>
       </c>
     </row>
@@ -3645,127 +4949,138 @@
       <c r="A9" t="n">
         <v>8</v>
       </c>
-      <c r="B9" t="n">
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
         <v>8</v>
       </c>
-      <c r="C9" t="n">
+      <c r="D9" t="n">
         <v>12</v>
       </c>
-      <c r="D9" t="n">
+      <c r="E9" t="n">
         <v>6</v>
       </c>
-      <c r="E9" t="n">
+      <c r="F9" t="n">
+        <v>-0.004504606958510099</v>
+      </c>
+      <c r="G9" t="n">
+        <v>-0.0007507678264183498</v>
+      </c>
+      <c r="H9" t="n">
         <v>-711.7278994445957</v>
       </c>
-      <c r="F9" t="n">
+      <c r="I9" t="n">
         <v>-150153.56528367</v>
       </c>
-      <c r="G9" t="n">
+      <c r="J9" t="n">
         <v>3.596176627226205</v>
       </c>
-      <c r="H9" t="n">
+      <c r="K9" t="n">
         <v>-5.264656553496323e-05</v>
       </c>
-      <c r="I9" t="n">
+      <c r="L9" t="n">
         <v>-0.00751673012656329</v>
       </c>
-      <c r="J9" t="n">
+      <c r="M9" t="n">
         <v>5.817587130890855e-06</v>
       </c>
-      <c r="K9" t="n">
+      <c r="N9" t="n">
         <v>0.5737082536251945</v>
       </c>
-      <c r="L9" t="n">
+      <c r="O9" t="n">
         <v>-0.04500689564325982</v>
       </c>
-      <c r="M9" t="n">
+      <c r="P9" t="n">
         <v>8.114175479585626</v>
       </c>
-      <c r="N9" t="n">
+      <c r="Q9" t="n">
         <v>-5.27481476574951e-05</v>
       </c>
-      <c r="O9" t="n">
+      <c r="R9" t="n">
         <v>-0.01202133708507339</v>
       </c>
-      <c r="P9" t="n">
+      <c r="S9" t="n">
         <v>-1.276246312679776e-06</v>
       </c>
-      <c r="Q9" t="n">
+      <c r="T9" t="n">
         <v>0.475877587642983</v>
       </c>
-      <c r="R9" t="n">
+      <c r="U9" t="n">
         <v>-0.04505488004271615</v>
       </c>
-      <c r="S9" t="n">
+      <c r="V9" t="n">
         <v>-0.00751673012656329</v>
       </c>
-      <c r="T9" t="n">
+      <c r="W9" t="n">
         <v>-5.264656553496323e-05</v>
       </c>
-      <c r="U9" t="n">
+      <c r="X9" t="n">
         <v>-3.596176627226205</v>
       </c>
-      <c r="V9" t="n">
+      <c r="Y9" t="n">
         <v>-0.04500689564325982</v>
       </c>
-      <c r="W9" t="n">
+      <c r="Z9" t="n">
         <v>0.5737082536251945</v>
       </c>
-      <c r="X9" t="n">
+      <c r="AA9" t="n">
         <v>-5.817587130890855e-06</v>
       </c>
-      <c r="Y9" t="n">
+      <c r="AB9" t="n">
         <v>-0.01202133708507339</v>
       </c>
-      <c r="Z9" t="n">
+      <c r="AC9" t="n">
         <v>-5.27481476574951e-05</v>
       </c>
-      <c r="AA9" t="n">
+      <c r="AD9" t="n">
         <v>-8.114175479585626</v>
       </c>
-      <c r="AB9" t="n">
+      <c r="AE9" t="n">
         <v>-0.04505488004271615</v>
       </c>
-      <c r="AC9" t="n">
+      <c r="AF9" t="n">
         <v>0.475877587642983</v>
       </c>
-      <c r="AD9" t="n">
+      <c r="AG9" t="n">
         <v>1.276246312679776e-06</v>
       </c>
-      <c r="AE9" t="n">
+      <c r="AH9" t="n">
         <v>711.7278994445958</v>
       </c>
-      <c r="AF9" t="n">
+      <c r="AI9" t="n">
         <v>-0.003335535281918336</v>
       </c>
-      <c r="AG9" t="n">
+      <c r="AJ9" t="n">
         <v>412.7461943768724</v>
       </c>
-      <c r="AH9" t="n">
+      <c r="AK9" t="n">
         <v>0.0001365709830680184</v>
       </c>
-      <c r="AI9" t="n">
+      <c r="AL9" t="n">
         <v>-1015.843890303781</v>
       </c>
-      <c r="AJ9" t="n">
+      <c r="AM9" t="n">
         <v>-0.01525604259399728</v>
       </c>
-      <c r="AK9" t="n">
+      <c r="AN9" t="n">
         <v>-711.7278994445958</v>
       </c>
-      <c r="AL9" t="n">
+      <c r="AO9" t="n">
         <v>0.003335535281918336</v>
       </c>
-      <c r="AM9" t="n">
+      <c r="AP9" t="n">
         <v>-262.7461943768724</v>
       </c>
-      <c r="AN9" t="n">
+      <c r="AQ9" t="n">
         <v>-0.0001365709830680184</v>
       </c>
-      <c r="AO9" t="n">
+      <c r="AR9" t="n">
         <v>-1010.633275957454</v>
       </c>
-      <c r="AP9" t="n">
+      <c r="AS9" t="n">
         <v>-0.00475716909751274</v>
       </c>
     </row>
@@ -3773,127 +5088,138 @@
       <c r="A10" t="n">
         <v>9</v>
       </c>
-      <c r="B10" t="n">
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
         <v>9</v>
       </c>
-      <c r="C10" t="n">
+      <c r="D10" t="n">
         <v>13</v>
       </c>
-      <c r="D10" t="n">
+      <c r="E10" t="n">
         <v>6</v>
       </c>
-      <c r="E10" t="n">
+      <c r="F10" t="n">
+        <v>0.002010446251387233</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.0003350743752312055</v>
+      </c>
+      <c r="H10" t="n">
         <v>317.6505077191828</v>
       </c>
-      <c r="F10" t="n">
+      <c r="I10" t="n">
         <v>67014.8750462411</v>
       </c>
-      <c r="G10" t="n">
+      <c r="J10" t="n">
         <v>8.113133295381624</v>
       </c>
-      <c r="H10" t="n">
+      <c r="K10" t="n">
         <v>5.27481476618041e-05</v>
       </c>
-      <c r="I10" t="n">
+      <c r="L10" t="n">
         <v>0.01202133708507339</v>
       </c>
-      <c r="J10" t="n">
+      <c r="M10" t="n">
         <v>1.276246312356512e-06</v>
       </c>
-      <c r="K10" t="n">
+      <c r="N10" t="n">
         <v>0.4768655535134581</v>
       </c>
-      <c r="L10" t="n">
+      <c r="O10" t="n">
         <v>0.01500508180328185</v>
       </c>
-      <c r="M10" t="n">
+      <c r="P10" t="n">
         <v>11.24253477912758</v>
       </c>
-      <c r="N10" t="n">
+      <c r="Q10" t="n">
         <v>5.272740302799424e-05</v>
       </c>
-      <c r="O10" t="n">
+      <c r="R10" t="n">
         <v>0.01403178333646062</v>
       </c>
-      <c r="P10" t="n">
+      <c r="S10" t="n">
         <v>-2.886833036039658e-07</v>
       </c>
-      <c r="Q10" t="n">
+      <c r="T10" t="n">
         <v>0.2774101967681684</v>
       </c>
-      <c r="R10" t="n">
+      <c r="U10" t="n">
         <v>0.01500512856537014</v>
       </c>
-      <c r="S10" t="n">
+      <c r="V10" t="n">
         <v>0.01202133708507339</v>
       </c>
-      <c r="T10" t="n">
+      <c r="W10" t="n">
         <v>5.27481476618041e-05</v>
       </c>
-      <c r="U10" t="n">
+      <c r="X10" t="n">
         <v>-8.113133295381624</v>
       </c>
-      <c r="V10" t="n">
+      <c r="Y10" t="n">
         <v>0.01500508180328185</v>
       </c>
-      <c r="W10" t="n">
+      <c r="Z10" t="n">
         <v>0.4768655535134581</v>
       </c>
-      <c r="X10" t="n">
+      <c r="AA10" t="n">
         <v>-1.276246312356512e-06</v>
       </c>
-      <c r="Y10" t="n">
+      <c r="AB10" t="n">
         <v>0.01403178333646062</v>
       </c>
-      <c r="Z10" t="n">
+      <c r="AC10" t="n">
         <v>5.272740302799424e-05</v>
       </c>
-      <c r="AA10" t="n">
+      <c r="AD10" t="n">
         <v>-11.24253477912758</v>
       </c>
-      <c r="AB10" t="n">
+      <c r="AE10" t="n">
         <v>0.01500512856537014</v>
       </c>
-      <c r="AC10" t="n">
+      <c r="AF10" t="n">
         <v>0.2774101967681684</v>
       </c>
-      <c r="AD10" t="n">
+      <c r="AG10" t="n">
         <v>2.886833036039658e-07</v>
       </c>
-      <c r="AE10" t="n">
+      <c r="AH10" t="n">
         <v>-317.6505077191828</v>
       </c>
-      <c r="AF10" t="n">
+      <c r="AI10" t="n">
         <v>-0.000725679616803785</v>
       </c>
-      <c r="AG10" t="n">
+      <c r="AJ10" t="n">
         <v>213.7549774489315</v>
       </c>
-      <c r="AH10" t="n">
+      <c r="AK10" t="n">
         <v>-1.330920974471073e-07</v>
       </c>
-      <c r="AI10" t="n">
+      <c r="AL10" t="n">
         <v>-493.6679683552808</v>
       </c>
-      <c r="AJ10" t="n">
+      <c r="AM10" t="n">
         <v>-0.003335086766222121</v>
       </c>
-      <c r="AK10" t="n">
+      <c r="AN10" t="n">
         <v>317.6505077191828</v>
       </c>
-      <c r="AL10" t="n">
+      <c r="AO10" t="n">
         <v>0.000725679616803785</v>
       </c>
-      <c r="AM10" t="n">
+      <c r="AP10" t="n">
         <v>-213.7549774489315</v>
       </c>
-      <c r="AN10" t="n">
+      <c r="AQ10" t="n">
         <v>1.330920974471073e-07</v>
       </c>
-      <c r="AO10" t="n">
+      <c r="AR10" t="n">
         <v>-788.861896338309</v>
       </c>
-      <c r="AP10" t="n">
+      <c r="AS10" t="n">
         <v>-0.00101899093460061</v>
       </c>
     </row>
@@ -3901,127 +5227,138 @@
       <c r="A11" t="n">
         <v>10</v>
       </c>
-      <c r="B11" t="n">
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
         <v>10</v>
       </c>
-      <c r="C11" t="n">
+      <c r="D11" t="n">
         <v>14</v>
       </c>
-      <c r="D11" t="n">
+      <c r="E11" t="n">
         <v>6</v>
       </c>
-      <c r="E11" t="n">
+      <c r="F11" t="n">
+        <v>0.00201044625138745</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.0003350743752312416</v>
+      </c>
+      <c r="H11" t="n">
         <v>317.6505077192171</v>
       </c>
-      <c r="F11" t="n">
+      <c r="I11" t="n">
         <v>67014.87504624833</v>
       </c>
-      <c r="G11" t="n">
+      <c r="J11" t="n">
         <v>8.113133295376661</v>
       </c>
-      <c r="H11" t="n">
+      <c r="K11" t="n">
         <v>-5.274815211736379e-05</v>
       </c>
-      <c r="I11" t="n">
+      <c r="L11" t="n">
         <v>0.01202133708507298</v>
       </c>
-      <c r="J11" t="n">
+      <c r="M11" t="n">
         <v>-1.276246011702428e-06</v>
       </c>
-      <c r="K11" t="n">
+      <c r="N11" t="n">
         <v>0.4768655535130946</v>
       </c>
-      <c r="L11" t="n">
+      <c r="O11" t="n">
         <v>-0.01500508180210351</v>
       </c>
-      <c r="M11" t="n">
+      <c r="P11" t="n">
         <v>11.2425347791201</v>
       </c>
-      <c r="N11" t="n">
+      <c r="Q11" t="n">
         <v>-5.272740957680732e-05</v>
       </c>
-      <c r="O11" t="n">
+      <c r="R11" t="n">
         <v>0.01403178333646043</v>
       </c>
-      <c r="P11" t="n">
+      <c r="S11" t="n">
         <v>2.886834930193329e-07</v>
       </c>
-      <c r="Q11" t="n">
+      <c r="T11" t="n">
         <v>0.2774101967679769</v>
       </c>
-      <c r="R11" t="n">
+      <c r="U11" t="n">
         <v>-0.01500512856361739</v>
       </c>
-      <c r="S11" t="n">
+      <c r="V11" t="n">
         <v>0.01202133708507298</v>
       </c>
-      <c r="T11" t="n">
+      <c r="W11" t="n">
         <v>-5.274815211736379e-05</v>
       </c>
-      <c r="U11" t="n">
+      <c r="X11" t="n">
         <v>-8.113133295376661</v>
       </c>
-      <c r="V11" t="n">
+      <c r="Y11" t="n">
         <v>-0.01500508180210351</v>
       </c>
-      <c r="W11" t="n">
+      <c r="Z11" t="n">
         <v>0.4768655535130946</v>
       </c>
-      <c r="X11" t="n">
+      <c r="AA11" t="n">
         <v>1.276246011702428e-06</v>
       </c>
-      <c r="Y11" t="n">
+      <c r="AB11" t="n">
         <v>0.01403178333646043</v>
       </c>
-      <c r="Z11" t="n">
+      <c r="AC11" t="n">
         <v>-5.272740957680732e-05</v>
       </c>
-      <c r="AA11" t="n">
+      <c r="AD11" t="n">
         <v>-11.2425347791201</v>
       </c>
-      <c r="AB11" t="n">
+      <c r="AE11" t="n">
         <v>-0.01500512856361739</v>
       </c>
-      <c r="AC11" t="n">
+      <c r="AF11" t="n">
         <v>0.2774101967679769</v>
       </c>
-      <c r="AD11" t="n">
+      <c r="AG11" t="n">
         <v>-2.886834930193329e-07</v>
       </c>
-      <c r="AE11" t="n">
+      <c r="AH11" t="n">
         <v>-317.6505077192171</v>
       </c>
-      <c r="AF11" t="n">
+      <c r="AI11" t="n">
         <v>0.0007256797704882252</v>
       </c>
-      <c r="AG11" t="n">
+      <c r="AJ11" t="n">
         <v>213.7549774487221</v>
       </c>
-      <c r="AH11" t="n">
+      <c r="AK11" t="n">
         <v>1.330904625743146e-07</v>
       </c>
-      <c r="AI11" t="n">
+      <c r="AL11" t="n">
         <v>-493.6679683547802</v>
       </c>
-      <c r="AJ11" t="n">
+      <c r="AM11" t="n">
         <v>0.003335087144958782</v>
       </c>
-      <c r="AK11" t="n">
+      <c r="AN11" t="n">
         <v>317.6505077192171</v>
       </c>
-      <c r="AL11" t="n">
+      <c r="AO11" t="n">
         <v>-0.0007256797704882252</v>
       </c>
-      <c r="AM11" t="n">
+      <c r="AP11" t="n">
         <v>-213.7549774487221</v>
       </c>
-      <c r="AN11" t="n">
+      <c r="AQ11" t="n">
         <v>-1.330904625743146e-07</v>
       </c>
-      <c r="AO11" t="n">
+      <c r="AR11" t="n">
         <v>-788.8618963375543</v>
       </c>
-      <c r="AP11" t="n">
+      <c r="AS11" t="n">
         <v>0.001018991477970577</v>
       </c>
     </row>
@@ -4029,127 +5366,138 @@
       <c r="A12" t="n">
         <v>11</v>
       </c>
-      <c r="B12" t="n">
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
         <v>11</v>
       </c>
-      <c r="C12" t="n">
+      <c r="D12" t="n">
         <v>15</v>
       </c>
-      <c r="D12" t="n">
+      <c r="E12" t="n">
         <v>6</v>
       </c>
-      <c r="E12" t="n">
+      <c r="F12" t="n">
+        <v>-0.002010446251387455</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.0003350743752312425</v>
+      </c>
+      <c r="H12" t="n">
         <v>-317.6505077192179</v>
       </c>
-      <c r="F12" t="n">
+      <c r="I12" t="n">
         <v>-67014.8750462485</v>
       </c>
-      <c r="G12" t="n">
+      <c r="J12" t="n">
         <v>8.114175479580663</v>
       </c>
-      <c r="H12" t="n">
+      <c r="K12" t="n">
         <v>5.274815212167277e-05</v>
       </c>
-      <c r="I12" t="n">
+      <c r="L12" t="n">
         <v>-0.012021337085073</v>
       </c>
-      <c r="J12" t="n">
+      <c r="M12" t="n">
         <v>1.27624601135778e-06</v>
       </c>
-      <c r="K12" t="n">
+      <c r="N12" t="n">
         <v>0.4758775876426199</v>
       </c>
-      <c r="L12" t="n">
+      <c r="O12" t="n">
         <v>0.04505488004389391</v>
       </c>
-      <c r="M12" t="n">
+      <c r="P12" t="n">
         <v>11.24364880861739</v>
       </c>
-      <c r="N12" t="n">
+      <c r="Q12" t="n">
         <v>5.272740958393851e-05</v>
       </c>
-      <c r="O12" t="n">
+      <c r="R12" t="n">
         <v>-0.01403178333646046</v>
       </c>
-      <c r="P12" t="n">
+      <c r="S12" t="n">
         <v>-2.886834933623841e-07</v>
       </c>
-      <c r="Q12" t="n">
+      <c r="T12" t="n">
         <v>0.2818139420127958</v>
       </c>
-      <c r="R12" t="n">
+      <c r="U12" t="n">
         <v>0.04505493137084957</v>
       </c>
-      <c r="S12" t="n">
+      <c r="V12" t="n">
         <v>-0.012021337085073</v>
       </c>
-      <c r="T12" t="n">
+      <c r="W12" t="n">
         <v>5.274815212167277e-05</v>
       </c>
-      <c r="U12" t="n">
+      <c r="X12" t="n">
         <v>-8.114175479580663</v>
       </c>
-      <c r="V12" t="n">
+      <c r="Y12" t="n">
         <v>0.04505488004389391</v>
       </c>
-      <c r="W12" t="n">
+      <c r="Z12" t="n">
         <v>0.4758775876426199</v>
       </c>
-      <c r="X12" t="n">
+      <c r="AA12" t="n">
         <v>-1.27624601135778e-06</v>
       </c>
-      <c r="Y12" t="n">
+      <c r="AB12" t="n">
         <v>-0.01403178333646046</v>
       </c>
-      <c r="Z12" t="n">
+      <c r="AC12" t="n">
         <v>5.272740958393851e-05</v>
       </c>
-      <c r="AA12" t="n">
+      <c r="AD12" t="n">
         <v>-11.24364880861739</v>
       </c>
-      <c r="AB12" t="n">
+      <c r="AE12" t="n">
         <v>0.04505493137084957</v>
       </c>
-      <c r="AC12" t="n">
+      <c r="AF12" t="n">
         <v>0.2818139420127958</v>
       </c>
-      <c r="AD12" t="n">
+      <c r="AG12" t="n">
         <v>2.886834933623841e-07</v>
       </c>
-      <c r="AE12" t="n">
+      <c r="AH12" t="n">
         <v>317.6505077192182</v>
       </c>
-      <c r="AF12" t="n">
+      <c r="AI12" t="n">
         <v>-0.0007256797706754747</v>
       </c>
-      <c r="AG12" t="n">
+      <c r="AJ12" t="n">
         <v>286.2450225507185</v>
       </c>
-      <c r="AH12" t="n">
+      <c r="AK12" t="n">
         <v>-1.460844122613825e-07</v>
       </c>
-      <c r="AI12" t="n">
+      <c r="AL12" t="n">
         <v>-565.1279698860859</v>
       </c>
-      <c r="AJ12" t="n">
+      <c r="AM12" t="n">
         <v>-0.003335087145519354</v>
       </c>
-      <c r="AK12" t="n">
+      <c r="AN12" t="n">
         <v>-317.6505077192182</v>
       </c>
-      <c r="AL12" t="n">
+      <c r="AO12" t="n">
         <v>0.0007256797706754747</v>
       </c>
-      <c r="AM12" t="n">
+      <c r="AP12" t="n">
         <v>-136.2450225507185</v>
       </c>
-      <c r="AN12" t="n">
+      <c r="AQ12" t="n">
         <v>1.460844122613825e-07</v>
       </c>
-      <c r="AO12" t="n">
+      <c r="AR12" t="n">
         <v>-702.342165418225</v>
       </c>
-      <c r="AP12" t="n">
+      <c r="AS12" t="n">
         <v>-0.001018991478533501</v>
       </c>
     </row>
@@ -4157,127 +5505,138 @@
       <c r="A13" t="n">
         <v>12</v>
       </c>
-      <c r="B13" t="n">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
         <v>12</v>
       </c>
-      <c r="C13" t="n">
+      <c r="D13" t="n">
         <v>16</v>
       </c>
-      <c r="D13" t="n">
+      <c r="E13" t="n">
         <v>6</v>
       </c>
-      <c r="E13" t="n">
+      <c r="F13" t="n">
+        <v>-0.002010446251387236</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.0003350743752312061</v>
+      </c>
+      <c r="H13" t="n">
         <v>-317.6505077191833</v>
       </c>
-      <c r="F13" t="n">
+      <c r="I13" t="n">
         <v>-67014.87504624121</v>
       </c>
-      <c r="G13" t="n">
+      <c r="J13" t="n">
         <v>8.114175479585626</v>
       </c>
-      <c r="H13" t="n">
+      <c r="K13" t="n">
         <v>-5.27481476574951e-05</v>
       </c>
-      <c r="I13" t="n">
+      <c r="L13" t="n">
         <v>-0.01202133708507339</v>
       </c>
-      <c r="J13" t="n">
+      <c r="M13" t="n">
         <v>-1.276246312679776e-06</v>
       </c>
-      <c r="K13" t="n">
+      <c r="N13" t="n">
         <v>0.475877587642983</v>
       </c>
-      <c r="L13" t="n">
+      <c r="O13" t="n">
         <v>-0.04505488004271615</v>
       </c>
-      <c r="M13" t="n">
+      <c r="P13" t="n">
         <v>11.24364880862486</v>
       </c>
-      <c r="N13" t="n">
+      <c r="Q13" t="n">
         <v>-5.272740302085454e-05</v>
       </c>
-      <c r="O13" t="n">
+      <c r="R13" t="n">
         <v>-0.01403178333646063</v>
       </c>
-      <c r="P13" t="n">
+      <c r="S13" t="n">
         <v>2.886833031477993e-07</v>
       </c>
-      <c r="Q13" t="n">
+      <c r="T13" t="n">
         <v>0.2818139420129872</v>
       </c>
-      <c r="R13" t="n">
+      <c r="U13" t="n">
         <v>-0.04505493136909523</v>
       </c>
-      <c r="S13" t="n">
+      <c r="V13" t="n">
         <v>-0.01202133708507339</v>
       </c>
-      <c r="T13" t="n">
+      <c r="W13" t="n">
         <v>-5.27481476574951e-05</v>
       </c>
-      <c r="U13" t="n">
+      <c r="X13" t="n">
         <v>-8.114175479585626</v>
       </c>
-      <c r="V13" t="n">
+      <c r="Y13" t="n">
         <v>-0.04505488004271615</v>
       </c>
-      <c r="W13" t="n">
+      <c r="Z13" t="n">
         <v>0.475877587642983</v>
       </c>
-      <c r="X13" t="n">
+      <c r="AA13" t="n">
         <v>1.276246312679776e-06</v>
       </c>
-      <c r="Y13" t="n">
+      <c r="AB13" t="n">
         <v>-0.01403178333646063</v>
       </c>
-      <c r="Z13" t="n">
+      <c r="AC13" t="n">
         <v>-5.272740302085454e-05</v>
       </c>
-      <c r="AA13" t="n">
+      <c r="AD13" t="n">
         <v>-11.24364880862486</v>
       </c>
-      <c r="AB13" t="n">
+      <c r="AE13" t="n">
         <v>-0.04505493136909523</v>
       </c>
-      <c r="AC13" t="n">
+      <c r="AF13" t="n">
         <v>0.2818139420129872</v>
       </c>
-      <c r="AD13" t="n">
+      <c r="AG13" t="n">
         <v>-2.886833031477993e-07</v>
       </c>
-      <c r="AE13" t="n">
+      <c r="AH13" t="n">
         <v>317.6505077191835</v>
       </c>
-      <c r="AF13" t="n">
+      <c r="AI13" t="n">
         <v>0.0007256796166823266</v>
       </c>
-      <c r="AG13" t="n">
+      <c r="AJ13" t="n">
         <v>286.245022550927</v>
       </c>
-      <c r="AH13" t="n">
+      <c r="AK13" t="n">
         <v>1.460827712407298e-07</v>
       </c>
-      <c r="AI13" t="n">
+      <c r="AL13" t="n">
         <v>-565.127969886584</v>
       </c>
-      <c r="AJ13" t="n">
+      <c r="AM13" t="n">
         <v>0.003335086765759374</v>
       </c>
-      <c r="AK13" t="n">
+      <c r="AN13" t="n">
         <v>-317.6505077191835</v>
       </c>
-      <c r="AL13" t="n">
+      <c r="AO13" t="n">
         <v>-0.0007256796166823266</v>
       </c>
-      <c r="AM13" t="n">
+      <c r="AP13" t="n">
         <v>-136.245022550927</v>
       </c>
-      <c r="AN13" t="n">
+      <c r="AQ13" t="n">
         <v>-1.460827712407298e-07</v>
       </c>
-      <c r="AO13" t="n">
+      <c r="AR13" t="n">
         <v>-702.3421654189774</v>
       </c>
-      <c r="AP13" t="n">
+      <c r="AS13" t="n">
         <v>0.001018990934334565</v>
       </c>
     </row>
@@ -4285,127 +5644,138 @@
       <c r="A14" t="n">
         <v>13</v>
       </c>
-      <c r="B14" t="n">
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
         <v>13</v>
       </c>
-      <c r="C14" t="n">
+      <c r="D14" t="n">
         <v>17</v>
       </c>
-      <c r="D14" t="n">
+      <c r="E14" t="n">
         <v>6</v>
       </c>
-      <c r="E14" t="n">
+      <c r="F14" t="n">
+        <v>0.0005556571193576412</v>
+      </c>
+      <c r="G14" t="n">
+        <v>9.260951989294019e-05</v>
+      </c>
+      <c r="H14" t="n">
         <v>87.79382485850731</v>
       </c>
-      <c r="F14" t="n">
+      <c r="I14" t="n">
         <v>18521.90397858804</v>
       </c>
-      <c r="G14" t="n">
+      <c r="J14" t="n">
         <v>11.24253477912758</v>
       </c>
-      <c r="H14" t="n">
+      <c r="K14" t="n">
         <v>5.272740302799424e-05</v>
       </c>
-      <c r="I14" t="n">
+      <c r="L14" t="n">
         <v>0.01403178333646062</v>
       </c>
-      <c r="J14" t="n">
+      <c r="M14" t="n">
         <v>-2.886833036039658e-07</v>
       </c>
-      <c r="K14" t="n">
+      <c r="N14" t="n">
         <v>0.2774101967681684</v>
       </c>
-      <c r="L14" t="n">
+      <c r="O14" t="n">
         <v>0.01500512856537014</v>
       </c>
-      <c r="M14" t="n">
+      <c r="P14" t="n">
         <v>12.7636275507655</v>
       </c>
-      <c r="N14" t="n">
+      <c r="Q14" t="n">
         <v>5.273160743815383e-05</v>
       </c>
-      <c r="O14" t="n">
+      <c r="R14" t="n">
         <v>0.01458744045581826</v>
       </c>
-      <c r="P14" t="n">
+      <c r="S14" t="n">
         <v>1.041020896839185e-07</v>
       </c>
-      <c r="Q14" t="n">
+      <c r="T14" t="n">
         <v>0.1191579135705716</v>
       </c>
-      <c r="R14" t="n">
+      <c r="U14" t="n">
         <v>0.01500512783931789</v>
       </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
         <v>0.01403178333646062</v>
       </c>
-      <c r="T14" t="n">
+      <c r="W14" t="n">
         <v>5.272740302799424e-05</v>
       </c>
-      <c r="U14" t="n">
+      <c r="X14" t="n">
         <v>-11.24253477912758</v>
       </c>
-      <c r="V14" t="n">
+      <c r="Y14" t="n">
         <v>0.01500512856537014</v>
       </c>
-      <c r="W14" t="n">
+      <c r="Z14" t="n">
         <v>0.2774101967681684</v>
       </c>
-      <c r="X14" t="n">
+      <c r="AA14" t="n">
         <v>2.886833036039658e-07</v>
       </c>
-      <c r="Y14" t="n">
+      <c r="AB14" t="n">
         <v>0.01458744045581826</v>
       </c>
-      <c r="Z14" t="n">
+      <c r="AC14" t="n">
         <v>5.273160743815383e-05</v>
       </c>
-      <c r="AA14" t="n">
+      <c r="AD14" t="n">
         <v>-12.7636275507655</v>
       </c>
-      <c r="AB14" t="n">
+      <c r="AE14" t="n">
         <v>0.01500512783931789</v>
       </c>
-      <c r="AC14" t="n">
+      <c r="AF14" t="n">
         <v>0.1191579135705716</v>
       </c>
-      <c r="AD14" t="n">
+      <c r="AG14" t="n">
         <v>-1.041020896839185e-07</v>
       </c>
-      <c r="AE14" t="n">
+      <c r="AH14" t="n">
         <v>-87.79382485850738</v>
       </c>
-      <c r="AF14" t="n">
+      <c r="AI14" t="n">
         <v>0.000135553010461472</v>
       </c>
-      <c r="AG14" t="n">
+      <c r="AJ14" t="n">
         <v>81.74248202001982</v>
       </c>
-      <c r="AH14" t="n">
+      <c r="AK14" t="n">
         <v>2.066456408766904e-09</v>
       </c>
-      <c r="AI14" t="n">
+      <c r="AL14" t="n">
         <v>-128.1207564938366</v>
       </c>
-      <c r="AJ14" t="n">
+      <c r="AM14" t="n">
         <v>0.0006973202224174468</v>
       </c>
-      <c r="AK14" t="n">
+      <c r="AN14" t="n">
         <v>87.79382485850738</v>
       </c>
-      <c r="AL14" t="n">
+      <c r="AO14" t="n">
         <v>-0.000135553010461472</v>
       </c>
-      <c r="AM14" t="n">
+      <c r="AP14" t="n">
         <v>-81.74248202001982</v>
       </c>
-      <c r="AN14" t="n">
+      <c r="AQ14" t="n">
         <v>-2.066456408766904e-09</v>
       </c>
-      <c r="AO14" t="n">
+      <c r="AR14" t="n">
         <v>-362.3341356262787</v>
       </c>
-      <c r="AP14" t="n">
+      <c r="AS14" t="n">
         <v>0.0001159978403513784</v>
       </c>
     </row>
@@ -4413,127 +5783,138 @@
       <c r="A15" t="n">
         <v>14</v>
       </c>
-      <c r="B15" t="n">
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
         <v>14</v>
       </c>
-      <c r="C15" t="n">
+      <c r="D15" t="n">
         <v>18</v>
       </c>
-      <c r="D15" t="n">
+      <c r="E15" t="n">
         <v>6</v>
       </c>
-      <c r="E15" t="n">
+      <c r="F15" t="n">
+        <v>0.0005556571193578615</v>
+      </c>
+      <c r="G15" t="n">
+        <v>9.260951989297692e-05</v>
+      </c>
+      <c r="H15" t="n">
         <v>87.79382485854211</v>
       </c>
-      <c r="F15" t="n">
+      <c r="I15" t="n">
         <v>18521.90397859538</v>
       </c>
-      <c r="G15" t="n">
+      <c r="J15" t="n">
         <v>11.2425347791201</v>
       </c>
-      <c r="H15" t="n">
+      <c r="K15" t="n">
         <v>-5.272740957680732e-05</v>
       </c>
-      <c r="I15" t="n">
+      <c r="L15" t="n">
         <v>0.01403178333646043</v>
       </c>
-      <c r="J15" t="n">
+      <c r="M15" t="n">
         <v>2.886834930193329e-07</v>
       </c>
-      <c r="K15" t="n">
+      <c r="N15" t="n">
         <v>0.2774101967679769</v>
       </c>
-      <c r="L15" t="n">
+      <c r="O15" t="n">
         <v>-0.01500512856361739</v>
       </c>
-      <c r="M15" t="n">
+      <c r="P15" t="n">
         <v>12.76362755075735</v>
       </c>
-      <c r="N15" t="n">
+      <c r="Q15" t="n">
         <v>-5.273161501681668e-05</v>
       </c>
-      <c r="O15" t="n">
+      <c r="R15" t="n">
         <v>0.01458744045581829</v>
       </c>
-      <c r="P15" t="n">
+      <c r="S15" t="n">
         <v>-1.041020131429611e-07</v>
       </c>
-      <c r="Q15" t="n">
+      <c r="T15" t="n">
         <v>0.1191579135705384</v>
       </c>
-      <c r="R15" t="n">
+      <c r="U15" t="n">
         <v>-0.01500512783735091</v>
       </c>
-      <c r="S15" t="n">
+      <c r="V15" t="n">
         <v>0.01403178333646043</v>
       </c>
-      <c r="T15" t="n">
+      <c r="W15" t="n">
         <v>-5.272740957680732e-05</v>
       </c>
-      <c r="U15" t="n">
+      <c r="X15" t="n">
         <v>-11.2425347791201</v>
       </c>
-      <c r="V15" t="n">
+      <c r="Y15" t="n">
         <v>-0.01500512856361739</v>
       </c>
-      <c r="W15" t="n">
+      <c r="Z15" t="n">
         <v>0.2774101967679769</v>
       </c>
-      <c r="X15" t="n">
+      <c r="AA15" t="n">
         <v>-2.886834930193329e-07</v>
       </c>
-      <c r="Y15" t="n">
+      <c r="AB15" t="n">
         <v>0.01458744045581829</v>
       </c>
-      <c r="Z15" t="n">
+      <c r="AC15" t="n">
         <v>-5.273161501681668e-05</v>
       </c>
-      <c r="AA15" t="n">
+      <c r="AD15" t="n">
         <v>-12.76362755075735</v>
       </c>
-      <c r="AB15" t="n">
+      <c r="AE15" t="n">
         <v>-0.01500512783735091</v>
       </c>
-      <c r="AC15" t="n">
+      <c r="AF15" t="n">
         <v>0.1191579135705384</v>
       </c>
-      <c r="AD15" t="n">
+      <c r="AG15" t="n">
         <v>1.041020131429611e-07</v>
       </c>
-      <c r="AE15" t="n">
+      <c r="AH15" t="n">
         <v>-87.79382485854194</v>
       </c>
-      <c r="AF15" t="n">
+      <c r="AI15" t="n">
         <v>-0.0001355529532395382</v>
       </c>
-      <c r="AG15" t="n">
+      <c r="AJ15" t="n">
         <v>81.74248202002072</v>
       </c>
-      <c r="AH15" t="n">
+      <c r="AK15" t="n">
         <v>-2.06706612937424e-09</v>
       </c>
-      <c r="AI15" t="n">
+      <c r="AL15" t="n">
         <v>-128.1207564939566</v>
       </c>
-      <c r="AJ15" t="n">
+      <c r="AM15" t="n">
         <v>-0.0006973201342787144</v>
       </c>
-      <c r="AK15" t="n">
+      <c r="AN15" t="n">
         <v>87.79382485854194</v>
       </c>
-      <c r="AL15" t="n">
+      <c r="AO15" t="n">
         <v>0.0001355529532395382</v>
       </c>
-      <c r="AM15" t="n">
+      <c r="AP15" t="n">
         <v>-81.74248202002072</v>
       </c>
-      <c r="AN15" t="n">
+      <c r="AQ15" t="n">
         <v>2.06706612937424e-09</v>
       </c>
-      <c r="AO15" t="n">
+      <c r="AR15" t="n">
         <v>-362.3341356261658</v>
       </c>
-      <c r="AP15" t="n">
+      <c r="AS15" t="n">
         <v>-0.0001159975851585185</v>
       </c>
     </row>
@@ -4541,127 +5922,138 @@
       <c r="A16" t="n">
         <v>15</v>
       </c>
-      <c r="B16" t="n">
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
         <v>15</v>
       </c>
-      <c r="C16" t="n">
+      <c r="D16" t="n">
         <v>19</v>
       </c>
-      <c r="D16" t="n">
+      <c r="E16" t="n">
         <v>6</v>
       </c>
-      <c r="E16" t="n">
+      <c r="F16" t="n">
+        <v>-0.0005556571193578649</v>
+      </c>
+      <c r="G16" t="n">
+        <v>-9.260951989297748e-05</v>
+      </c>
+      <c r="H16" t="n">
         <v>-87.79382485854266</v>
       </c>
-      <c r="F16" t="n">
+      <c r="I16" t="n">
         <v>-18521.9039785955</v>
       </c>
-      <c r="G16" t="n">
+      <c r="J16" t="n">
         <v>11.24364880861739</v>
       </c>
-      <c r="H16" t="n">
+      <c r="K16" t="n">
         <v>5.272740958393851e-05</v>
       </c>
-      <c r="I16" t="n">
+      <c r="L16" t="n">
         <v>-0.01403178333646046</v>
       </c>
-      <c r="J16" t="n">
+      <c r="M16" t="n">
         <v>-2.886834933623841e-07</v>
       </c>
-      <c r="K16" t="n">
+      <c r="N16" t="n">
         <v>0.2818139420127958</v>
       </c>
-      <c r="L16" t="n">
+      <c r="O16" t="n">
         <v>0.04505493137084957</v>
       </c>
-      <c r="M16" t="n">
+      <c r="P16" t="n">
         <v>12.76431736073221</v>
       </c>
-      <c r="N16" t="n">
+      <c r="Q16" t="n">
         <v>5.273161502770671e-05</v>
       </c>
-      <c r="O16" t="n">
+      <c r="R16" t="n">
         <v>-0.01458744045581832</v>
       </c>
-      <c r="P16" t="n">
+      <c r="S16" t="n">
         <v>1.041020126456332e-07</v>
       </c>
-      <c r="Q16" t="n">
+      <c r="T16" t="n">
         <v>0.09905190241355175</v>
       </c>
-      <c r="R16" t="n">
+      <c r="U16" t="n">
         <v>0.04505493222254756</v>
       </c>
-      <c r="S16" t="n">
+      <c r="V16" t="n">
         <v>-0.01403178333646046</v>
       </c>
-      <c r="T16" t="n">
+      <c r="W16" t="n">
         <v>5.272740958393851e-05</v>
       </c>
-      <c r="U16" t="n">
+      <c r="X16" t="n">
         <v>-11.24364880861739</v>
       </c>
-      <c r="V16" t="n">
+      <c r="Y16" t="n">
         <v>0.04505493137084957</v>
       </c>
-      <c r="W16" t="n">
+      <c r="Z16" t="n">
         <v>0.2818139420127958</v>
       </c>
-      <c r="X16" t="n">
+      <c r="AA16" t="n">
         <v>2.886834933623841e-07</v>
       </c>
-      <c r="Y16" t="n">
+      <c r="AB16" t="n">
         <v>-0.01458744045581832</v>
       </c>
-      <c r="Z16" t="n">
+      <c r="AC16" t="n">
         <v>5.273161502770671e-05</v>
       </c>
-      <c r="AA16" t="n">
+      <c r="AD16" t="n">
         <v>-12.76431736073221</v>
       </c>
-      <c r="AB16" t="n">
+      <c r="AE16" t="n">
         <v>0.04505493222254756</v>
       </c>
-      <c r="AC16" t="n">
+      <c r="AF16" t="n">
         <v>0.09905190241355175</v>
       </c>
-      <c r="AD16" t="n">
+      <c r="AG16" t="n">
         <v>-1.041020126456332e-07</v>
       </c>
-      <c r="AE16" t="n">
+      <c r="AH16" t="n">
         <v>87.79382485854239</v>
       </c>
-      <c r="AF16" t="n">
+      <c r="AI16" t="n">
         <v>0.0001355529529342408</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AJ16" t="n">
         <v>168.2575179794908</v>
       </c>
-      <c r="AH16" t="n">
+      <c r="AK16" t="n">
         <v>-2.424063477723948e-09</v>
       </c>
-      <c r="AI16" t="n">
+      <c r="AL16" t="n">
         <v>-219.5286446350328</v>
       </c>
-      <c r="AJ16" t="n">
+      <c r="AM16" t="n">
         <v>0.0006973201332486564</v>
       </c>
-      <c r="AK16" t="n">
+      <c r="AN16" t="n">
         <v>-87.79382485854239</v>
       </c>
-      <c r="AL16" t="n">
+      <c r="AO16" t="n">
         <v>-0.0001355529529342408</v>
       </c>
-      <c r="AM16" t="n">
+      <c r="AP16" t="n">
         <v>-18.25751797949079</v>
       </c>
-      <c r="AN16" t="n">
+      <c r="AQ16" t="n">
         <v>2.424063477723948e-09</v>
       </c>
-      <c r="AO16" t="n">
+      <c r="AR16" t="n">
         <v>-340.0164632419128</v>
       </c>
-      <c r="AP16" t="n">
+      <c r="AS16" t="n">
         <v>0.0001159975843567848</v>
       </c>
     </row>
@@ -4669,127 +6061,138 @@
       <c r="A17" t="n">
         <v>16</v>
       </c>
-      <c r="B17" t="n">
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
         <v>16</v>
       </c>
-      <c r="C17" t="n">
+      <c r="D17" t="n">
         <v>20</v>
       </c>
-      <c r="D17" t="n">
+      <c r="E17" t="n">
         <v>6</v>
       </c>
-      <c r="E17" t="n">
+      <c r="F17" t="n">
+        <v>-0.0005556571193576377</v>
+      </c>
+      <c r="G17" t="n">
+        <v>-9.260951989293962e-05</v>
+      </c>
+      <c r="H17" t="n">
         <v>-87.79382485850675</v>
       </c>
-      <c r="F17" t="n">
+      <c r="I17" t="n">
         <v>-18521.90397858792</v>
       </c>
-      <c r="G17" t="n">
+      <c r="J17" t="n">
         <v>11.24364880862486</v>
       </c>
-      <c r="H17" t="n">
+      <c r="K17" t="n">
         <v>-5.272740302085454e-05</v>
       </c>
-      <c r="I17" t="n">
+      <c r="L17" t="n">
         <v>-0.01403178333646063</v>
       </c>
-      <c r="J17" t="n">
+      <c r="M17" t="n">
         <v>2.886833031477993e-07</v>
       </c>
-      <c r="K17" t="n">
+      <c r="N17" t="n">
         <v>0.2818139420129872</v>
       </c>
-      <c r="L17" t="n">
+      <c r="O17" t="n">
         <v>-0.04505493136909523</v>
       </c>
-      <c r="M17" t="n">
+      <c r="P17" t="n">
         <v>12.76431736074036</v>
       </c>
-      <c r="N17" t="n">
+      <c r="Q17" t="n">
         <v>-5.273160742726827e-05</v>
       </c>
-      <c r="O17" t="n">
+      <c r="R17" t="n">
         <v>-0.01458744045581826</v>
       </c>
-      <c r="P17" t="n">
+      <c r="S17" t="n">
         <v>-1.041020899760041e-07</v>
       </c>
-      <c r="Q17" t="n">
+      <c r="T17" t="n">
         <v>0.09905190241358573</v>
       </c>
-      <c r="R17" t="n">
+      <c r="U17" t="n">
         <v>-0.04505493222058038</v>
       </c>
-      <c r="S17" t="n">
+      <c r="V17" t="n">
         <v>-0.01403178333646063</v>
       </c>
-      <c r="T17" t="n">
+      <c r="W17" t="n">
         <v>-5.272740302085454e-05</v>
       </c>
-      <c r="U17" t="n">
+      <c r="X17" t="n">
         <v>-11.24364880862486</v>
       </c>
-      <c r="V17" t="n">
+      <c r="Y17" t="n">
         <v>-0.04505493136909523</v>
       </c>
-      <c r="W17" t="n">
+      <c r="Z17" t="n">
         <v>0.2818139420129872</v>
       </c>
-      <c r="X17" t="n">
+      <c r="AA17" t="n">
         <v>-2.886833031477993e-07</v>
       </c>
-      <c r="Y17" t="n">
+      <c r="AB17" t="n">
         <v>-0.01458744045581826</v>
       </c>
-      <c r="Z17" t="n">
+      <c r="AC17" t="n">
         <v>-5.273160742726827e-05</v>
       </c>
-      <c r="AA17" t="n">
+      <c r="AD17" t="n">
         <v>-12.76431736074036</v>
       </c>
-      <c r="AB17" t="n">
+      <c r="AE17" t="n">
         <v>-0.04505493222058038</v>
       </c>
-      <c r="AC17" t="n">
+      <c r="AF17" t="n">
         <v>0.09905190241358573</v>
       </c>
-      <c r="AD17" t="n">
+      <c r="AG17" t="n">
         <v>1.041020899760041e-07</v>
       </c>
-      <c r="AE17" t="n">
+      <c r="AH17" t="n">
         <v>87.79382485850692</v>
       </c>
-      <c r="AF17" t="n">
+      <c r="AI17" t="n">
         <v>-0.0001355530108317436</v>
       </c>
-      <c r="AG17" t="n">
+      <c r="AJ17" t="n">
         <v>168.2575179794911</v>
       </c>
-      <c r="AH17" t="n">
+      <c r="AK17" t="n">
         <v>2.423457712286137e-09</v>
       </c>
-      <c r="AI17" t="n">
+      <c r="AL17" t="n">
         <v>-219.528644634917</v>
       </c>
-      <c r="AJ17" t="n">
+      <c r="AM17" t="n">
         <v>-0.000697320223406836</v>
       </c>
-      <c r="AK17" t="n">
+      <c r="AN17" t="n">
         <v>-87.79382485850692</v>
       </c>
-      <c r="AL17" t="n">
+      <c r="AO17" t="n">
         <v>0.0001355530108317436</v>
       </c>
-      <c r="AM17" t="n">
+      <c r="AP17" t="n">
         <v>-18.2575179794911</v>
       </c>
-      <c r="AN17" t="n">
+      <c r="AQ17" t="n">
         <v>-2.423457712286137e-09</v>
       </c>
-      <c r="AO17" t="n">
+      <c r="AR17" t="n">
         <v>-340.0164632420323</v>
       </c>
-      <c r="AP17" t="n">
+      <c r="AS17" t="n">
         <v>-0.0001159978415836149</v>
       </c>
     </row>
@@ -4797,127 +6200,138 @@
       <c r="A18" t="n">
         <v>17</v>
       </c>
-      <c r="B18" t="n">
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
         <v>5</v>
       </c>
-      <c r="C18" t="n">
+      <c r="D18" t="n">
         <v>6</v>
       </c>
-      <c r="D18" t="n">
+      <c r="E18" t="n">
         <v>8</v>
       </c>
-      <c r="E18" t="n">
+      <c r="F18" t="n">
+        <v>-0.0001052931328663778</v>
+      </c>
+      <c r="G18" t="n">
+        <v>-1.316164160829722e-05</v>
+      </c>
+      <c r="H18" t="n">
         <v>-12.47723624466577</v>
       </c>
-      <c r="F18" t="n">
+      <c r="I18" t="n">
         <v>-2632.328321659445</v>
       </c>
-      <c r="G18" t="n">
+      <c r="J18" t="n">
         <v>3.595119805279563</v>
       </c>
-      <c r="H18" t="n">
+      <c r="K18" t="n">
         <v>5.264656553662592e-05</v>
       </c>
-      <c r="I18" t="n">
+      <c r="L18" t="n">
         <v>0.007516730126563289</v>
       </c>
-      <c r="J18" t="n">
+      <c r="M18" t="n">
         <v>-5.817587131184721e-06</v>
       </c>
-      <c r="K18" t="n">
+      <c r="N18" t="n">
         <v>0.5733905572099365</v>
       </c>
-      <c r="L18" t="n">
+      <c r="O18" t="n">
         <v>0.01497636114535011</v>
       </c>
-      <c r="M18" t="n">
+      <c r="P18" t="n">
         <v>3.595119805277692</v>
       </c>
-      <c r="N18" t="n">
+      <c r="Q18" t="n">
         <v>-5.264656732975187e-05</v>
       </c>
-      <c r="O18" t="n">
+      <c r="R18" t="n">
         <v>0.007516730126563006</v>
       </c>
-      <c r="P18" t="n">
+      <c r="S18" t="n">
         <v>5.817587439357226e-06</v>
       </c>
-      <c r="Q18" t="n">
+      <c r="T18" t="n">
         <v>0.5733905572095976</v>
       </c>
-      <c r="R18" t="n">
+      <c r="U18" t="n">
         <v>-0.01497636114489171</v>
       </c>
-      <c r="S18" t="n">
+      <c r="V18" t="n">
         <v>5.264656553662592e-05</v>
       </c>
-      <c r="T18" t="n">
+      <c r="W18" t="n">
         <v>-3.595119805279563</v>
       </c>
-      <c r="U18" t="n">
+      <c r="X18" t="n">
         <v>0.007516730126563289</v>
       </c>
-      <c r="V18" t="n">
+      <c r="Y18" t="n">
         <v>0.5733905572099365</v>
       </c>
-      <c r="W18" t="n">
+      <c r="Z18" t="n">
         <v>5.817587131184721e-06</v>
       </c>
-      <c r="X18" t="n">
+      <c r="AA18" t="n">
         <v>0.01497636114535011</v>
       </c>
-      <c r="Y18" t="n">
+      <c r="AB18" t="n">
         <v>-5.264656732975187e-05</v>
       </c>
-      <c r="Z18" t="n">
+      <c r="AC18" t="n">
         <v>-3.595119805277692</v>
       </c>
-      <c r="AA18" t="n">
+      <c r="AD18" t="n">
         <v>0.007516730126563006</v>
       </c>
-      <c r="AB18" t="n">
+      <c r="AE18" t="n">
         <v>0.5733905572095976</v>
       </c>
-      <c r="AC18" t="n">
+      <c r="AF18" t="n">
         <v>-5.817587439357226e-06</v>
       </c>
-      <c r="AD18" t="n">
+      <c r="AG18" t="n">
         <v>-0.01497636114489171</v>
       </c>
-      <c r="AE18" t="n">
+      <c r="AH18" t="n">
         <v>12.47723624466577</v>
       </c>
-      <c r="AF18" t="n">
+      <c r="AI18" t="n">
         <v>-3.865352482534945e-12</v>
       </c>
-      <c r="AG18" t="n">
+      <c r="AJ18" t="n">
         <v>1.28306291372754e-10</v>
       </c>
-      <c r="AH18" t="n">
+      <c r="AK18" t="n">
         <v>7.23199278240827e-13</v>
       </c>
-      <c r="AI18" t="n">
+      <c r="AL18" t="n">
         <v>0.006457521373425529</v>
       </c>
-      <c r="AJ18" t="n">
+      <c r="AM18" t="n">
         <v>16.62376087106873</v>
       </c>
-      <c r="AK18" t="n">
+      <c r="AN18" t="n">
         <v>-12.47723624466577</v>
       </c>
-      <c r="AL18" t="n">
+      <c r="AO18" t="n">
         <v>3.865352482534945e-12</v>
       </c>
-      <c r="AM18" t="n">
+      <c r="AP18" t="n">
         <v>-1.28306291372754e-10</v>
       </c>
-      <c r="AN18" t="n">
+      <c r="AQ18" t="n">
         <v>-7.23199278240827e-13</v>
       </c>
-      <c r="AO18" t="n">
+      <c r="AR18" t="n">
         <v>-0.006457522399876302</v>
       </c>
-      <c r="AP18" t="n">
+      <c r="AS18" t="n">
         <v>-16.62376087109965</v>
       </c>
     </row>
@@ -4925,127 +6339,138 @@
       <c r="A19" t="n">
         <v>18</v>
       </c>
-      <c r="B19" t="n">
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
         <v>6</v>
       </c>
-      <c r="C19" t="n">
+      <c r="D19" t="n">
         <v>7</v>
       </c>
-      <c r="D19" t="n">
+      <c r="E19" t="n">
         <v>8</v>
       </c>
-      <c r="E19" t="n">
+      <c r="F19" t="n">
+        <v>0.001056821946642028</v>
+      </c>
+      <c r="G19" t="n">
+        <v>0.0001321027433302535</v>
+      </c>
+      <c r="H19" t="n">
         <v>125.2334006770803</v>
       </c>
-      <c r="F19" t="n">
+      <c r="I19" t="n">
         <v>26420.5486660507</v>
       </c>
-      <c r="G19" t="n">
+      <c r="J19" t="n">
         <v>3.595119805277692</v>
       </c>
-      <c r="H19" t="n">
+      <c r="K19" t="n">
         <v>-5.264656732975187e-05</v>
       </c>
-      <c r="I19" t="n">
+      <c r="L19" t="n">
         <v>0.007516730126563006</v>
       </c>
-      <c r="J19" t="n">
+      <c r="M19" t="n">
         <v>5.817587439357226e-06</v>
       </c>
-      <c r="K19" t="n">
+      <c r="N19" t="n">
         <v>0.5733905572095976</v>
       </c>
-      <c r="L19" t="n">
+      <c r="O19" t="n">
         <v>-0.01497636114489171</v>
       </c>
-      <c r="M19" t="n">
+      <c r="P19" t="n">
         <v>3.596176627224334</v>
       </c>
-      <c r="N19" t="n">
+      <c r="Q19" t="n">
         <v>5.264656733141418e-05</v>
       </c>
-      <c r="O19" t="n">
+      <c r="R19" t="n">
         <v>-0.007516730126563017</v>
       </c>
-      <c r="P19" t="n">
+      <c r="S19" t="n">
         <v>-5.817587439646455e-06</v>
       </c>
-      <c r="Q19" t="n">
+      <c r="T19" t="n">
         <v>0.5737082536248554</v>
       </c>
-      <c r="R19" t="n">
+      <c r="U19" t="n">
         <v>0.04500689564371815</v>
       </c>
-      <c r="S19" t="n">
+      <c r="V19" t="n">
         <v>3.595119805277692</v>
       </c>
-      <c r="T19" t="n">
+      <c r="W19" t="n">
         <v>-5.264656732975187e-05</v>
       </c>
-      <c r="U19" t="n">
+      <c r="X19" t="n">
         <v>0.007516730126563006</v>
       </c>
-      <c r="V19" t="n">
+      <c r="Y19" t="n">
         <v>5.817587439357226e-06</v>
       </c>
-      <c r="W19" t="n">
+      <c r="Z19" t="n">
         <v>0.5733905572095976</v>
       </c>
-      <c r="X19" t="n">
+      <c r="AA19" t="n">
         <v>-0.01497636114489171</v>
       </c>
-      <c r="Y19" t="n">
+      <c r="AB19" t="n">
         <v>3.596176627224334</v>
       </c>
-      <c r="Z19" t="n">
+      <c r="AC19" t="n">
         <v>5.264656733141418e-05</v>
       </c>
-      <c r="AA19" t="n">
+      <c r="AD19" t="n">
         <v>-0.007516730126563017</v>
       </c>
-      <c r="AB19" t="n">
+      <c r="AE19" t="n">
         <v>-5.817587439646455e-06</v>
       </c>
-      <c r="AC19" t="n">
+      <c r="AF19" t="n">
         <v>0.5737082536248554</v>
       </c>
-      <c r="AD19" t="n">
+      <c r="AG19" t="n">
         <v>0.04500689564371815</v>
       </c>
-      <c r="AE19" t="n">
+      <c r="AH19" t="n">
         <v>-125.233400677098</v>
       </c>
-      <c r="AF19" t="n">
+      <c r="AI19" t="n">
         <v>12.48925291831083</v>
       </c>
-      <c r="AG19" t="n">
+      <c r="AJ19" t="n">
         <v>-475.9154605522502</v>
       </c>
-      <c r="AH19" t="n">
+      <c r="AK19" t="n">
         <v>2.48366232994117e-05</v>
       </c>
-      <c r="AI19" t="n">
+      <c r="AL19" t="n">
         <v>1903.485520698533</v>
       </c>
-      <c r="AJ19" t="n">
+      <c r="AM19" t="n">
         <v>16.66630415556484</v>
       </c>
-      <c r="AK19" t="n">
+      <c r="AN19" t="n">
         <v>125.233400677098</v>
       </c>
-      <c r="AL19" t="n">
+      <c r="AO19" t="n">
         <v>-12.48925291831083</v>
       </c>
-      <c r="AM19" t="n">
+      <c r="AP19" t="n">
         <v>475.9154605522502</v>
       </c>
-      <c r="AN19" t="n">
+      <c r="AQ19" t="n">
         <v>-2.48366232994117e-05</v>
       </c>
-      <c r="AO19" t="n">
+      <c r="AR19" t="n">
         <v>1903.838163719469</v>
       </c>
-      <c r="AP19" t="n">
+      <c r="AS19" t="n">
         <v>83.24771919092179</v>
       </c>
     </row>
@@ -5053,127 +6478,138 @@
       <c r="A20" t="n">
         <v>19</v>
       </c>
-      <c r="B20" t="n">
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
         <v>7</v>
-      </c>
-      <c r="C20" t="n">
-        <v>8</v>
       </c>
       <c r="D20" t="n">
         <v>8</v>
       </c>
       <c r="E20" t="n">
+        <v>8</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.0001052931328663774</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1.316164160829718e-05</v>
+      </c>
+      <c r="H20" t="n">
         <v>12.47723624466572</v>
       </c>
-      <c r="F20" t="n">
+      <c r="I20" t="n">
         <v>2632.328321659435</v>
       </c>
-      <c r="G20" t="n">
+      <c r="J20" t="n">
         <v>3.596176627224334</v>
       </c>
-      <c r="H20" t="n">
+      <c r="K20" t="n">
         <v>5.264656733141418e-05</v>
       </c>
-      <c r="I20" t="n">
+      <c r="L20" t="n">
         <v>-0.007516730126563017</v>
       </c>
-      <c r="J20" t="n">
+      <c r="M20" t="n">
         <v>-5.817587439646455e-06</v>
       </c>
-      <c r="K20" t="n">
+      <c r="N20" t="n">
         <v>0.5737082536248554</v>
       </c>
-      <c r="L20" t="n">
+      <c r="O20" t="n">
         <v>0.04500689564371815</v>
       </c>
-      <c r="M20" t="n">
+      <c r="P20" t="n">
         <v>3.596176627226205</v>
       </c>
-      <c r="N20" t="n">
+      <c r="Q20" t="n">
         <v>-5.264656553496323e-05</v>
       </c>
-      <c r="O20" t="n">
+      <c r="R20" t="n">
         <v>-0.00751673012656329</v>
       </c>
-      <c r="P20" t="n">
+      <c r="S20" t="n">
         <v>5.817587130890855e-06</v>
       </c>
-      <c r="Q20" t="n">
+      <c r="T20" t="n">
         <v>0.5737082536251945</v>
       </c>
-      <c r="R20" t="n">
+      <c r="U20" t="n">
         <v>-0.04500689564325982</v>
       </c>
-      <c r="S20" t="n">
+      <c r="V20" t="n">
         <v>-5.264656733141418e-05</v>
       </c>
-      <c r="T20" t="n">
+      <c r="W20" t="n">
         <v>3.596176627224334</v>
       </c>
-      <c r="U20" t="n">
+      <c r="X20" t="n">
         <v>-0.007516730126563017</v>
       </c>
-      <c r="V20" t="n">
+      <c r="Y20" t="n">
         <v>-0.5737082536248554</v>
       </c>
-      <c r="W20" t="n">
+      <c r="Z20" t="n">
         <v>-5.817587439646455e-06</v>
       </c>
-      <c r="X20" t="n">
+      <c r="AA20" t="n">
         <v>0.04500689564371815</v>
       </c>
-      <c r="Y20" t="n">
+      <c r="AB20" t="n">
         <v>5.264656553496323e-05</v>
       </c>
-      <c r="Z20" t="n">
+      <c r="AC20" t="n">
         <v>3.596176627226205</v>
       </c>
-      <c r="AA20" t="n">
+      <c r="AD20" t="n">
         <v>-0.00751673012656329</v>
       </c>
-      <c r="AB20" t="n">
+      <c r="AE20" t="n">
         <v>-0.5737082536251945</v>
       </c>
-      <c r="AC20" t="n">
+      <c r="AF20" t="n">
         <v>5.817587130890855e-06</v>
       </c>
-      <c r="AD20" t="n">
+      <c r="AG20" t="n">
         <v>-0.04500689564325982</v>
       </c>
-      <c r="AE20" t="n">
+      <c r="AH20" t="n">
         <v>-12.47723624466572</v>
       </c>
-      <c r="AF20" t="n">
+      <c r="AI20" t="n">
         <v>-100.000000000004</v>
       </c>
-      <c r="AG20" t="n">
+      <c r="AJ20" t="n">
         <v>1.285480819013252e-10</v>
       </c>
-      <c r="AH20" t="n">
+      <c r="AK20" t="n">
         <v>7.238654120556021e-13</v>
       </c>
-      <c r="AI20" t="n">
+      <c r="AL20" t="n">
         <v>-0.006457522400840577</v>
       </c>
-      <c r="AJ20" t="n">
+      <c r="AM20" t="n">
         <v>-83.37567916907628</v>
       </c>
-      <c r="AK20" t="n">
+      <c r="AN20" t="n">
         <v>12.47723624466572</v>
       </c>
-      <c r="AL20" t="n">
+      <c r="AO20" t="n">
         <v>-99.99999999999602</v>
       </c>
-      <c r="AM20" t="n">
+      <c r="AP20" t="n">
         <v>-1.285480819013252e-10</v>
       </c>
-      <c r="AN20" t="n">
+      <c r="AQ20" t="n">
         <v>-7.238654120556021e-13</v>
       </c>
-      <c r="AO20" t="n">
+      <c r="AR20" t="n">
         <v>0.006457521372455919</v>
       </c>
-      <c r="AP20" t="n">
+      <c r="AS20" t="n">
         <v>83.37567916904467</v>
       </c>
     </row>
@@ -5181,127 +6617,138 @@
       <c r="A21" t="n">
         <v>20</v>
       </c>
-      <c r="B21" t="n">
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
         <v>8</v>
       </c>
-      <c r="C21" t="n">
+      <c r="D21" t="n">
         <v>5</v>
       </c>
-      <c r="D21" t="n">
+      <c r="E21" t="n">
         <v>8</v>
       </c>
-      <c r="E21" t="n">
+      <c r="F21" t="n">
+        <v>0.001056821946642472</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0.000132102743330309</v>
+      </c>
+      <c r="H21" t="n">
         <v>125.2334006771329</v>
       </c>
-      <c r="F21" t="n">
+      <c r="I21" t="n">
         <v>26420.5486660618</v>
       </c>
-      <c r="G21" t="n">
+      <c r="J21" t="n">
         <v>3.596176627226205</v>
       </c>
-      <c r="H21" t="n">
+      <c r="K21" t="n">
         <v>-5.264656553496323e-05</v>
       </c>
-      <c r="I21" t="n">
+      <c r="L21" t="n">
         <v>-0.00751673012656329</v>
       </c>
-      <c r="J21" t="n">
+      <c r="M21" t="n">
         <v>5.817587130890855e-06</v>
       </c>
-      <c r="K21" t="n">
+      <c r="N21" t="n">
         <v>0.5737082536251945</v>
       </c>
-      <c r="L21" t="n">
+      <c r="O21" t="n">
         <v>-0.04500689564325982</v>
       </c>
-      <c r="M21" t="n">
+      <c r="P21" t="n">
         <v>3.595119805279563</v>
       </c>
-      <c r="N21" t="n">
+      <c r="Q21" t="n">
         <v>5.264656553662592e-05</v>
       </c>
-      <c r="O21" t="n">
+      <c r="R21" t="n">
         <v>0.007516730126563289</v>
       </c>
-      <c r="P21" t="n">
+      <c r="S21" t="n">
         <v>-5.817587131184721e-06</v>
       </c>
-      <c r="Q21" t="n">
+      <c r="T21" t="n">
         <v>0.5733905572099365</v>
       </c>
-      <c r="R21" t="n">
+      <c r="U21" t="n">
         <v>0.01497636114535011</v>
       </c>
-      <c r="S21" t="n">
+      <c r="V21" t="n">
         <v>-3.596176627226205</v>
       </c>
-      <c r="T21" t="n">
+      <c r="W21" t="n">
         <v>-5.264656553496323e-05</v>
       </c>
-      <c r="U21" t="n">
+      <c r="X21" t="n">
         <v>0.00751673012656329</v>
       </c>
-      <c r="V21" t="n">
+      <c r="Y21" t="n">
         <v>-5.817587130890855e-06</v>
       </c>
-      <c r="W21" t="n">
+      <c r="Z21" t="n">
         <v>0.5737082536251945</v>
       </c>
-      <c r="X21" t="n">
+      <c r="AA21" t="n">
         <v>0.04500689564325982</v>
       </c>
-      <c r="Y21" t="n">
+      <c r="AB21" t="n">
         <v>-3.595119805279563</v>
       </c>
-      <c r="Z21" t="n">
+      <c r="AC21" t="n">
         <v>5.264656553662592e-05</v>
       </c>
-      <c r="AA21" t="n">
+      <c r="AD21" t="n">
         <v>-0.007516730126563289</v>
       </c>
-      <c r="AB21" t="n">
+      <c r="AE21" t="n">
         <v>5.817587131184721e-06</v>
       </c>
-      <c r="AC21" t="n">
+      <c r="AF21" t="n">
         <v>0.5733905572099365</v>
       </c>
-      <c r="AD21" t="n">
+      <c r="AG21" t="n">
         <v>-0.01497636114535011</v>
       </c>
-      <c r="AE21" t="n">
+      <c r="AH21" t="n">
         <v>-125.233400677098</v>
       </c>
-      <c r="AF21" t="n">
+      <c r="AI21" t="n">
         <v>12.48925291830278</v>
       </c>
-      <c r="AG21" t="n">
+      <c r="AJ21" t="n">
         <v>-475.9154605525324</v>
       </c>
-      <c r="AH21" t="n">
+      <c r="AK21" t="n">
         <v>-2.483662198250748e-05</v>
       </c>
-      <c r="AI21" t="n">
+      <c r="AL21" t="n">
         <v>1903.838163720598</v>
       </c>
-      <c r="AJ21" t="n">
+      <c r="AM21" t="n">
         <v>83.24771919088963</v>
       </c>
-      <c r="AK21" t="n">
+      <c r="AN21" t="n">
         <v>125.233400677098</v>
       </c>
-      <c r="AL21" t="n">
+      <c r="AO21" t="n">
         <v>-12.48925291830278</v>
       </c>
-      <c r="AM21" t="n">
+      <c r="AP21" t="n">
         <v>475.9154605525324</v>
       </c>
-      <c r="AN21" t="n">
+      <c r="AQ21" t="n">
         <v>2.483662198250748e-05</v>
       </c>
-      <c r="AO21" t="n">
+      <c r="AR21" t="n">
         <v>1903.485520699661</v>
       </c>
-      <c r="AP21" t="n">
+      <c r="AS21" t="n">
         <v>16.6663041555326</v>
       </c>
     </row>
@@ -5309,127 +6756,138 @@
       <c r="A22" t="n">
         <v>21</v>
       </c>
-      <c r="B22" t="n">
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
         <v>9</v>
       </c>
-      <c r="C22" t="n">
+      <c r="D22" t="n">
         <v>10</v>
       </c>
-      <c r="D22" t="n">
+      <c r="E22" t="n">
         <v>8</v>
       </c>
-      <c r="E22" t="n">
+      <c r="F22" t="n">
+        <v>-0.0001054962997791679</v>
+      </c>
+      <c r="G22" t="n">
+        <v>-1.318703747239599e-05</v>
+      </c>
+      <c r="H22" t="n">
         <v>-12.5013115238314</v>
       </c>
-      <c r="F22" t="n">
+      <c r="I22" t="n">
         <v>-2637.407494479197</v>
       </c>
-      <c r="G22" t="n">
+      <c r="J22" t="n">
         <v>8.113133295381624</v>
       </c>
-      <c r="H22" t="n">
+      <c r="K22" t="n">
         <v>5.27481476618041e-05</v>
       </c>
-      <c r="I22" t="n">
+      <c r="L22" t="n">
         <v>0.01202133708507339</v>
       </c>
-      <c r="J22" t="n">
+      <c r="M22" t="n">
         <v>1.276246312356512e-06</v>
       </c>
-      <c r="K22" t="n">
+      <c r="N22" t="n">
         <v>0.4768655535134581</v>
       </c>
-      <c r="L22" t="n">
+      <c r="O22" t="n">
         <v>0.01500508180328185</v>
       </c>
-      <c r="M22" t="n">
+      <c r="P22" t="n">
         <v>8.113133295376661</v>
       </c>
-      <c r="N22" t="n">
+      <c r="Q22" t="n">
         <v>-5.274815211736379e-05</v>
       </c>
-      <c r="O22" t="n">
+      <c r="R22" t="n">
         <v>0.01202133708507298</v>
       </c>
-      <c r="P22" t="n">
+      <c r="S22" t="n">
         <v>-1.276246011702428e-06</v>
       </c>
-      <c r="Q22" t="n">
+      <c r="T22" t="n">
         <v>0.4768655535130946</v>
       </c>
-      <c r="R22" t="n">
+      <c r="U22" t="n">
         <v>-0.01500508180210351</v>
       </c>
-      <c r="S22" t="n">
+      <c r="V22" t="n">
         <v>5.27481476618041e-05</v>
       </c>
-      <c r="T22" t="n">
+      <c r="W22" t="n">
         <v>-8.113133295381624</v>
       </c>
-      <c r="U22" t="n">
+      <c r="X22" t="n">
         <v>0.01202133708507339</v>
       </c>
-      <c r="V22" t="n">
+      <c r="Y22" t="n">
         <v>0.4768655535134581</v>
       </c>
-      <c r="W22" t="n">
+      <c r="Z22" t="n">
         <v>-1.276246312356512e-06</v>
       </c>
-      <c r="X22" t="n">
+      <c r="AA22" t="n">
         <v>0.01500508180328185</v>
       </c>
-      <c r="Y22" t="n">
+      <c r="AB22" t="n">
         <v>-5.274815211736379e-05</v>
       </c>
-      <c r="Z22" t="n">
+      <c r="AC22" t="n">
         <v>-8.113133295376661</v>
       </c>
-      <c r="AA22" t="n">
+      <c r="AD22" t="n">
         <v>0.01202133708507298</v>
       </c>
-      <c r="AB22" t="n">
+      <c r="AE22" t="n">
         <v>0.4768655535130946</v>
       </c>
-      <c r="AC22" t="n">
+      <c r="AF22" t="n">
         <v>1.276246011702428e-06</v>
       </c>
-      <c r="AD22" t="n">
+      <c r="AG22" t="n">
         <v>-0.01500508180210351</v>
       </c>
-      <c r="AE22" t="n">
+      <c r="AH22" t="n">
         <v>12.5013115238314</v>
       </c>
-      <c r="AF22" t="n">
+      <c r="AI22" t="n">
         <v>-2.592059900052845e-11</v>
       </c>
-      <c r="AG22" t="n">
+      <c r="AJ22" t="n">
         <v>1.251894328219844e-10</v>
       </c>
-      <c r="AH22" t="n">
+      <c r="AK22" t="n">
         <v>7.758238496080594e-13</v>
       </c>
-      <c r="AI22" t="n">
+      <c r="AL22" t="n">
         <v>-0.001416633740610715</v>
       </c>
-      <c r="AJ22" t="n">
+      <c r="AM22" t="n">
         <v>16.65564080088552</v>
       </c>
-      <c r="AK22" t="n">
+      <c r="AN22" t="n">
         <v>-12.5013115238314</v>
       </c>
-      <c r="AL22" t="n">
+      <c r="AO22" t="n">
         <v>2.592059900052845e-11</v>
       </c>
-      <c r="AM22" t="n">
+      <c r="AP22" t="n">
         <v>-1.251894328219844e-10</v>
       </c>
-      <c r="AN22" t="n">
+      <c r="AQ22" t="n">
         <v>-7.758238496080594e-13</v>
       </c>
-      <c r="AO22" t="n">
+      <c r="AR22" t="n">
         <v>0.001416632739095252</v>
       </c>
-      <c r="AP22" t="n">
+      <c r="AS22" t="n">
         <v>-16.65564080109243</v>
       </c>
     </row>
@@ -5437,127 +6895,138 @@
       <c r="A23" t="n">
         <v>22</v>
       </c>
-      <c r="B23" t="n">
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
         <v>10</v>
       </c>
-      <c r="C23" t="n">
+      <c r="D23" t="n">
         <v>11</v>
       </c>
-      <c r="D23" t="n">
+      <c r="E23" t="n">
         <v>8</v>
       </c>
-      <c r="E23" t="n">
+      <c r="F23" t="n">
+        <v>0.001042184204001373</v>
+      </c>
+      <c r="G23" t="n">
+        <v>0.0001302730255001716</v>
+      </c>
+      <c r="H23" t="n">
         <v>123.4988281741627</v>
       </c>
-      <c r="F23" t="n">
+      <c r="I23" t="n">
         <v>26054.60510003432</v>
       </c>
-      <c r="G23" t="n">
+      <c r="J23" t="n">
         <v>8.113133295376661</v>
       </c>
-      <c r="H23" t="n">
+      <c r="K23" t="n">
         <v>-5.274815211736379e-05</v>
       </c>
-      <c r="I23" t="n">
+      <c r="L23" t="n">
         <v>0.01202133708507298</v>
       </c>
-      <c r="J23" t="n">
+      <c r="M23" t="n">
         <v>-1.276246011702428e-06</v>
       </c>
-      <c r="K23" t="n">
+      <c r="N23" t="n">
         <v>0.4768655535130946</v>
       </c>
-      <c r="L23" t="n">
+      <c r="O23" t="n">
         <v>-0.01500508180210351</v>
       </c>
-      <c r="M23" t="n">
+      <c r="P23" t="n">
         <v>8.114175479580663</v>
       </c>
-      <c r="N23" t="n">
+      <c r="Q23" t="n">
         <v>5.274815212167277e-05</v>
       </c>
-      <c r="O23" t="n">
+      <c r="R23" t="n">
         <v>-0.012021337085073</v>
       </c>
-      <c r="P23" t="n">
+      <c r="S23" t="n">
         <v>1.27624601135778e-06</v>
       </c>
-      <c r="Q23" t="n">
+      <c r="T23" t="n">
         <v>0.4758775876426199</v>
       </c>
-      <c r="R23" t="n">
+      <c r="U23" t="n">
         <v>0.04505488004389391</v>
       </c>
-      <c r="S23" t="n">
+      <c r="V23" t="n">
         <v>8.113133295376661</v>
       </c>
-      <c r="T23" t="n">
+      <c r="W23" t="n">
         <v>-5.274815211736379e-05</v>
       </c>
-      <c r="U23" t="n">
+      <c r="X23" t="n">
         <v>0.01202133708507298</v>
       </c>
-      <c r="V23" t="n">
+      <c r="Y23" t="n">
         <v>-1.276246011702428e-06</v>
       </c>
-      <c r="W23" t="n">
+      <c r="Z23" t="n">
         <v>0.4768655535130946</v>
       </c>
-      <c r="X23" t="n">
+      <c r="AA23" t="n">
         <v>-0.01500508180210351</v>
       </c>
-      <c r="Y23" t="n">
+      <c r="AB23" t="n">
         <v>8.114175479580663</v>
       </c>
-      <c r="Z23" t="n">
+      <c r="AC23" t="n">
         <v>5.274815212167277e-05</v>
       </c>
-      <c r="AA23" t="n">
+      <c r="AD23" t="n">
         <v>-0.012021337085073</v>
       </c>
-      <c r="AB23" t="n">
+      <c r="AE23" t="n">
         <v>1.27624601135778e-06</v>
       </c>
-      <c r="AC23" t="n">
+      <c r="AF23" t="n">
         <v>0.4758775876426199</v>
       </c>
-      <c r="AD23" t="n">
+      <c r="AG23" t="n">
         <v>0.04505488004389391</v>
       </c>
-      <c r="AE23" t="n">
+      <c r="AH23" t="n">
         <v>-123.4988281741971</v>
       </c>
-      <c r="AF23" t="n">
+      <c r="AI23" t="n">
         <v>12.49725030898538</v>
       </c>
-      <c r="AG23" t="n">
+      <c r="AJ23" t="n">
         <v>-394.0773917252354</v>
       </c>
-      <c r="AH23" t="n">
+      <c r="AK23" t="n">
         <v>-5.448588741532367e-06</v>
       </c>
-      <c r="AI23" t="n">
+      <c r="AL23" t="n">
         <v>1576.857887959055</v>
       </c>
-      <c r="AJ23" t="n">
+      <c r="AM23" t="n">
         <v>16.65572241141295</v>
       </c>
-      <c r="AK23" t="n">
+      <c r="AN23" t="n">
         <v>123.4988281741971</v>
       </c>
-      <c r="AL23" t="n">
+      <c r="AO23" t="n">
         <v>-12.49725030898538</v>
       </c>
-      <c r="AM23" t="n">
+      <c r="AP23" t="n">
         <v>394.0773917252354</v>
       </c>
-      <c r="AN23" t="n">
+      <c r="AQ23" t="n">
         <v>5.448588741532367e-06</v>
       </c>
-      <c r="AO23" t="n">
+      <c r="AR23" t="n">
         <v>1575.761245842828</v>
       </c>
-      <c r="AP23" t="n">
+      <c r="AS23" t="n">
         <v>83.32228006047011</v>
       </c>
     </row>
@@ -5565,127 +7034,138 @@
       <c r="A24" t="n">
         <v>23</v>
       </c>
-      <c r="B24" t="n">
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
         <v>11</v>
       </c>
-      <c r="C24" t="n">
+      <c r="D24" t="n">
         <v>12</v>
       </c>
-      <c r="D24" t="n">
+      <c r="E24" t="n">
         <v>8</v>
       </c>
-      <c r="E24" t="n">
+      <c r="F24" t="n">
+        <v>0.0001054962997791679</v>
+      </c>
+      <c r="G24" t="n">
+        <v>1.318703747239598e-05</v>
+      </c>
+      <c r="H24" t="n">
         <v>12.50131152383139</v>
       </c>
-      <c r="F24" t="n">
+      <c r="I24" t="n">
         <v>2637.407494479197</v>
       </c>
-      <c r="G24" t="n">
+      <c r="J24" t="n">
         <v>8.114175479580663</v>
       </c>
-      <c r="H24" t="n">
+      <c r="K24" t="n">
         <v>5.274815212167277e-05</v>
       </c>
-      <c r="I24" t="n">
+      <c r="L24" t="n">
         <v>-0.012021337085073</v>
       </c>
-      <c r="J24" t="n">
+      <c r="M24" t="n">
         <v>1.27624601135778e-06</v>
       </c>
-      <c r="K24" t="n">
+      <c r="N24" t="n">
         <v>0.4758775876426199</v>
       </c>
-      <c r="L24" t="n">
+      <c r="O24" t="n">
         <v>0.04505488004389391</v>
       </c>
-      <c r="M24" t="n">
+      <c r="P24" t="n">
         <v>8.114175479585626</v>
       </c>
-      <c r="N24" t="n">
+      <c r="Q24" t="n">
         <v>-5.27481476574951e-05</v>
       </c>
-      <c r="O24" t="n">
+      <c r="R24" t="n">
         <v>-0.01202133708507339</v>
       </c>
-      <c r="P24" t="n">
+      <c r="S24" t="n">
         <v>-1.276246312679776e-06</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="T24" t="n">
         <v>0.475877587642983</v>
       </c>
-      <c r="R24" t="n">
+      <c r="U24" t="n">
         <v>-0.04505488004271615</v>
       </c>
-      <c r="S24" t="n">
+      <c r="V24" t="n">
         <v>-5.274815212167277e-05</v>
       </c>
-      <c r="T24" t="n">
+      <c r="W24" t="n">
         <v>8.114175479580663</v>
       </c>
-      <c r="U24" t="n">
+      <c r="X24" t="n">
         <v>-0.012021337085073</v>
       </c>
-      <c r="V24" t="n">
+      <c r="Y24" t="n">
         <v>-0.4758775876426199</v>
       </c>
-      <c r="W24" t="n">
+      <c r="Z24" t="n">
         <v>1.27624601135778e-06</v>
       </c>
-      <c r="X24" t="n">
+      <c r="AA24" t="n">
         <v>0.04505488004389391</v>
       </c>
-      <c r="Y24" t="n">
+      <c r="AB24" t="n">
         <v>5.27481476574951e-05</v>
       </c>
-      <c r="Z24" t="n">
+      <c r="AC24" t="n">
         <v>8.114175479585626</v>
       </c>
-      <c r="AA24" t="n">
+      <c r="AD24" t="n">
         <v>-0.01202133708507339</v>
       </c>
-      <c r="AB24" t="n">
+      <c r="AE24" t="n">
         <v>-0.475877587642983</v>
       </c>
-      <c r="AC24" t="n">
+      <c r="AF24" t="n">
         <v>-1.276246312679776e-06</v>
       </c>
-      <c r="AD24" t="n">
+      <c r="AG24" t="n">
         <v>-0.04505488004271615</v>
       </c>
-      <c r="AE24" t="n">
+      <c r="AH24" t="n">
         <v>-12.50131152383139</v>
       </c>
-      <c r="AF24" t="n">
+      <c r="AI24" t="n">
         <v>-100.0000000000263</v>
       </c>
-      <c r="AG24" t="n">
+      <c r="AJ24" t="n">
         <v>1.254654333985444e-10</v>
       </c>
-      <c r="AH24" t="n">
+      <c r="AK24" t="n">
         <v>7.751577157932843e-13</v>
       </c>
-      <c r="AI24" t="n">
+      <c r="AL24" t="n">
         <v>0.001416632737978864</v>
       </c>
-      <c r="AJ24" t="n">
+      <c r="AM24" t="n">
         <v>-83.32241648536987</v>
       </c>
-      <c r="AK24" t="n">
+      <c r="AN24" t="n">
         <v>12.50131152383139</v>
       </c>
-      <c r="AL24" t="n">
+      <c r="AO24" t="n">
         <v>-99.99999999997374</v>
       </c>
-      <c r="AM24" t="n">
+      <c r="AP24" t="n">
         <v>-1.254654333985444e-10</v>
       </c>
-      <c r="AN24" t="n">
+      <c r="AQ24" t="n">
         <v>-7.751577157932843e-13</v>
       </c>
-      <c r="AO24" t="n">
+      <c r="AR24" t="n">
         <v>-0.00141663374170233</v>
       </c>
-      <c r="AP24" t="n">
+      <c r="AS24" t="n">
         <v>83.32241648516023</v>
       </c>
     </row>
@@ -5693,127 +7173,138 @@
       <c r="A25" t="n">
         <v>24</v>
       </c>
-      <c r="B25" t="n">
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
         <v>12</v>
       </c>
-      <c r="C25" t="n">
+      <c r="D25" t="n">
         <v>9</v>
       </c>
-      <c r="D25" t="n">
+      <c r="E25" t="n">
         <v>8</v>
       </c>
-      <c r="E25" t="n">
+      <c r="F25" t="n">
+        <v>0.001042184204001373</v>
+      </c>
+      <c r="G25" t="n">
+        <v>0.0001302730255001716</v>
+      </c>
+      <c r="H25" t="n">
         <v>123.4988281741627</v>
       </c>
-      <c r="F25" t="n">
+      <c r="I25" t="n">
         <v>26054.60510003432</v>
       </c>
-      <c r="G25" t="n">
+      <c r="J25" t="n">
         <v>8.114175479585626</v>
       </c>
-      <c r="H25" t="n">
+      <c r="K25" t="n">
         <v>-5.27481476574951e-05</v>
       </c>
-      <c r="I25" t="n">
+      <c r="L25" t="n">
         <v>-0.01202133708507339</v>
       </c>
-      <c r="J25" t="n">
+      <c r="M25" t="n">
         <v>-1.276246312679776e-06</v>
       </c>
-      <c r="K25" t="n">
+      <c r="N25" t="n">
         <v>0.475877587642983</v>
       </c>
-      <c r="L25" t="n">
+      <c r="O25" t="n">
         <v>-0.04505488004271615</v>
       </c>
-      <c r="M25" t="n">
+      <c r="P25" t="n">
         <v>8.113133295381624</v>
       </c>
-      <c r="N25" t="n">
+      <c r="Q25" t="n">
         <v>5.27481476618041e-05</v>
       </c>
-      <c r="O25" t="n">
+      <c r="R25" t="n">
         <v>0.01202133708507339</v>
       </c>
-      <c r="P25" t="n">
+      <c r="S25" t="n">
         <v>1.276246312356512e-06</v>
       </c>
-      <c r="Q25" t="n">
+      <c r="T25" t="n">
         <v>0.4768655535134581</v>
       </c>
-      <c r="R25" t="n">
+      <c r="U25" t="n">
         <v>0.01500508180328185</v>
       </c>
-      <c r="S25" t="n">
+      <c r="V25" t="n">
         <v>-8.114175479585626</v>
       </c>
-      <c r="T25" t="n">
+      <c r="W25" t="n">
         <v>-5.27481476574951e-05</v>
       </c>
-      <c r="U25" t="n">
+      <c r="X25" t="n">
         <v>0.01202133708507339</v>
       </c>
-      <c r="V25" t="n">
+      <c r="Y25" t="n">
         <v>1.276246312679776e-06</v>
       </c>
-      <c r="W25" t="n">
+      <c r="Z25" t="n">
         <v>0.475877587642983</v>
       </c>
-      <c r="X25" t="n">
+      <c r="AA25" t="n">
         <v>0.04505488004271615</v>
       </c>
-      <c r="Y25" t="n">
+      <c r="AB25" t="n">
         <v>-8.113133295381624</v>
       </c>
-      <c r="Z25" t="n">
+      <c r="AC25" t="n">
         <v>5.27481476618041e-05</v>
       </c>
-      <c r="AA25" t="n">
+      <c r="AD25" t="n">
         <v>-0.01202133708507339</v>
       </c>
-      <c r="AB25" t="n">
+      <c r="AE25" t="n">
         <v>-1.276246312356512e-06</v>
       </c>
-      <c r="AC25" t="n">
+      <c r="AF25" t="n">
         <v>0.4768655535134581</v>
       </c>
-      <c r="AD25" t="n">
+      <c r="AG25" t="n">
         <v>-0.01500508180328185</v>
       </c>
-      <c r="AE25" t="n">
+      <c r="AH25" t="n">
         <v>-123.4988281741971</v>
       </c>
-      <c r="AF25" t="n">
+      <c r="AI25" t="n">
         <v>12.49725030893287</v>
       </c>
-      <c r="AG25" t="n">
+      <c r="AJ25" t="n">
         <v>-394.0773917255378</v>
       </c>
-      <c r="AH25" t="n">
+      <c r="AK25" t="n">
         <v>5.448590026519767e-06</v>
       </c>
-      <c r="AI25" t="n">
+      <c r="AL25" t="n">
         <v>1575.761245844037</v>
       </c>
-      <c r="AJ25" t="n">
+      <c r="AM25" t="n">
         <v>83.32228006026035</v>
       </c>
-      <c r="AK25" t="n">
+      <c r="AN25" t="n">
         <v>123.4988281741971</v>
       </c>
-      <c r="AL25" t="n">
+      <c r="AO25" t="n">
         <v>-12.49725030893287</v>
       </c>
-      <c r="AM25" t="n">
+      <c r="AP25" t="n">
         <v>394.0773917255378</v>
       </c>
-      <c r="AN25" t="n">
+      <c r="AQ25" t="n">
         <v>-5.448590026519767e-06</v>
       </c>
-      <c r="AO25" t="n">
+      <c r="AR25" t="n">
         <v>1576.857887960265</v>
       </c>
-      <c r="AP25" t="n">
+      <c r="AS25" t="n">
         <v>16.65572241120256</v>
       </c>
     </row>
@@ -5821,127 +7312,138 @@
       <c r="A26" t="n">
         <v>25</v>
       </c>
-      <c r="B26" t="n">
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
         <v>13</v>
       </c>
-      <c r="C26" t="n">
+      <c r="D26" t="n">
         <v>14</v>
       </c>
-      <c r="D26" t="n">
+      <c r="E26" t="n">
         <v>8</v>
       </c>
-      <c r="E26" t="n">
+      <c r="F26" t="n">
+        <v>-0.0001054548126048016</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.318185157560019e-05</v>
+      </c>
+      <c r="H26" t="n">
         <v>-12.49639529366899</v>
       </c>
-      <c r="F26" t="n">
+      <c r="I26" t="n">
         <v>-2636.370315120039</v>
       </c>
-      <c r="G26" t="n">
+      <c r="J26" t="n">
         <v>11.24253477912758</v>
       </c>
-      <c r="H26" t="n">
+      <c r="K26" t="n">
         <v>5.272740302799424e-05</v>
       </c>
-      <c r="I26" t="n">
+      <c r="L26" t="n">
         <v>0.01403178333646062</v>
       </c>
-      <c r="J26" t="n">
+      <c r="M26" t="n">
         <v>-2.886833036039658e-07</v>
       </c>
-      <c r="K26" t="n">
+      <c r="N26" t="n">
         <v>0.2774101967681684</v>
       </c>
-      <c r="L26" t="n">
+      <c r="O26" t="n">
         <v>0.01500512856537014</v>
       </c>
-      <c r="M26" t="n">
+      <c r="P26" t="n">
         <v>11.2425347791201</v>
       </c>
-      <c r="N26" t="n">
+      <c r="Q26" t="n">
         <v>-5.272740957680732e-05</v>
       </c>
-      <c r="O26" t="n">
+      <c r="R26" t="n">
         <v>0.01403178333646043</v>
       </c>
-      <c r="P26" t="n">
+      <c r="S26" t="n">
         <v>2.886834930193329e-07</v>
       </c>
-      <c r="Q26" t="n">
+      <c r="T26" t="n">
         <v>0.2774101967679769</v>
       </c>
-      <c r="R26" t="n">
+      <c r="U26" t="n">
         <v>-0.01500512856361739</v>
       </c>
-      <c r="S26" t="n">
+      <c r="V26" t="n">
         <v>5.272740302799424e-05</v>
       </c>
-      <c r="T26" t="n">
+      <c r="W26" t="n">
         <v>-11.24253477912758</v>
       </c>
-      <c r="U26" t="n">
+      <c r="X26" t="n">
         <v>0.01403178333646062</v>
       </c>
-      <c r="V26" t="n">
+      <c r="Y26" t="n">
         <v>0.2774101967681684</v>
       </c>
-      <c r="W26" t="n">
+      <c r="Z26" t="n">
         <v>2.886833036039658e-07</v>
       </c>
-      <c r="X26" t="n">
+      <c r="AA26" t="n">
         <v>0.01500512856537014</v>
       </c>
-      <c r="Y26" t="n">
+      <c r="AB26" t="n">
         <v>-5.272740957680732e-05</v>
       </c>
-      <c r="Z26" t="n">
+      <c r="AC26" t="n">
         <v>-11.2425347791201</v>
       </c>
-      <c r="AA26" t="n">
+      <c r="AD26" t="n">
         <v>0.01403178333646043</v>
       </c>
-      <c r="AB26" t="n">
+      <c r="AE26" t="n">
         <v>0.2774101967679769</v>
       </c>
-      <c r="AC26" t="n">
+      <c r="AF26" t="n">
         <v>-2.886834930193329e-07</v>
       </c>
-      <c r="AD26" t="n">
+      <c r="AG26" t="n">
         <v>-0.01500512856361739</v>
       </c>
-      <c r="AE26" t="n">
+      <c r="AH26" t="n">
         <v>12.49639529366899</v>
       </c>
-      <c r="AF26" t="n">
+      <c r="AI26" t="n">
         <v>-4.843059286940843e-11</v>
       </c>
-      <c r="AG26" t="n">
+      <c r="AJ26" t="n">
         <v>7.886364625849396e-11</v>
       </c>
-      <c r="AH26" t="n">
+      <c r="AK26" t="n">
         <v>4.087841176669826e-13</v>
       </c>
-      <c r="AI26" t="n">
+      <c r="AL26" t="n">
         <v>0.0003204382566711034</v>
       </c>
-      <c r="AJ26" t="n">
+      <c r="AM26" t="n">
         <v>16.65569270639389</v>
       </c>
-      <c r="AK26" t="n">
+      <c r="AN26" t="n">
         <v>-12.49639529366899</v>
       </c>
-      <c r="AL26" t="n">
+      <c r="AO26" t="n">
         <v>4.843059286940843e-11</v>
       </c>
-      <c r="AM26" t="n">
+      <c r="AP26" t="n">
         <v>-7.886364625849396e-11</v>
       </c>
-      <c r="AN26" t="n">
+      <c r="AQ26" t="n">
         <v>-4.087841176669826e-13</v>
       </c>
-      <c r="AO26" t="n">
+      <c r="AR26" t="n">
         <v>-0.0003204388875802733</v>
       </c>
-      <c r="AP26" t="n">
+      <c r="AS26" t="n">
         <v>-16.65569270678225</v>
       </c>
     </row>
@@ -5949,127 +7451,138 @@
       <c r="A27" t="n">
         <v>26</v>
       </c>
-      <c r="B27" t="n">
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
         <v>14</v>
       </c>
-      <c r="C27" t="n">
+      <c r="D27" t="n">
         <v>15</v>
       </c>
-      <c r="D27" t="n">
+      <c r="E27" t="n">
         <v>8</v>
       </c>
-      <c r="E27" t="n">
+      <c r="F27" t="n">
+        <v>0.001114029497289337</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0.0001392536871611672</v>
+      </c>
+      <c r="H27" t="n">
         <v>132.0124954287865</v>
       </c>
-      <c r="F27" t="n">
+      <c r="I27" t="n">
         <v>27850.73743223343</v>
       </c>
-      <c r="G27" t="n">
+      <c r="J27" t="n">
         <v>11.2425347791201</v>
       </c>
-      <c r="H27" t="n">
+      <c r="K27" t="n">
         <v>-5.272740957680732e-05</v>
       </c>
-      <c r="I27" t="n">
+      <c r="L27" t="n">
         <v>0.01403178333646043</v>
       </c>
-      <c r="J27" t="n">
+      <c r="M27" t="n">
         <v>2.886834930193329e-07</v>
       </c>
-      <c r="K27" t="n">
+      <c r="N27" t="n">
         <v>0.2774101967679769</v>
       </c>
-      <c r="L27" t="n">
+      <c r="O27" t="n">
         <v>-0.01500512856361739</v>
       </c>
-      <c r="M27" t="n">
+      <c r="P27" t="n">
         <v>11.24364880861739</v>
       </c>
-      <c r="N27" t="n">
+      <c r="Q27" t="n">
         <v>5.272740958393851e-05</v>
       </c>
-      <c r="O27" t="n">
+      <c r="R27" t="n">
         <v>-0.01403178333646046</v>
       </c>
-      <c r="P27" t="n">
+      <c r="S27" t="n">
         <v>-2.886834933623841e-07</v>
       </c>
-      <c r="Q27" t="n">
+      <c r="T27" t="n">
         <v>0.2818139420127958</v>
       </c>
-      <c r="R27" t="n">
+      <c r="U27" t="n">
         <v>0.04505493137084957</v>
       </c>
-      <c r="S27" t="n">
+      <c r="V27" t="n">
         <v>11.2425347791201</v>
       </c>
-      <c r="T27" t="n">
+      <c r="W27" t="n">
         <v>-5.272740957680732e-05</v>
       </c>
-      <c r="U27" t="n">
+      <c r="X27" t="n">
         <v>0.01403178333646043</v>
       </c>
-      <c r="V27" t="n">
+      <c r="Y27" t="n">
         <v>2.886834930193329e-07</v>
       </c>
-      <c r="W27" t="n">
+      <c r="Z27" t="n">
         <v>0.2774101967679769</v>
       </c>
-      <c r="X27" t="n">
+      <c r="AA27" t="n">
         <v>-0.01500512856361739</v>
       </c>
-      <c r="Y27" t="n">
+      <c r="AB27" t="n">
         <v>11.24364880861739</v>
       </c>
-      <c r="Z27" t="n">
+      <c r="AC27" t="n">
         <v>5.272740958393851e-05</v>
       </c>
-      <c r="AA27" t="n">
+      <c r="AD27" t="n">
         <v>-0.01403178333646046</v>
       </c>
-      <c r="AB27" t="n">
+      <c r="AE27" t="n">
         <v>-2.886834933623841e-07</v>
       </c>
-      <c r="AC27" t="n">
+      <c r="AF27" t="n">
         <v>0.2818139420127958</v>
       </c>
-      <c r="AD27" t="n">
+      <c r="AG27" t="n">
         <v>0.04505493137084957</v>
       </c>
-      <c r="AE27" t="n">
+      <c r="AH27" t="n">
         <v>-132.0124954287894</v>
       </c>
-      <c r="AF27" t="n">
+      <c r="AI27" t="n">
         <v>12.49725652639148</v>
       </c>
-      <c r="AG27" t="n">
+      <c r="AJ27" t="n">
         <v>-229.8566828605958</v>
       </c>
-      <c r="AH27" t="n">
+      <c r="AK27" t="n">
         <v>1.232456451699434e-06</v>
       </c>
-      <c r="AI27" t="n">
+      <c r="AL27" t="n">
         <v>916.9826528315087</v>
       </c>
-      <c r="AJ27" t="n">
+      <c r="AM27" t="n">
         <v>16.65569284193676</v>
       </c>
-      <c r="AK27" t="n">
+      <c r="AN27" t="n">
         <v>132.0124954287894</v>
       </c>
-      <c r="AL27" t="n">
+      <c r="AO27" t="n">
         <v>-12.49725652639148</v>
       </c>
-      <c r="AM27" t="n">
+      <c r="AP27" t="n">
         <v>229.8566828605958</v>
       </c>
-      <c r="AN27" t="n">
+      <c r="AQ27" t="n">
         <v>-1.232456451699434e-06</v>
       </c>
-      <c r="AO27" t="n">
+      <c r="AR27" t="n">
         <v>921.8708100532576</v>
       </c>
-      <c r="AP27" t="n">
+      <c r="AS27" t="n">
         <v>83.32235936919508</v>
       </c>
     </row>
@@ -6077,127 +7590,138 @@
       <c r="A28" t="n">
         <v>27</v>
       </c>
-      <c r="B28" t="n">
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
         <v>15</v>
       </c>
-      <c r="C28" t="n">
+      <c r="D28" t="n">
         <v>16</v>
       </c>
-      <c r="D28" t="n">
+      <c r="E28" t="n">
         <v>8</v>
       </c>
-      <c r="E28" t="n">
+      <c r="F28" t="n">
+        <v>0.000105454812604793</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1.318185157559913e-05</v>
+      </c>
+      <c r="H28" t="n">
         <v>12.49639529366798</v>
       </c>
-      <c r="F28" t="n">
+      <c r="I28" t="n">
         <v>2636.370315119826</v>
       </c>
-      <c r="G28" t="n">
+      <c r="J28" t="n">
         <v>11.24364880861739</v>
       </c>
-      <c r="H28" t="n">
+      <c r="K28" t="n">
         <v>5.272740958393851e-05</v>
       </c>
-      <c r="I28" t="n">
+      <c r="L28" t="n">
         <v>-0.01403178333646046</v>
       </c>
-      <c r="J28" t="n">
+      <c r="M28" t="n">
         <v>-2.886834933623841e-07</v>
       </c>
-      <c r="K28" t="n">
+      <c r="N28" t="n">
         <v>0.2818139420127958</v>
       </c>
-      <c r="L28" t="n">
+      <c r="O28" t="n">
         <v>0.04505493137084957</v>
       </c>
-      <c r="M28" t="n">
+      <c r="P28" t="n">
         <v>11.24364880862486</v>
       </c>
-      <c r="N28" t="n">
+      <c r="Q28" t="n">
         <v>-5.272740302085454e-05</v>
       </c>
-      <c r="O28" t="n">
+      <c r="R28" t="n">
         <v>-0.01403178333646063</v>
       </c>
-      <c r="P28" t="n">
+      <c r="S28" t="n">
         <v>2.886833031477993e-07</v>
       </c>
-      <c r="Q28" t="n">
+      <c r="T28" t="n">
         <v>0.2818139420129872</v>
       </c>
-      <c r="R28" t="n">
+      <c r="U28" t="n">
         <v>-0.04505493136909523</v>
       </c>
-      <c r="S28" t="n">
+      <c r="V28" t="n">
         <v>-5.272740958393851e-05</v>
       </c>
-      <c r="T28" t="n">
+      <c r="W28" t="n">
         <v>11.24364880861739</v>
       </c>
-      <c r="U28" t="n">
+      <c r="X28" t="n">
         <v>-0.01403178333646046</v>
       </c>
-      <c r="V28" t="n">
+      <c r="Y28" t="n">
         <v>-0.2818139420127958</v>
       </c>
-      <c r="W28" t="n">
+      <c r="Z28" t="n">
         <v>-2.886834933623841e-07</v>
       </c>
-      <c r="X28" t="n">
+      <c r="AA28" t="n">
         <v>0.04505493137084957</v>
       </c>
-      <c r="Y28" t="n">
+      <c r="AB28" t="n">
         <v>5.272740302085454e-05</v>
       </c>
-      <c r="Z28" t="n">
+      <c r="AC28" t="n">
         <v>11.24364880862486</v>
       </c>
-      <c r="AA28" t="n">
+      <c r="AD28" t="n">
         <v>-0.01403178333646063</v>
       </c>
-      <c r="AB28" t="n">
+      <c r="AE28" t="n">
         <v>-0.2818139420129872</v>
       </c>
-      <c r="AC28" t="n">
+      <c r="AF28" t="n">
         <v>2.886833031477993e-07</v>
       </c>
-      <c r="AD28" t="n">
+      <c r="AG28" t="n">
         <v>-0.04505493136909523</v>
       </c>
-      <c r="AE28" t="n">
+      <c r="AH28" t="n">
         <v>-12.49639529366798</v>
       </c>
-      <c r="AF28" t="n">
+      <c r="AI28" t="n">
         <v>-100.0000000000475</v>
       </c>
-      <c r="AG28" t="n">
+      <c r="AJ28" t="n">
         <v>7.919405605740729e-11</v>
       </c>
-      <c r="AH28" t="n">
+      <c r="AK28" t="n">
         <v>4.084510507595951e-13</v>
       </c>
-      <c r="AI28" t="n">
+      <c r="AL28" t="n">
         <v>-0.0003204388888398558</v>
       </c>
-      <c r="AJ28" t="n">
+      <c r="AM28" t="n">
         <v>-83.32235951285415</v>
       </c>
-      <c r="AK28" t="n">
+      <c r="AN28" t="n">
         <v>12.49639529366798</v>
       </c>
-      <c r="AL28" t="n">
+      <c r="AO28" t="n">
         <v>-99.99999999995248</v>
       </c>
-      <c r="AM28" t="n">
+      <c r="AP28" t="n">
         <v>-7.919405605740729e-11</v>
       </c>
-      <c r="AN28" t="n">
+      <c r="AQ28" t="n">
         <v>-4.084510507595951e-13</v>
       </c>
-      <c r="AO28" t="n">
+      <c r="AR28" t="n">
         <v>0.0003204382552865191</v>
       </c>
-      <c r="AP28" t="n">
+      <c r="AS28" t="n">
         <v>83.32235951247489</v>
       </c>
     </row>
@@ -6205,127 +7729,138 @@
       <c r="A29" t="n">
         <v>28</v>
       </c>
-      <c r="B29" t="n">
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
         <v>16</v>
       </c>
-      <c r="C29" t="n">
+      <c r="D29" t="n">
         <v>13</v>
       </c>
-      <c r="D29" t="n">
+      <c r="E29" t="n">
         <v>8</v>
       </c>
-      <c r="E29" t="n">
+      <c r="F29" t="n">
+        <v>0.001114029497285784</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0.0001392536871607231</v>
+      </c>
+      <c r="H29" t="n">
         <v>132.0124954283655</v>
       </c>
-      <c r="F29" t="n">
+      <c r="I29" t="n">
         <v>27850.73743214461</v>
       </c>
-      <c r="G29" t="n">
+      <c r="J29" t="n">
         <v>11.24364880862486</v>
       </c>
-      <c r="H29" t="n">
+      <c r="K29" t="n">
         <v>-5.272740302085454e-05</v>
       </c>
-      <c r="I29" t="n">
+      <c r="L29" t="n">
         <v>-0.01403178333646063</v>
       </c>
-      <c r="J29" t="n">
+      <c r="M29" t="n">
         <v>2.886833031477993e-07</v>
       </c>
-      <c r="K29" t="n">
+      <c r="N29" t="n">
         <v>0.2818139420129872</v>
       </c>
-      <c r="L29" t="n">
+      <c r="O29" t="n">
         <v>-0.04505493136909523</v>
       </c>
-      <c r="M29" t="n">
+      <c r="P29" t="n">
         <v>11.24253477912758</v>
       </c>
-      <c r="N29" t="n">
+      <c r="Q29" t="n">
         <v>5.272740302799424e-05</v>
       </c>
-      <c r="O29" t="n">
+      <c r="R29" t="n">
         <v>0.01403178333646062</v>
       </c>
-      <c r="P29" t="n">
+      <c r="S29" t="n">
         <v>-2.886833036039658e-07</v>
       </c>
-      <c r="Q29" t="n">
+      <c r="T29" t="n">
         <v>0.2774101967681684</v>
       </c>
-      <c r="R29" t="n">
+      <c r="U29" t="n">
         <v>0.01500512856537014</v>
       </c>
-      <c r="S29" t="n">
+      <c r="V29" t="n">
         <v>-11.24364880862486</v>
       </c>
-      <c r="T29" t="n">
+      <c r="W29" t="n">
         <v>-5.272740302085454e-05</v>
       </c>
-      <c r="U29" t="n">
+      <c r="X29" t="n">
         <v>0.01403178333646063</v>
       </c>
-      <c r="V29" t="n">
+      <c r="Y29" t="n">
         <v>-2.886833031477993e-07</v>
       </c>
-      <c r="W29" t="n">
+      <c r="Z29" t="n">
         <v>0.2818139420129872</v>
       </c>
-      <c r="X29" t="n">
+      <c r="AA29" t="n">
         <v>0.04505493136909523</v>
       </c>
-      <c r="Y29" t="n">
+      <c r="AB29" t="n">
         <v>-11.24253477912758</v>
       </c>
-      <c r="Z29" t="n">
+      <c r="AC29" t="n">
         <v>5.272740302799424e-05</v>
       </c>
-      <c r="AA29" t="n">
+      <c r="AD29" t="n">
         <v>-0.01403178333646062</v>
       </c>
-      <c r="AB29" t="n">
+      <c r="AE29" t="n">
         <v>2.886833036039658e-07</v>
       </c>
-      <c r="AC29" t="n">
+      <c r="AF29" t="n">
         <v>0.2774101967681684</v>
       </c>
-      <c r="AD29" t="n">
+      <c r="AG29" t="n">
         <v>-0.01500512856537014</v>
       </c>
-      <c r="AE29" t="n">
+      <c r="AH29" t="n">
         <v>-132.0124954283237</v>
       </c>
-      <c r="AF29" t="n">
+      <c r="AI29" t="n">
         <v>12.49725652629611</v>
       </c>
-      <c r="AG29" t="n">
+      <c r="AJ29" t="n">
         <v>-229.8566828607552</v>
       </c>
-      <c r="AH29" t="n">
+      <c r="AK29" t="n">
         <v>-1.232455641335499e-06</v>
       </c>
-      <c r="AI29" t="n">
+      <c r="AL29" t="n">
         <v>921.870810053895</v>
       </c>
-      <c r="AJ29" t="n">
+      <c r="AM29" t="n">
         <v>83.32235936881273</v>
       </c>
-      <c r="AK29" t="n">
+      <c r="AN29" t="n">
         <v>132.0124954283237</v>
       </c>
-      <c r="AL29" t="n">
+      <c r="AO29" t="n">
         <v>-12.49725652629611</v>
       </c>
-      <c r="AM29" t="n">
+      <c r="AP29" t="n">
         <v>229.8566828607552</v>
       </c>
-      <c r="AN29" t="n">
+      <c r="AQ29" t="n">
         <v>1.232455641335499e-06</v>
       </c>
-      <c r="AO29" t="n">
+      <c r="AR29" t="n">
         <v>916.9826528321462</v>
       </c>
-      <c r="AP29" t="n">
+      <c r="AS29" t="n">
         <v>16.65569284155616</v>
       </c>
     </row>
@@ -6333,127 +7868,138 @@
       <c r="A30" t="n">
         <v>29</v>
       </c>
-      <c r="B30" t="n">
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
         <v>17</v>
       </c>
-      <c r="C30" t="n">
+      <c r="D30" t="n">
         <v>18</v>
       </c>
-      <c r="D30" t="n">
+      <c r="E30" t="n">
         <v>8</v>
       </c>
-      <c r="E30" t="n">
+      <c r="F30" t="n">
+        <v>-0.0001054632224549705</v>
+      </c>
+      <c r="G30" t="n">
+        <v>-1.318290280687131e-05</v>
+      </c>
+      <c r="H30" t="n">
         <v>-12.49739186091401</v>
       </c>
-      <c r="F30" t="n">
+      <c r="I30" t="n">
         <v>-2636.580561374263</v>
       </c>
-      <c r="G30" t="n">
+      <c r="J30" t="n">
         <v>12.7636275507655</v>
       </c>
-      <c r="H30" t="n">
+      <c r="K30" t="n">
         <v>5.273160743815383e-05</v>
       </c>
-      <c r="I30" t="n">
+      <c r="L30" t="n">
         <v>0.01458744045581826</v>
       </c>
-      <c r="J30" t="n">
+      <c r="M30" t="n">
         <v>1.041020896839185e-07</v>
       </c>
-      <c r="K30" t="n">
+      <c r="N30" t="n">
         <v>0.1191579135705716</v>
       </c>
-      <c r="L30" t="n">
+      <c r="O30" t="n">
         <v>0.01500512783931789</v>
       </c>
-      <c r="M30" t="n">
+      <c r="P30" t="n">
         <v>12.76362755075735</v>
       </c>
-      <c r="N30" t="n">
+      <c r="Q30" t="n">
         <v>-5.273161501681668e-05</v>
       </c>
-      <c r="O30" t="n">
+      <c r="R30" t="n">
         <v>0.01458744045581829</v>
       </c>
-      <c r="P30" t="n">
+      <c r="S30" t="n">
         <v>-1.041020131429611e-07</v>
       </c>
-      <c r="Q30" t="n">
+      <c r="T30" t="n">
         <v>0.1191579135705384</v>
       </c>
-      <c r="R30" t="n">
+      <c r="U30" t="n">
         <v>-0.01500512783735091</v>
       </c>
-      <c r="S30" t="n">
+      <c r="V30" t="n">
         <v>5.273160743815383e-05</v>
       </c>
-      <c r="T30" t="n">
+      <c r="W30" t="n">
         <v>-12.7636275507655</v>
       </c>
-      <c r="U30" t="n">
+      <c r="X30" t="n">
         <v>0.01458744045581826</v>
       </c>
-      <c r="V30" t="n">
+      <c r="Y30" t="n">
         <v>0.1191579135705716</v>
       </c>
-      <c r="W30" t="n">
+      <c r="Z30" t="n">
         <v>-1.041020896839185e-07</v>
       </c>
-      <c r="X30" t="n">
+      <c r="AA30" t="n">
         <v>0.01500512783931789</v>
       </c>
-      <c r="Y30" t="n">
+      <c r="AB30" t="n">
         <v>-5.273161501681668e-05</v>
       </c>
-      <c r="Z30" t="n">
+      <c r="AC30" t="n">
         <v>-12.76362755075735</v>
       </c>
-      <c r="AA30" t="n">
+      <c r="AD30" t="n">
         <v>0.01458744045581829</v>
       </c>
-      <c r="AB30" t="n">
+      <c r="AE30" t="n">
         <v>0.1191579135705384</v>
       </c>
-      <c r="AC30" t="n">
+      <c r="AF30" t="n">
         <v>1.041020131429611e-07</v>
       </c>
-      <c r="AD30" t="n">
+      <c r="AG30" t="n">
         <v>-0.01500512783735091</v>
       </c>
-      <c r="AE30" t="n">
+      <c r="AH30" t="n">
         <v>12.49739186091401</v>
       </c>
-      <c r="AF30" t="n">
+      <c r="AI30" t="n">
         <v>-2.91038304567337e-11</v>
       </c>
-      <c r="AG30" t="n">
+      <c r="AJ30" t="n">
         <v>3.185670624457392e-11</v>
       </c>
-      <c r="AH30" t="n">
+      <c r="AK30" t="n">
         <v>7.083222897108499e-14</v>
       </c>
-      <c r="AI30" t="n">
+      <c r="AL30" t="n">
         <v>-0.000115553404494969</v>
       </c>
-      <c r="AJ30" t="n">
+      <c r="AM30" t="n">
         <v>16.65569190043516</v>
       </c>
-      <c r="AK30" t="n">
+      <c r="AN30" t="n">
         <v>-12.49739186091401</v>
       </c>
-      <c r="AL30" t="n">
+      <c r="AO30" t="n">
         <v>2.91038304567337e-11</v>
       </c>
-      <c r="AM30" t="n">
+      <c r="AP30" t="n">
         <v>-3.185670624457392e-11</v>
       </c>
-      <c r="AN30" t="n">
+      <c r="AQ30" t="n">
         <v>-7.083222897108499e-14</v>
       </c>
-      <c r="AO30" t="n">
+      <c r="AR30" t="n">
         <v>0.0001155531496422071</v>
       </c>
-      <c r="AP30" t="n">
+      <c r="AS30" t="n">
         <v>-16.65569190066799</v>
       </c>
     </row>
@@ -6461,127 +8007,138 @@
       <c r="A31" t="n">
         <v>30</v>
       </c>
-      <c r="B31" t="n">
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
         <v>18</v>
       </c>
-      <c r="C31" t="n">
+      <c r="D31" t="n">
         <v>19</v>
       </c>
-      <c r="D31" t="n">
+      <c r="E31" t="n">
         <v>8</v>
       </c>
-      <c r="E31" t="n">
+      <c r="F31" t="n">
+        <v>0.0006898099748529063</v>
+      </c>
+      <c r="G31" t="n">
+        <v>8.622624685661329e-05</v>
+      </c>
+      <c r="H31" t="n">
         <v>81.74248202006939</v>
       </c>
-      <c r="F31" t="n">
+      <c r="I31" t="n">
         <v>17245.24937132265</v>
       </c>
-      <c r="G31" t="n">
+      <c r="J31" t="n">
         <v>12.76362755075735</v>
       </c>
-      <c r="H31" t="n">
+      <c r="K31" t="n">
         <v>-5.273161501681668e-05</v>
       </c>
-      <c r="I31" t="n">
+      <c r="L31" t="n">
         <v>0.01458744045581829</v>
       </c>
-      <c r="J31" t="n">
+      <c r="M31" t="n">
         <v>-1.041020131429611e-07</v>
       </c>
-      <c r="K31" t="n">
+      <c r="N31" t="n">
         <v>0.1191579135705384</v>
       </c>
-      <c r="L31" t="n">
+      <c r="O31" t="n">
         <v>-0.01500512783735091</v>
       </c>
-      <c r="M31" t="n">
+      <c r="P31" t="n">
         <v>12.76431736073221</v>
       </c>
-      <c r="N31" t="n">
+      <c r="Q31" t="n">
         <v>5.273161502770671e-05</v>
       </c>
-      <c r="O31" t="n">
+      <c r="R31" t="n">
         <v>-0.01458744045581832</v>
       </c>
-      <c r="P31" t="n">
+      <c r="S31" t="n">
         <v>1.041020126456332e-07</v>
       </c>
-      <c r="Q31" t="n">
+      <c r="T31" t="n">
         <v>0.09905190241355175</v>
       </c>
-      <c r="R31" t="n">
+      <c r="U31" t="n">
         <v>0.04505493222254756</v>
       </c>
-      <c r="S31" t="n">
+      <c r="V31" t="n">
         <v>12.76362755075735</v>
       </c>
-      <c r="T31" t="n">
+      <c r="W31" t="n">
         <v>-5.273161501681668e-05</v>
       </c>
-      <c r="U31" t="n">
+      <c r="X31" t="n">
         <v>0.01458744045581829</v>
       </c>
-      <c r="V31" t="n">
+      <c r="Y31" t="n">
         <v>-1.041020131429611e-07</v>
       </c>
-      <c r="W31" t="n">
+      <c r="Z31" t="n">
         <v>0.1191579135705384</v>
       </c>
-      <c r="X31" t="n">
+      <c r="AA31" t="n">
         <v>-0.01500512783735091</v>
       </c>
-      <c r="Y31" t="n">
+      <c r="AB31" t="n">
         <v>12.76431736073221</v>
       </c>
-      <c r="Z31" t="n">
+      <c r="AC31" t="n">
         <v>5.273161502770671e-05</v>
       </c>
-      <c r="AA31" t="n">
+      <c r="AD31" t="n">
         <v>-0.01458744045581832</v>
       </c>
-      <c r="AB31" t="n">
+      <c r="AE31" t="n">
         <v>1.041020126456332e-07</v>
       </c>
-      <c r="AC31" t="n">
+      <c r="AF31" t="n">
         <v>0.09905190241355175</v>
       </c>
-      <c r="AD31" t="n">
+      <c r="AG31" t="n">
         <v>0.04505493222254756</v>
       </c>
-      <c r="AE31" t="n">
+      <c r="AH31" t="n">
         <v>-81.74248202005401</v>
       </c>
-      <c r="AF31" t="n">
+      <c r="AI31" t="n">
         <v>12.49725630796159</v>
       </c>
-      <c r="AG31" t="n">
+      <c r="AJ31" t="n">
         <v>-87.79382485851036</v>
       </c>
-      <c r="AH31" t="n">
+      <c r="AK31" t="n">
         <v>-4.444355165871917e-07</v>
       </c>
-      <c r="AI31" t="n">
+      <c r="AL31" t="n">
         <v>362.3341356261689</v>
       </c>
-      <c r="AJ31" t="n">
+      <c r="AM31" t="n">
         <v>16.65569189860274</v>
       </c>
-      <c r="AK31" t="n">
+      <c r="AN31" t="n">
         <v>81.74248202005401</v>
       </c>
-      <c r="AL31" t="n">
+      <c r="AO31" t="n">
         <v>-12.49725630796159</v>
       </c>
-      <c r="AM31" t="n">
+      <c r="AP31" t="n">
         <v>87.79382485851036</v>
       </c>
-      <c r="AN31" t="n">
+      <c r="AQ31" t="n">
         <v>4.444355165871917e-07</v>
       </c>
-      <c r="AO31" t="n">
+      <c r="AR31" t="n">
         <v>340.0164632419138</v>
       </c>
-      <c r="AP31" t="n">
+      <c r="AS31" t="n">
         <v>83.32235856509004</v>
       </c>
     </row>
@@ -6589,127 +8146,138 @@
       <c r="A32" t="n">
         <v>31</v>
       </c>
-      <c r="B32" t="n">
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
         <v>19</v>
       </c>
-      <c r="C32" t="n">
+      <c r="D32" t="n">
         <v>20</v>
       </c>
-      <c r="D32" t="n">
+      <c r="E32" t="n">
         <v>8</v>
       </c>
-      <c r="E32" t="n">
+      <c r="F32" t="n">
+        <v>0.000105463222454975</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1.318290280687187e-05</v>
+      </c>
+      <c r="H32" t="n">
         <v>12.49739186091453</v>
       </c>
-      <c r="F32" t="n">
+      <c r="I32" t="n">
         <v>2636.580561374374</v>
       </c>
-      <c r="G32" t="n">
+      <c r="J32" t="n">
         <v>12.76431736073221</v>
       </c>
-      <c r="H32" t="n">
+      <c r="K32" t="n">
         <v>5.273161502770671e-05</v>
       </c>
-      <c r="I32" t="n">
+      <c r="L32" t="n">
         <v>-0.01458744045581832</v>
       </c>
-      <c r="J32" t="n">
+      <c r="M32" t="n">
         <v>1.041020126456332e-07</v>
       </c>
-      <c r="K32" t="n">
+      <c r="N32" t="n">
         <v>0.09905190241355175</v>
       </c>
-      <c r="L32" t="n">
+      <c r="O32" t="n">
         <v>0.04505493222254756</v>
       </c>
-      <c r="M32" t="n">
+      <c r="P32" t="n">
         <v>12.76431736074036</v>
       </c>
-      <c r="N32" t="n">
+      <c r="Q32" t="n">
         <v>-5.273160742726827e-05</v>
       </c>
-      <c r="O32" t="n">
+      <c r="R32" t="n">
         <v>-0.01458744045581826</v>
       </c>
-      <c r="P32" t="n">
+      <c r="S32" t="n">
         <v>-1.041020899760041e-07</v>
       </c>
-      <c r="Q32" t="n">
+      <c r="T32" t="n">
         <v>0.09905190241358573</v>
       </c>
-      <c r="R32" t="n">
+      <c r="U32" t="n">
         <v>-0.04505493222058038</v>
       </c>
-      <c r="S32" t="n">
+      <c r="V32" t="n">
         <v>-5.273161502770671e-05</v>
       </c>
-      <c r="T32" t="n">
+      <c r="W32" t="n">
         <v>12.76431736073221</v>
       </c>
-      <c r="U32" t="n">
+      <c r="X32" t="n">
         <v>-0.01458744045581832</v>
       </c>
-      <c r="V32" t="n">
+      <c r="Y32" t="n">
         <v>-0.09905190241355175</v>
       </c>
-      <c r="W32" t="n">
+      <c r="Z32" t="n">
         <v>1.041020126456332e-07</v>
       </c>
-      <c r="X32" t="n">
+      <c r="AA32" t="n">
         <v>0.04505493222254756</v>
       </c>
-      <c r="Y32" t="n">
+      <c r="AB32" t="n">
         <v>5.273160742726827e-05</v>
       </c>
-      <c r="Z32" t="n">
+      <c r="AC32" t="n">
         <v>12.76431736074036</v>
       </c>
-      <c r="AA32" t="n">
+      <c r="AD32" t="n">
         <v>-0.01458744045581826</v>
       </c>
-      <c r="AB32" t="n">
+      <c r="AE32" t="n">
         <v>-0.09905190241358573</v>
       </c>
-      <c r="AC32" t="n">
+      <c r="AF32" t="n">
         <v>-1.041020899760041e-07</v>
       </c>
-      <c r="AD32" t="n">
+      <c r="AG32" t="n">
         <v>-0.04505493222058038</v>
       </c>
-      <c r="AE32" t="n">
+      <c r="AH32" t="n">
         <v>-12.49739186091453</v>
       </c>
-      <c r="AF32" t="n">
+      <c r="AI32" t="n">
         <v>-100.0000000000293</v>
       </c>
-      <c r="AG32" t="n">
+      <c r="AJ32" t="n">
         <v>3.218251569913049e-11</v>
       </c>
-      <c r="AH32" t="n">
+      <c r="AK32" t="n">
         <v>7.255307465925398e-14</v>
       </c>
-      <c r="AI32" t="n">
+      <c r="AL32" t="n">
         <v>0.0001155531482243991</v>
       </c>
-      <c r="AJ32" t="n">
+      <c r="AM32" t="n">
         <v>-83.32235856751535</v>
       </c>
-      <c r="AK32" t="n">
+      <c r="AN32" t="n">
         <v>12.49739186091453</v>
       </c>
-      <c r="AL32" t="n">
+      <c r="AO32" t="n">
         <v>-99.99999999997067</v>
       </c>
-      <c r="AM32" t="n">
+      <c r="AP32" t="n">
         <v>-3.218251569913049e-11</v>
       </c>
-      <c r="AN32" t="n">
+      <c r="AQ32" t="n">
         <v>-7.255307465925398e-14</v>
       </c>
-      <c r="AO32" t="n">
+      <c r="AR32" t="n">
         <v>-0.0001155534056854128</v>
       </c>
-      <c r="AP32" t="n">
+      <c r="AS32" t="n">
         <v>83.32235856727888</v>
       </c>
     </row>
@@ -6717,127 +8285,138 @@
       <c r="A33" t="n">
         <v>32</v>
       </c>
-      <c r="B33" t="n">
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>F</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
         <v>20</v>
       </c>
-      <c r="C33" t="n">
+      <c r="D33" t="n">
         <v>17</v>
       </c>
-      <c r="D33" t="n">
+      <c r="E33" t="n">
         <v>8</v>
       </c>
-      <c r="E33" t="n">
+      <c r="F33" t="n">
+        <v>0.0006898099748582354</v>
+      </c>
+      <c r="G33" t="n">
+        <v>8.622624685727942e-05</v>
+      </c>
+      <c r="H33" t="n">
         <v>81.74248202070089</v>
       </c>
-      <c r="F33" t="n">
+      <c r="I33" t="n">
         <v>17245.24937145588</v>
       </c>
-      <c r="G33" t="n">
+      <c r="J33" t="n">
         <v>12.76431736074036</v>
       </c>
-      <c r="H33" t="n">
+      <c r="K33" t="n">
         <v>-5.273160742726827e-05</v>
       </c>
-      <c r="I33" t="n">
+      <c r="L33" t="n">
         <v>-0.01458744045581826</v>
       </c>
-      <c r="J33" t="n">
+      <c r="M33" t="n">
         <v>-1.041020899760041e-07</v>
       </c>
-      <c r="K33" t="n">
+      <c r="N33" t="n">
         <v>0.09905190241358573</v>
       </c>
-      <c r="L33" t="n">
+      <c r="O33" t="n">
         <v>-0.04505493222058038</v>
       </c>
-      <c r="M33" t="n">
+      <c r="P33" t="n">
         <v>12.7636275507655</v>
       </c>
-      <c r="N33" t="n">
+      <c r="Q33" t="n">
         <v>5.273160743815383e-05</v>
       </c>
-      <c r="O33" t="n">
+      <c r="R33" t="n">
         <v>0.01458744045581826</v>
       </c>
-      <c r="P33" t="n">
+      <c r="S33" t="n">
         <v>1.041020896839185e-07</v>
       </c>
-      <c r="Q33" t="n">
+      <c r="T33" t="n">
         <v>0.1191579135705716</v>
       </c>
-      <c r="R33" t="n">
+      <c r="U33" t="n">
         <v>0.01500512783931789</v>
       </c>
-      <c r="S33" t="n">
+      <c r="V33" t="n">
         <v>-12.76431736074036</v>
       </c>
-      <c r="T33" t="n">
+      <c r="W33" t="n">
         <v>-5.273160742726827e-05</v>
       </c>
-      <c r="U33" t="n">
+      <c r="X33" t="n">
         <v>0.01458744045581826</v>
       </c>
-      <c r="V33" t="n">
+      <c r="Y33" t="n">
         <v>1.041020899760041e-07</v>
       </c>
-      <c r="W33" t="n">
+      <c r="Z33" t="n">
         <v>0.09905190241358573</v>
       </c>
-      <c r="X33" t="n">
+      <c r="AA33" t="n">
         <v>0.04505493222058038</v>
       </c>
-      <c r="Y33" t="n">
+      <c r="AB33" t="n">
         <v>-12.7636275507655</v>
       </c>
-      <c r="Z33" t="n">
+      <c r="AC33" t="n">
         <v>5.273160743815383e-05</v>
       </c>
-      <c r="AA33" t="n">
+      <c r="AD33" t="n">
         <v>-0.01458744045581826</v>
       </c>
-      <c r="AB33" t="n">
+      <c r="AE33" t="n">
         <v>-1.041020896839185e-07</v>
       </c>
-      <c r="AC33" t="n">
+      <c r="AF33" t="n">
         <v>0.1191579135705716</v>
       </c>
-      <c r="AD33" t="n">
+      <c r="AG33" t="n">
         <v>-0.01500512783931789</v>
       </c>
-      <c r="AE33" t="n">
+      <c r="AH33" t="n">
         <v>-81.7424820207525</v>
       </c>
-      <c r="AF33" t="n">
+      <c r="AI33" t="n">
         <v>12.49725630790358</v>
       </c>
-      <c r="AG33" t="n">
+      <c r="AJ33" t="n">
         <v>-87.79382485853831</v>
       </c>
-      <c r="AH33" t="n">
+      <c r="AK33" t="n">
         <v>4.444358450432963e-07</v>
       </c>
-      <c r="AI33" t="n">
+      <c r="AL33" t="n">
         <v>340.0164632420261</v>
       </c>
-      <c r="AJ33" t="n">
+      <c r="AM33" t="n">
         <v>83.32235856485785</v>
       </c>
-      <c r="AK33" t="n">
+      <c r="AN33" t="n">
         <v>81.7424820207525</v>
       </c>
-      <c r="AL33" t="n">
+      <c r="AO33" t="n">
         <v>-12.49725630790358</v>
       </c>
-      <c r="AM33" t="n">
+      <c r="AP33" t="n">
         <v>87.79382485853831</v>
       </c>
-      <c r="AN33" t="n">
+      <c r="AQ33" t="n">
         <v>-4.444358450432963e-07</v>
       </c>
-      <c r="AO33" t="n">
+      <c r="AR33" t="n">
         <v>362.3341356262804</v>
       </c>
-      <c r="AP33" t="n">
+      <c r="AS33" t="n">
         <v>16.65569189837078</v>
       </c>
     </row>
